--- a/inst/extdata/MetricNames.xlsx
+++ b/inst/extdata/MetricNames.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/ben_block_tetratech_com/Documents/GitHub/BioMonTools/inst/extdata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erik.Leppo\Documents\GitHub\BioMonTools\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="13_ncr:1_{D068F702-01C0-4E14-90ED-E7975EAE9E5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C057D4FE-96BF-4E17-BAC0-733CDEE6ED68}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A88802A9-394E-41BA-BC9A-F8BD19AC7D9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NOTES" sheetId="4" r:id="rId1"/>
@@ -230,7 +230,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8014" uniqueCount="2344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8015" uniqueCount="2345">
   <si>
     <t>nt_total</t>
   </si>
@@ -7262,6 +7262,9 @@
   </si>
   <si>
     <t>presence absence of Genus Rhinichthys and/or Family Catostomidae</t>
+  </si>
+  <si>
+    <t>Add new metrics, Issue #  xyz</t>
   </si>
 </sst>
 </file>
@@ -8036,7 +8039,7 @@
   <sheetPr>
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:N110"/>
+  <dimension ref="A1:N111"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -8064,7 +8067,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="24">
-        <v>45827</v>
+        <v>46119</v>
       </c>
       <c r="J5" s="43" t="s">
         <v>1999</v>
@@ -8097,7 +8100,7 @@
       </c>
       <c r="B7" s="26" t="str">
         <f ca="1">LEFT(CELL("filename",B7),FIND("]",CELL("filename",B7)))</f>
-        <v>https://tetratechinc-my.sharepoint.com/personal/ben_block_tetratech_com/Documents/GitHub/BioMonTools/inst/extdata/[MetricNames.xlsx]</v>
+        <v>C:\Users\Erik.Leppo\Documents\GitHub\BioMonTools\inst\extdata\[MetricNames.xlsx]</v>
       </c>
       <c r="G7" t="s">
         <v>652</v>
@@ -8944,6 +8947,14 @@
       </c>
       <c r="B110" t="s">
         <v>2313</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" s="24">
+        <v>46017</v>
+      </c>
+      <c r="B111" t="s">
+        <v>2344</v>
       </c>
     </row>
   </sheetData>

--- a/inst/extdata/MetricNames.xlsx
+++ b/inst/extdata/MetricNames.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erik.Leppo\Documents\GitHub\BioMonTools\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A88802A9-394E-41BA-BC9A-F8BD19AC7D9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A8B33B6-7B01-433D-AAC8-67480E162A4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NOTES" sheetId="4" r:id="rId1"/>
     <sheet name="MetricMetadata" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">MetricMetadata!$A$5:$N$1204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">MetricMetadata!$A$5:$N$1207</definedName>
     <definedName name="FileName" localSheetId="0">NOTES!$B$8</definedName>
     <definedName name="FileName">#REF!</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">MetricMetadata!$A:$A,MetricMetadata!$5:$5</definedName>
@@ -225,12 +225,36 @@
         </r>
       </text>
     </comment>
+    <comment ref="C1210" authorId="1" shapeId="0" xr:uid="{905B8F54-2067-4968-9CE3-86EB0853D83A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Leppo, Erik:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Not implemented yet</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8015" uniqueCount="2345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8057" uniqueCount="2372">
   <si>
     <t>nt_total</t>
   </si>
@@ -7265,6 +7289,87 @@
   </si>
   <si>
     <t>Add new metrics, Issue #  xyz</t>
+  </si>
+  <si>
+    <t>https://github.com/leppott/BioMonTools/issues/140</t>
+  </si>
+  <si>
+    <t>https://github.com/leppott/BioMonTools/issues/129</t>
+  </si>
+  <si>
+    <t>https://github.com/leppott/BioMonTools/issues/118</t>
+  </si>
+  <si>
+    <t>https://github.com/leppott/BioMonTools/issues/120</t>
+  </si>
+  <si>
+    <t>https://github.com/leppott/BioMonTools/issues/121</t>
+  </si>
+  <si>
+    <t>https://github.com/leppott/BioMonTools/issues/79</t>
+  </si>
+  <si>
+    <t>https://github.com/leppott/BioMonTools/issues/73</t>
+  </si>
+  <si>
+    <t>Add new metrics, Issue #140, Boise BCG</t>
+  </si>
+  <si>
+    <t>pt_NonIns_BCG_att456t</t>
+  </si>
+  <si>
+    <t>pi_dom01_BCG_att456</t>
+  </si>
+  <si>
+    <t>Boise</t>
+  </si>
+  <si>
+    <t>percent of taxa - non-Insecta, BCG attributes 4, 5, or 6t</t>
+  </si>
+  <si>
+    <t>pi_dom01_BCG_att456t</t>
+  </si>
+  <si>
+    <t>percent individuals, dominant 1, BCG attributes 4, 5, or 6t</t>
+  </si>
+  <si>
+    <t>percent individuals, dominant 1, BCG attributes 4, 5, or 6</t>
+  </si>
+  <si>
+    <t>percent individuals, dominant 1, BCG attributes 4 or 5</t>
+  </si>
+  <si>
+    <t>percent individuals, dominant 1, BCG attribute 5</t>
+  </si>
+  <si>
+    <t>percent individuals, dominant 1, BCG attribute 4</t>
+  </si>
+  <si>
+    <t>percent individuals, dominant 1, BCG attribute 5a</t>
+  </si>
+  <si>
+    <t>percent individuals, dominant 1, BCG attributes 5a or 6a</t>
+  </si>
+  <si>
+    <t>percent individuals, dominant 1, BCG attributes 5, 5a, or 6a</t>
+  </si>
+  <si>
+    <t>Missing names from Excel in metric.values function</t>
+  </si>
+  <si>
+    <t>nt_ffg2_deepdep</t>
+  </si>
+  <si>
+    <t>pi_ffg2_deepdep</t>
+  </si>
+  <si>
+    <t>number of individuals - per square meter</t>
+  </si>
+  <si>
+    <t>number of taxa - ffg2 - deep deposit feeders</t>
+  </si>
+  <si>
+    <t>percent of individuals - ffg2 - deep deposit feeders</t>
   </si>
 </sst>
 </file>
@@ -7542,7 +7647,7 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -7698,6 +7803,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Bad" xfId="6" builtinId="27"/>
@@ -8039,7 +8145,7 @@
   <sheetPr>
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:N111"/>
+  <dimension ref="A1:N113"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -8084,8 +8190,8 @@
         <v>1832</v>
       </c>
       <c r="J6" s="42">
-        <f>COUNTA(MetricMetadata!$H$6:$H$2025)</f>
-        <v>1199</v>
+        <f>COUNTA(MetricMetadata!$H$6:$H$2023)</f>
+        <v>1205</v>
       </c>
       <c r="M6" t="s">
         <v>2012</v>
@@ -8106,8 +8212,8 @@
         <v>652</v>
       </c>
       <c r="H7">
-        <f>COUNTIF(MetricMetadata!$H$6:$H$2025,G7)</f>
-        <v>548</v>
+        <f>COUNTIF(MetricMetadata!$H$6:$H$2023,G7)</f>
+        <v>554</v>
       </c>
       <c r="M7" t="s">
         <v>2014</v>
@@ -8128,7 +8234,7 @@
         <v>391</v>
       </c>
       <c r="H8">
-        <f>COUNTIF(MetricMetadata!$H$6:$H$2025,G8)</f>
+        <f>COUNTIF(MetricMetadata!$H$6:$H$2023,G8)</f>
         <v>379</v>
       </c>
       <c r="M8" t="s">
@@ -8150,7 +8256,7 @@
         <v>799</v>
       </c>
       <c r="H9">
-        <f>COUNTIF(MetricMetadata!$H$6:$H$2025,G9)</f>
+        <f>COUNTIF(MetricMetadata!$H$6:$H$2023,G9)</f>
         <v>253</v>
       </c>
       <c r="M9" t="s">
@@ -8165,7 +8271,7 @@
         <v>1955</v>
       </c>
       <c r="H10">
-        <f>COUNTIF(MetricMetadata!$H$6:$H$2025,G10)</f>
+        <f>COUNTIF(MetricMetadata!$H$6:$H$2023,G10)</f>
         <v>16</v>
       </c>
       <c r="M10" t="s">
@@ -8183,7 +8289,7 @@
         <v>390</v>
       </c>
       <c r="H11">
-        <f>COUNTIF(MetricMetadata!$H$6:$H$2025,G11)</f>
+        <f>COUNTIF(MetricMetadata!$H$6:$H$2023,G11)</f>
         <v>3</v>
       </c>
       <c r="M11" t="s">
@@ -8198,7 +8304,7 @@
         <v>208</v>
       </c>
       <c r="H12">
-        <f>COUNTIF(MetricMetadata!$H$6:$H$2025,G12)</f>
+        <f>COUNTIF(MetricMetadata!$H$6:$H$2023,G12)</f>
         <v>0</v>
       </c>
       <c r="I12" s="40" t="s">
@@ -8219,7 +8325,7 @@
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="H14" s="41">
         <f>SUM(H7:H11)</f>
-        <v>1199</v>
+        <v>1205</v>
       </c>
       <c r="I14" t="s">
         <v>1998</v>
@@ -8465,7 +8571,7 @@
         <v>1428</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="24">
         <v>44543</v>
       </c>
@@ -8473,7 +8579,7 @@
         <v>1549</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="24">
         <v>44564</v>
       </c>
@@ -8481,12 +8587,12 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>1555</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="24">
         <v>44593</v>
       </c>
@@ -8494,7 +8600,7 @@
         <v>1573</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="24">
         <v>44595</v>
       </c>
@@ -8502,7 +8608,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="24">
         <v>44603</v>
       </c>
@@ -8510,7 +8616,7 @@
         <v>1586</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="24">
         <v>44642</v>
       </c>
@@ -8518,7 +8624,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="24">
         <v>44648</v>
       </c>
@@ -8526,7 +8632,7 @@
         <v>1622</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="24">
         <v>44650</v>
       </c>
@@ -8534,7 +8640,7 @@
         <v>1637</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="24">
         <v>44699</v>
       </c>
@@ -8542,15 +8648,18 @@
         <v>1686</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="24">
         <v>44712</v>
       </c>
       <c r="B59" t="s">
         <v>1749</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C59" s="59" t="s">
+        <v>2351</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="24">
         <v>44721</v>
       </c>
@@ -8558,7 +8667,7 @@
         <v>1751</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="24">
         <v>44826</v>
       </c>
@@ -8566,15 +8675,18 @@
         <v>1770</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="24">
         <v>44831</v>
       </c>
       <c r="B62" t="s">
         <v>1777</v>
       </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C62" s="59" t="s">
+        <v>2350</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="24">
         <v>44833</v>
       </c>
@@ -8582,7 +8694,7 @@
         <v>1794</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="24">
         <v>44875</v>
       </c>
@@ -8843,7 +8955,7 @@
         <v>2188</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="24">
         <v>45595</v>
       </c>
@@ -8851,7 +8963,7 @@
         <v>2193</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="24">
         <v>45597</v>
       </c>
@@ -8859,7 +8971,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="24">
         <v>45601</v>
       </c>
@@ -8867,12 +8979,12 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B100" t="s">
         <v>2215</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="24">
         <v>45602</v>
       </c>
@@ -8880,12 +8992,12 @@
         <v>2223</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B102" t="s">
         <v>2224</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="24">
         <v>45603</v>
       </c>
@@ -8893,7 +9005,7 @@
         <v>2237</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="24">
         <v>45616</v>
       </c>
@@ -8901,7 +9013,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="24">
         <v>45671</v>
       </c>
@@ -8909,7 +9021,7 @@
         <v>2252</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="24">
         <v>45698</v>
       </c>
@@ -8917,44 +9029,75 @@
         <v>2253</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="24">
         <v>45820</v>
       </c>
       <c r="B107" t="s">
         <v>2292</v>
       </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C107" s="59" t="s">
+        <v>2347</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="24">
         <v>45821</v>
       </c>
       <c r="B108" t="s">
         <v>2291</v>
       </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C108" s="59" t="s">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="24">
         <v>45827</v>
       </c>
       <c r="B109" t="s">
         <v>2305</v>
       </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C109" s="59" t="s">
+        <v>2349</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="24">
         <v>46017</v>
       </c>
       <c r="B110" t="s">
         <v>2313</v>
       </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C110" s="59" t="s">
+        <v>2346</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="24">
         <v>46017</v>
       </c>
       <c r="B111" t="s">
         <v>2344</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="24">
+        <v>46157</v>
+      </c>
+      <c r="B112" t="s">
+        <v>2352</v>
+      </c>
+      <c r="C112" s="59" t="s">
+        <v>2345</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" s="24">
+        <v>46160</v>
+      </c>
+      <c r="B113" t="s">
+        <v>2366</v>
       </c>
     </row>
   </sheetData>
@@ -8970,16 +9113,23 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="A4" r:id="rId1" xr:uid="{FB228F59-1020-4061-AC4D-14560B8C12D4}"/>
+    <hyperlink ref="C112" r:id="rId2" xr:uid="{831CAA54-903C-4FA5-AB39-A18B3A70A40A}"/>
+    <hyperlink ref="C110" r:id="rId3" xr:uid="{CCAC8755-0EF9-45BB-8BB3-9267D5591883}"/>
+    <hyperlink ref="C109" r:id="rId4" xr:uid="{BB9D8941-A137-4421-8D3E-98A3BAEECA65}"/>
+    <hyperlink ref="C108" r:id="rId5" xr:uid="{F542B19C-9CEB-4DFB-A4A7-B867EA4E19BD}"/>
+    <hyperlink ref="C107" r:id="rId6" xr:uid="{9D23F2DB-3FE6-4075-8E01-AA0D79A7BA2D}"/>
+    <hyperlink ref="C62" r:id="rId7" xr:uid="{1F677AEA-DA00-4CC3-A569-4944779084C6}"/>
+    <hyperlink ref="C59" r:id="rId8" xr:uid="{E61D1D46-D820-43C4-83A4-C18E3A3A4142}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="91" orientation="portrait" r:id="rId2"/>
+  <pageSetup scale="91" orientation="portrait" r:id="rId9"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;A</oddHeader>
     <oddFooter>&amp;L&amp;D&amp;CPage &amp;P of &amp;N&amp;R&amp;F</oddFooter>
   </headerFooter>
-  <legacyDrawing r:id="rId3"/>
+  <legacyDrawing r:id="rId10"/>
   <tableParts count="1">
-    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId11"/>
   </tableParts>
 </worksheet>
 </file>
@@ -8989,7 +9139,7 @@
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
-  <dimension ref="A1:N2025"/>
+  <dimension ref="A1:N2023"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.7109375" style="4" bestFit="1" customWidth="1"/>
@@ -9030,7 +9180,7 @@
     </row>
     <row r="2" spans="1:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>46017</v>
+        <v>46160</v>
       </c>
       <c r="B2" s="38" t="s">
         <v>1762</v>
@@ -9049,12 +9199,12 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
-        <f>SUBTOTAL(3,A6:A2109)</f>
-        <v>1199</v>
+        <f>SUBTOTAL(3,A6:A2107)</f>
+        <v>1205</v>
       </c>
       <c r="B3" s="4">
         <f>COUNTIF($B$6:$B$1001,B2)</f>
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="H3" s="32" t="s">
         <v>651</v>
@@ -25330,8 +25480,8 @@
       <c r="A452" s="7" t="s">
         <v>1530</v>
       </c>
-      <c r="B452" s="39" t="s">
-        <v>1762</v>
+      <c r="B452" s="7" t="s">
+        <v>2362</v>
       </c>
       <c r="C452" s="16" t="s">
         <v>180</v>
@@ -25366,8 +25516,8 @@
       <c r="A453" s="7" t="s">
         <v>1531</v>
       </c>
-      <c r="B453" s="39" t="s">
-        <v>1762</v>
+      <c r="B453" s="7" t="s">
+        <v>2361</v>
       </c>
       <c r="C453" s="16" t="s">
         <v>180</v>
@@ -42990,8 +43140,8 @@
       <c r="A932" s="7" t="s">
         <v>1530</v>
       </c>
-      <c r="B932" s="38" t="s">
-        <v>1762</v>
+      <c r="B932" s="7" t="s">
+        <v>2362</v>
       </c>
       <c r="C932" s="12" t="s">
         <v>1720</v>
@@ -43026,8 +43176,8 @@
       <c r="A933" s="7" t="s">
         <v>1853</v>
       </c>
-      <c r="B933" s="38" t="s">
-        <v>1762</v>
+      <c r="B933" s="7" t="s">
+        <v>2360</v>
       </c>
       <c r="C933" s="12" t="s">
         <v>1720</v>
@@ -43062,8 +43212,8 @@
       <c r="A934" s="7" t="s">
         <v>1531</v>
       </c>
-      <c r="B934" s="38" t="s">
-        <v>1762</v>
+      <c r="B934" s="7" t="s">
+        <v>2361</v>
       </c>
       <c r="C934" s="12" t="s">
         <v>1720</v>
@@ -43098,8 +43248,8 @@
       <c r="A935" s="7" t="s">
         <v>1854</v>
       </c>
-      <c r="B935" s="38" t="s">
-        <v>1762</v>
+      <c r="B935" s="7" t="s">
+        <v>2363</v>
       </c>
       <c r="C935" s="12" t="s">
         <v>1720</v>
@@ -43134,8 +43284,8 @@
       <c r="A936" s="7" t="s">
         <v>1855</v>
       </c>
-      <c r="B936" s="38" t="s">
-        <v>1762</v>
+      <c r="B936" s="7" t="s">
+        <v>2364</v>
       </c>
       <c r="C936" s="12" t="s">
         <v>1720</v>
@@ -43170,8 +43320,8 @@
       <c r="A937" s="7" t="s">
         <v>1532</v>
       </c>
-      <c r="B937" s="38" t="s">
-        <v>1762</v>
+      <c r="B937" s="7" t="s">
+        <v>2365</v>
       </c>
       <c r="C937" s="12" t="s">
         <v>1720</v>
@@ -52811,7 +52961,7 @@
         <v>391</v>
       </c>
       <c r="I1195" s="19" t="str">
-        <f t="shared" ref="I1195:I1204" si="121">H1195&amp;"_"&amp;TRIM(A1195)</f>
+        <f t="shared" ref="I1195:I1210" si="121">H1195&amp;"_"&amp;TRIM(A1195)</f>
         <v>fish_n_ac_Cott</v>
       </c>
       <c r="J1195" s="7">
@@ -53108,11 +53258,11 @@
         <v>fish_x_Obs_CatoRhin</v>
       </c>
       <c r="J1202" s="7">
-        <f t="shared" ref="J1202:J1204" si="125">COUNTIF($I$6:$I$1194,I1202)</f>
+        <f t="shared" ref="J1202:J1207" si="125">COUNTIF($I$6:$I$1194,I1202)</f>
         <v>0</v>
       </c>
       <c r="K1202" s="1" t="str">
-        <f t="shared" ref="K1202:K1204" si="126">"unclassified_"&amp;H1202</f>
+        <f t="shared" ref="K1202:K1207" si="126">"unclassified_"&amp;H1202</f>
         <v>unclassified_fish</v>
       </c>
       <c r="L1202" s="1" t="s">
@@ -53205,11 +53355,221 @@
         <v>2133</v>
       </c>
     </row>
-    <row r="2025" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2025" s="52"/>
+    <row r="1205" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1205" s="7" t="s">
+        <v>2353</v>
+      </c>
+      <c r="B1205" s="7" t="s">
+        <v>2356</v>
+      </c>
+      <c r="C1205" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="D1205" s="12"/>
+      <c r="E1205" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1205" s="12"/>
+      <c r="G1205" s="8" t="s">
+        <v>2329</v>
+      </c>
+      <c r="H1205" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="I1205" s="19" t="str">
+        <f t="shared" si="121"/>
+        <v>bugs_pt_NonIns_BCG_att456t</v>
+      </c>
+      <c r="J1205" s="7">
+        <f t="shared" si="125"/>
+        <v>0</v>
+      </c>
+      <c r="K1205" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_bugs</v>
+      </c>
+      <c r="L1205" s="1" t="s">
+        <v>2355</v>
+      </c>
+      <c r="M1205" s="7"/>
+      <c r="N1205" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1206" s="7" t="s">
+        <v>2354</v>
+      </c>
+      <c r="B1206" s="7" t="s">
+        <v>2359</v>
+      </c>
+      <c r="C1206" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1206" s="12"/>
+      <c r="E1206" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1206" s="12"/>
+      <c r="G1206" s="8" t="s">
+        <v>2329</v>
+      </c>
+      <c r="H1206" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="I1206" s="19" t="str">
+        <f t="shared" si="121"/>
+        <v>bugs_pi_dom01_BCG_att456</v>
+      </c>
+      <c r="J1206" s="7">
+        <f t="shared" si="125"/>
+        <v>0</v>
+      </c>
+      <c r="K1206" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_bugs</v>
+      </c>
+      <c r="L1206" s="1" t="s">
+        <v>2355</v>
+      </c>
+      <c r="M1206" s="7"/>
+      <c r="N1206" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1207" s="7" t="s">
+        <v>2357</v>
+      </c>
+      <c r="B1207" s="7" t="s">
+        <v>2358</v>
+      </c>
+      <c r="C1207" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1207" s="12"/>
+      <c r="E1207" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1207" s="12"/>
+      <c r="G1207" s="8" t="s">
+        <v>2329</v>
+      </c>
+      <c r="H1207" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="I1207" s="19" t="str">
+        <f t="shared" si="121"/>
+        <v>bugs_pi_dom01_BCG_att456t</v>
+      </c>
+      <c r="J1207" s="7">
+        <f t="shared" si="125"/>
+        <v>0</v>
+      </c>
+      <c r="K1207" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_bugs</v>
+      </c>
+      <c r="L1207" s="1" t="s">
+        <v>2355</v>
+      </c>
+      <c r="M1207" s="7"/>
+      <c r="N1207" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1208" s="7" t="s">
+        <v>2367</v>
+      </c>
+      <c r="B1208" s="7" t="s">
+        <v>2370</v>
+      </c>
+      <c r="C1208" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="D1208" s="12"/>
+      <c r="E1208" s="12"/>
+      <c r="F1208" s="12"/>
+      <c r="G1208" s="8"/>
+      <c r="H1208" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="I1208" s="19" t="str">
+        <f t="shared" si="121"/>
+        <v>bugs_nt_ffg2_deepdep</v>
+      </c>
+      <c r="J1208" s="7"/>
+      <c r="K1208" s="1"/>
+      <c r="L1208" s="1"/>
+      <c r="M1208" s="7"/>
+      <c r="N1208" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1209" s="7" t="s">
+        <v>2368</v>
+      </c>
+      <c r="B1209" s="7" t="s">
+        <v>2371</v>
+      </c>
+      <c r="C1209" s="12" t="s">
+        <v>229</v>
+      </c>
+      <c r="D1209" s="12"/>
+      <c r="E1209" s="12"/>
+      <c r="F1209" s="12"/>
+      <c r="G1209" s="8"/>
+      <c r="H1209" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="I1209" s="19" t="str">
+        <f t="shared" si="121"/>
+        <v>bugs_pi_ffg2_deepdep</v>
+      </c>
+      <c r="J1209" s="7"/>
+      <c r="K1209" s="1"/>
+      <c r="L1209" s="1"/>
+      <c r="M1209" s="7"/>
+      <c r="N1209" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1210" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="B1210" s="7" t="s">
+        <v>2369</v>
+      </c>
+      <c r="C1210" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="D1210" s="12"/>
+      <c r="E1210" s="12"/>
+      <c r="F1210" s="12"/>
+      <c r="G1210" s="8"/>
+      <c r="H1210" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="I1210" s="19" t="str">
+        <f t="shared" si="121"/>
+        <v>bugs_ni_m2</v>
+      </c>
+      <c r="J1210" s="7"/>
+      <c r="K1210" s="1"/>
+      <c r="L1210" s="1"/>
+      <c r="M1210" s="7"/>
+      <c r="N1210" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2023" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2023" s="52"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:N1204" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A5:N1207" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1004:A1011">
     <sortCondition ref="A1004:A1011"/>
   </sortState>

--- a/inst/extdata/MetricNames.xlsx
+++ b/inst/extdata/MetricNames.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erik.Leppo\Documents\GitHub\BioMonTools\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A8B33B6-7B01-433D-AAC8-67480E162A4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2790DAB-E96B-4D76-8299-104CE43BBC50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="MetricMetadata" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">MetricMetadata!$A$5:$N$1207</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">MetricMetadata!$A$5:$N$1213</definedName>
     <definedName name="FileName" localSheetId="0">NOTES!$B$8</definedName>
     <definedName name="FileName">#REF!</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">MetricMetadata!$A:$A,MetricMetadata!$5:$5</definedName>
@@ -225,7 +225,31 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1210" authorId="1" shapeId="0" xr:uid="{905B8F54-2067-4968-9CE3-86EB0853D83A}">
+    <comment ref="B1211" authorId="1" shapeId="0" xr:uid="{EE6C7705-7E87-436A-AE80-A5FABC228A99}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Leppo, Erik:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Whole sample density</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1211" authorId="1" shapeId="0" xr:uid="{905B8F54-2067-4968-9CE3-86EB0853D83A}">
       <text>
         <r>
           <rPr>
@@ -249,12 +273,36 @@
         </r>
       </text>
     </comment>
+    <comment ref="B1212" authorId="1" shapeId="0" xr:uid="{C301695B-A8C0-41F3-B34F-89A2B62122FA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Leppo, Erik:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+For when density is reported per taxon</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8057" uniqueCount="2372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8082" uniqueCount="2382">
   <si>
     <t>nt_total</t>
   </si>
@@ -7370,13 +7418,43 @@
   </si>
   <si>
     <t>percent of individuals - ffg2 - deep deposit feeders</t>
+  </si>
+  <si>
+    <t>sum_density_m2</t>
+  </si>
+  <si>
+    <t>sum of density per square meter</t>
+  </si>
+  <si>
+    <t>Chesapeake Bay</t>
+  </si>
+  <si>
+    <t>n_ac_wmf</t>
+  </si>
+  <si>
+    <t>number of age class for Mountain Whitefish (PROSOPIUM WILLIAMSONI)</t>
+  </si>
+  <si>
+    <t>Add more metrics for Boise</t>
+  </si>
+  <si>
+    <t>density_m2</t>
+  </si>
+  <si>
+    <t>samp_area_m2</t>
+  </si>
+  <si>
+    <t>nt_NonIns_BCG_att456t</t>
+  </si>
+  <si>
+    <t>number of taxa - non-Insecta, BCG attributes 4, 5, or 6t</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7524,6 +7602,19 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="12">
@@ -8145,7 +8236,7 @@
   <sheetPr>
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:N113"/>
+  <dimension ref="A1:N114"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -8191,7 +8282,7 @@
       </c>
       <c r="J6" s="42">
         <f>COUNTA(MetricMetadata!$H$6:$H$2023)</f>
-        <v>1205</v>
+        <v>1208</v>
       </c>
       <c r="M6" t="s">
         <v>2012</v>
@@ -8213,7 +8304,7 @@
       </c>
       <c r="H7">
         <f>COUNTIF(MetricMetadata!$H$6:$H$2023,G7)</f>
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="M7" t="s">
         <v>2014</v>
@@ -8235,7 +8326,7 @@
       </c>
       <c r="H8">
         <f>COUNTIF(MetricMetadata!$H$6:$H$2023,G8)</f>
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M8" t="s">
         <v>2016</v>
@@ -8325,7 +8416,7 @@
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="H14" s="41">
         <f>SUM(H7:H11)</f>
-        <v>1205</v>
+        <v>1208</v>
       </c>
       <c r="I14" t="s">
         <v>1998</v>
@@ -9098,6 +9189,11 @@
       </c>
       <c r="B113" t="s">
         <v>2366</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B114" t="s">
+        <v>2377</v>
       </c>
     </row>
   </sheetData>
@@ -9200,7 +9296,7 @@
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <f>SUBTOTAL(3,A6:A2107)</f>
-        <v>1205</v>
+        <v>1208</v>
       </c>
       <c r="B3" s="4">
         <f>COUNTIF($B$6:$B$1001,B2)</f>
@@ -52961,7 +53057,7 @@
         <v>391</v>
       </c>
       <c r="I1195" s="19" t="str">
-        <f t="shared" ref="I1195:I1210" si="121">H1195&amp;"_"&amp;TRIM(A1195)</f>
+        <f t="shared" ref="I1195:I1211" si="121">H1195&amp;"_"&amp;TRIM(A1195)</f>
         <v>fish_n_ac_Cott</v>
       </c>
       <c r="J1195" s="7">
@@ -53258,11 +53354,11 @@
         <v>fish_x_Obs_CatoRhin</v>
       </c>
       <c r="J1202" s="7">
-        <f t="shared" ref="J1202:J1207" si="125">COUNTIF($I$6:$I$1194,I1202)</f>
+        <f t="shared" ref="J1202:J1208" si="125">COUNTIF($I$6:$I$1194,I1202)</f>
         <v>0</v>
       </c>
       <c r="K1202" s="1" t="str">
-        <f t="shared" ref="K1202:K1207" si="126">"unclassified_"&amp;H1202</f>
+        <f t="shared" ref="K1202:K1213" si="126">"unclassified_"&amp;H1202</f>
         <v>unclassified_fish</v>
       </c>
       <c r="L1202" s="1" t="s">
@@ -53357,10 +53453,10 @@
     </row>
     <row r="1205" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1205" s="7" t="s">
-        <v>2353</v>
+        <v>2380</v>
       </c>
       <c r="B1205" s="7" t="s">
-        <v>2356</v>
+        <v>2381</v>
       </c>
       <c r="C1205" s="12" t="s">
         <v>193</v>
@@ -53377,15 +53473,15 @@
         <v>652</v>
       </c>
       <c r="I1205" s="19" t="str">
-        <f t="shared" si="121"/>
-        <v>bugs_pt_NonIns_BCG_att456t</v>
+        <f t="shared" ref="I1205" si="127">H1205&amp;"_"&amp;TRIM(A1205)</f>
+        <v>bugs_nt_NonIns_BCG_att456t</v>
       </c>
       <c r="J1205" s="7">
-        <f t="shared" si="125"/>
+        <f t="shared" ref="J1205" si="128">COUNTIF($I$6:$I$1194,I1205)</f>
         <v>0</v>
       </c>
       <c r="K1205" s="1" t="str">
-        <f t="shared" si="126"/>
+        <f t="shared" ref="K1205" si="129">"unclassified_"&amp;H1205</f>
         <v>unclassified_bugs</v>
       </c>
       <c r="L1205" s="1" t="s">
@@ -53398,13 +53494,13 @@
     </row>
     <row r="1206" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1206" s="7" t="s">
-        <v>2354</v>
+        <v>2353</v>
       </c>
       <c r="B1206" s="7" t="s">
-        <v>2359</v>
+        <v>2356</v>
       </c>
       <c r="C1206" s="12" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="D1206" s="12"/>
       <c r="E1206" s="12" t="s">
@@ -53419,7 +53515,7 @@
       </c>
       <c r="I1206" s="19" t="str">
         <f t="shared" si="121"/>
-        <v>bugs_pi_dom01_BCG_att456</v>
+        <v>bugs_pt_NonIns_BCG_att456t</v>
       </c>
       <c r="J1206" s="7">
         <f t="shared" si="125"/>
@@ -53439,10 +53535,10 @@
     </row>
     <row r="1207" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1207" s="7" t="s">
-        <v>2357</v>
+        <v>2354</v>
       </c>
       <c r="B1207" s="7" t="s">
-        <v>2358</v>
+        <v>2359</v>
       </c>
       <c r="C1207" s="12" t="s">
         <v>180</v>
@@ -53460,7 +53556,7 @@
       </c>
       <c r="I1207" s="19" t="str">
         <f t="shared" si="121"/>
-        <v>bugs_pi_dom01_BCG_att456t</v>
+        <v>bugs_pi_dom01_BCG_att456</v>
       </c>
       <c r="J1207" s="7">
         <f t="shared" si="125"/>
@@ -53480,28 +53576,40 @@
     </row>
     <row r="1208" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1208" s="7" t="s">
-        <v>2367</v>
+        <v>2357</v>
       </c>
       <c r="B1208" s="7" t="s">
-        <v>2370</v>
+        <v>2358</v>
       </c>
       <c r="C1208" s="12" t="s">
-        <v>229</v>
+        <v>180</v>
       </c>
       <c r="D1208" s="12"/>
-      <c r="E1208" s="12"/>
+      <c r="E1208" s="12" t="s">
+        <v>1960</v>
+      </c>
       <c r="F1208" s="12"/>
-      <c r="G1208" s="8"/>
+      <c r="G1208" s="8" t="s">
+        <v>2329</v>
+      </c>
       <c r="H1208" s="7" t="s">
         <v>652</v>
       </c>
       <c r="I1208" s="19" t="str">
         <f t="shared" si="121"/>
-        <v>bugs_nt_ffg2_deepdep</v>
-      </c>
-      <c r="J1208" s="7"/>
-      <c r="K1208" s="1"/>
-      <c r="L1208" s="1"/>
+        <v>bugs_pi_dom01_BCG_att456t</v>
+      </c>
+      <c r="J1208" s="7">
+        <f t="shared" si="125"/>
+        <v>0</v>
+      </c>
+      <c r="K1208" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_bugs</v>
+      </c>
+      <c r="L1208" s="1" t="s">
+        <v>2355</v>
+      </c>
       <c r="M1208" s="7"/>
       <c r="N1208" s="1" t="b">
         <v>0</v>
@@ -53509,10 +53617,10 @@
     </row>
     <row r="1209" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1209" s="7" t="s">
-        <v>2368</v>
+        <v>2367</v>
       </c>
       <c r="B1209" s="7" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
       <c r="C1209" s="12" t="s">
         <v>229</v>
@@ -53526,11 +53634,16 @@
       </c>
       <c r="I1209" s="19" t="str">
         <f t="shared" si="121"/>
-        <v>bugs_pi_ffg2_deepdep</v>
+        <v>bugs_nt_ffg2_deepdep</v>
       </c>
       <c r="J1209" s="7"/>
-      <c r="K1209" s="1"/>
-      <c r="L1209" s="1"/>
+      <c r="K1209" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_bugs</v>
+      </c>
+      <c r="L1209" s="1" t="s">
+        <v>2374</v>
+      </c>
       <c r="M1209" s="7"/>
       <c r="N1209" s="1" t="b">
         <v>0</v>
@@ -53538,13 +53651,13 @@
     </row>
     <row r="1210" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1210" s="7" t="s">
-        <v>403</v>
+        <v>2368</v>
       </c>
       <c r="B1210" s="7" t="s">
-        <v>2369</v>
+        <v>2371</v>
       </c>
       <c r="C1210" s="12" t="s">
-        <v>390</v>
+        <v>229</v>
       </c>
       <c r="D1210" s="12"/>
       <c r="E1210" s="12"/>
@@ -53555,21 +53668,137 @@
       </c>
       <c r="I1210" s="19" t="str">
         <f t="shared" si="121"/>
-        <v>bugs_ni_m2</v>
+        <v>bugs_pi_ffg2_deepdep</v>
       </c>
       <c r="J1210" s="7"/>
-      <c r="K1210" s="1"/>
-      <c r="L1210" s="1"/>
+      <c r="K1210" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_bugs</v>
+      </c>
+      <c r="L1210" s="1" t="s">
+        <v>2374</v>
+      </c>
       <c r="M1210" s="7"/>
       <c r="N1210" s="1" t="b">
         <v>0</v>
       </c>
     </row>
+    <row r="1211" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1211" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="B1211" s="7" t="s">
+        <v>2369</v>
+      </c>
+      <c r="C1211" s="12" t="s">
+        <v>2379</v>
+      </c>
+      <c r="D1211" s="12"/>
+      <c r="E1211" s="12"/>
+      <c r="F1211" s="12"/>
+      <c r="G1211" s="8"/>
+      <c r="H1211" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="I1211" s="19" t="str">
+        <f t="shared" si="121"/>
+        <v>bugs_ni_m2</v>
+      </c>
+      <c r="J1211" s="7"/>
+      <c r="K1211" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_bugs</v>
+      </c>
+      <c r="L1211" s="1" t="s">
+        <v>2374</v>
+      </c>
+      <c r="M1211" s="7"/>
+      <c r="N1211" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1212" s="7" t="s">
+        <v>2372</v>
+      </c>
+      <c r="B1212" s="7" t="s">
+        <v>2373</v>
+      </c>
+      <c r="C1212" s="12" t="s">
+        <v>2378</v>
+      </c>
+      <c r="D1212" s="12"/>
+      <c r="E1212" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1212" s="12"/>
+      <c r="G1212" s="8"/>
+      <c r="H1212" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="I1212" s="19" t="str">
+        <f t="shared" ref="I1212:I1213" si="130">H1212&amp;"_"&amp;TRIM(A1212)</f>
+        <v>bugs_sum_density_m2</v>
+      </c>
+      <c r="J1212" s="7"/>
+      <c r="K1212" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_bugs</v>
+      </c>
+      <c r="L1212" s="1" t="s">
+        <v>2355</v>
+      </c>
+      <c r="M1212" s="7"/>
+      <c r="N1212" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1213" s="7" t="s">
+        <v>2375</v>
+      </c>
+      <c r="B1213" s="7" t="s">
+        <v>2376</v>
+      </c>
+      <c r="C1213" s="16" t="s">
+        <v>2322</v>
+      </c>
+      <c r="D1213" s="55"/>
+      <c r="E1213" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1213" s="12"/>
+      <c r="G1213" s="8" t="s">
+        <v>2329</v>
+      </c>
+      <c r="H1213" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="I1213" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>fish_n_ac_wmf</v>
+      </c>
+      <c r="J1213" s="7">
+        <f t="shared" ref="J1213" si="131">COUNTIF($I$6:$I$1123,I1213)</f>
+        <v>0</v>
+      </c>
+      <c r="K1213" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_fish</v>
+      </c>
+      <c r="L1213" s="1" t="s">
+        <v>1577</v>
+      </c>
+      <c r="M1213" s="1"/>
+      <c r="N1213" s="1" t="s">
+        <v>2133</v>
+      </c>
+    </row>
     <row r="2023" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2023" s="52"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:N1207" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A5:N1213" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1004:A1011">
     <sortCondition ref="A1004:A1011"/>
   </sortState>

--- a/inst/extdata/MetricNames.xlsx
+++ b/inst/extdata/MetricNames.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erik.Leppo\Documents\GitHub\BioMonTools\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2790DAB-E96B-4D76-8299-104CE43BBC50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE77DA2-1221-4259-8C25-0FA028BE6EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NOTES" sheetId="4" r:id="rId1"/>
@@ -233,7 +233,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Leppo, Erik:</t>
         </r>
@@ -242,7 +242,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Whole sample density</t>
@@ -281,7 +281,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Leppo, Erik:</t>
         </r>
@@ -290,7 +290,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 For when density is reported per taxon</t>
@@ -302,7 +302,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8082" uniqueCount="2382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8083" uniqueCount="2383">
   <si>
     <t>nt_total</t>
   </si>
@@ -7429,9 +7429,6 @@
     <t>Chesapeake Bay</t>
   </si>
   <si>
-    <t>n_ac_wmf</t>
-  </si>
-  <si>
     <t>number of age class for Mountain Whitefish (PROSOPIUM WILLIAMSONI)</t>
   </si>
   <si>
@@ -7448,13 +7445,19 @@
   </si>
   <si>
     <t>number of taxa - non-Insecta, BCG attributes 4, 5, or 6t</t>
+  </si>
+  <si>
+    <t>n_ac_mwf</t>
+  </si>
+  <si>
+    <t>Correct name of metric "n_ac_wmf" to "n_ac_mwf"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7602,19 +7605,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="12">
@@ -8236,7 +8226,7 @@
   <sheetPr>
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:N114"/>
+  <dimension ref="A1:N115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -9193,7 +9183,15 @@
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
-        <v>2377</v>
+        <v>2376</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" s="24">
+        <v>46161</v>
+      </c>
+      <c r="B115" t="s">
+        <v>2382</v>
       </c>
     </row>
   </sheetData>
@@ -53453,10 +53451,10 @@
     </row>
     <row r="1205" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1205" s="7" t="s">
+        <v>2379</v>
+      </c>
+      <c r="B1205" s="7" t="s">
         <v>2380</v>
-      </c>
-      <c r="B1205" s="7" t="s">
-        <v>2381</v>
       </c>
       <c r="C1205" s="12" t="s">
         <v>193</v>
@@ -53691,7 +53689,7 @@
         <v>2369</v>
       </c>
       <c r="C1211" s="12" t="s">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="D1211" s="12"/>
       <c r="E1211" s="12"/>
@@ -53725,7 +53723,7 @@
         <v>2373</v>
       </c>
       <c r="C1212" s="12" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
       <c r="D1212" s="12"/>
       <c r="E1212" s="12" t="s">
@@ -53755,10 +53753,10 @@
     </row>
     <row r="1213" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1213" s="7" t="s">
+        <v>2381</v>
+      </c>
+      <c r="B1213" s="7" t="s">
         <v>2375</v>
-      </c>
-      <c r="B1213" s="7" t="s">
-        <v>2376</v>
       </c>
       <c r="C1213" s="16" t="s">
         <v>2322</v>
@@ -53776,7 +53774,7 @@
       </c>
       <c r="I1213" s="19" t="str">
         <f t="shared" si="130"/>
-        <v>fish_n_ac_wmf</v>
+        <v>fish_n_ac_mwf</v>
       </c>
       <c r="J1213" s="7">
         <f t="shared" ref="J1213" si="131">COUNTIF($I$6:$I$1123,I1213)</f>

--- a/inst/extdata/MetricNames.xlsx
+++ b/inst/extdata/MetricNames.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erik.Leppo\Documents\GitHub\BioMonTools\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE77DA2-1221-4259-8C25-0FA028BE6EA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F906935-EDA5-49D6-9551-2832A171A26D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NOTES" sheetId="4" r:id="rId1"/>
     <sheet name="MetricMetadata" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">MetricMetadata!$A$5:$N$1213</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">MetricMetadata!$A$5:$N$1220</definedName>
     <definedName name="FileName" localSheetId="0">NOTES!$B$8</definedName>
     <definedName name="FileName">#REF!</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">MetricMetadata!$A:$A,MetricMetadata!$5:$5</definedName>
@@ -302,7 +302,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8083" uniqueCount="2383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8127" uniqueCount="2400">
   <si>
     <t>nt_total</t>
   </si>
@@ -7451,6 +7451,57 @@
   </si>
   <si>
     <t>Correct name of metric "n_ac_wmf" to "n_ac_mwf"</t>
+  </si>
+  <si>
+    <t>Additional bug metricss, Issue #142</t>
+  </si>
+  <si>
+    <t>https://github.com/leppott/BioMonTools/issues/142</t>
+  </si>
+  <si>
+    <t>nt_EPT_BCG_att1i2</t>
+  </si>
+  <si>
+    <t>number taxa - EPT BCG Attribute Ii + II</t>
+  </si>
+  <si>
+    <t>pt_EPT_BCG_att1i2</t>
+  </si>
+  <si>
+    <t>percent (0-100) taxa - EPT BCG Attribute Ii + II</t>
+  </si>
+  <si>
+    <t>pi_EPT_BCG_att1i2</t>
+  </si>
+  <si>
+    <t>percent (0-100) individuals - EPT BCG Attribute Ii + II</t>
+  </si>
+  <si>
+    <t>nord_COEPT</t>
+  </si>
+  <si>
+    <t>number of unique - orders - Order Coleoptera, Odonata, Ephemeroptera, Plecoptera or Trichoptera</t>
+  </si>
+  <si>
+    <t>nt_COEPT</t>
+  </si>
+  <si>
+    <t>number taxa - Orders Coleoptera, Odonata, Ephemertopera, Plecoptera and Trichoptera (COEPT)</t>
+  </si>
+  <si>
+    <t>pi_COEPT_BCG_att1i234b4m</t>
+  </si>
+  <si>
+    <t>percent (0-100) individuals - Orders Coleoptera, Odonata, Ephemertopera, Plecoptera and Trichoptera (COEPT) sensitive and intermediate tolerant (Attribute Ii + II + III + IV_better + IV_middle)</t>
+  </si>
+  <si>
+    <t>nt_EPT_volt_semi</t>
+  </si>
+  <si>
+    <t>number taxa - EPT semivoltine (SEMI)</t>
+  </si>
+  <si>
+    <t>Life_Cycle, Order</t>
   </si>
 </sst>
 </file>
@@ -8226,7 +8277,7 @@
   <sheetPr>
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:N115"/>
+  <dimension ref="A1:N116"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -8254,7 +8305,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="24">
-        <v>46119</v>
+        <v>46164</v>
       </c>
       <c r="J5" s="43" t="s">
         <v>1999</v>
@@ -8272,7 +8323,7 @@
       </c>
       <c r="J6" s="42">
         <f>COUNTA(MetricMetadata!$H$6:$H$2023)</f>
-        <v>1208</v>
+        <v>1215</v>
       </c>
       <c r="M6" t="s">
         <v>2012</v>
@@ -8294,7 +8345,7 @@
       </c>
       <c r="H7">
         <f>COUNTIF(MetricMetadata!$H$6:$H$2023,G7)</f>
-        <v>556</v>
+        <v>563</v>
       </c>
       <c r="M7" t="s">
         <v>2014</v>
@@ -8406,7 +8457,7 @@
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="H14" s="41">
         <f>SUM(H7:H11)</f>
-        <v>1208</v>
+        <v>1215</v>
       </c>
       <c r="I14" t="s">
         <v>1998</v>
@@ -9173,7 +9224,7 @@
         <v>2345</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="24">
         <v>46160</v>
       </c>
@@ -9181,17 +9232,28 @@
         <v>2366</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
         <v>2376</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="24">
         <v>46161</v>
       </c>
       <c r="B115" t="s">
         <v>2382</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="24">
+        <v>46164</v>
+      </c>
+      <c r="B116" t="s">
+        <v>2383</v>
+      </c>
+      <c r="C116" s="59" t="s">
+        <v>2384</v>
       </c>
     </row>
   </sheetData>
@@ -9214,16 +9276,17 @@
     <hyperlink ref="C107" r:id="rId6" xr:uid="{9D23F2DB-3FE6-4075-8E01-AA0D79A7BA2D}"/>
     <hyperlink ref="C62" r:id="rId7" xr:uid="{1F677AEA-DA00-4CC3-A569-4944779084C6}"/>
     <hyperlink ref="C59" r:id="rId8" xr:uid="{E61D1D46-D820-43C4-83A4-C18E3A3A4142}"/>
+    <hyperlink ref="C116" r:id="rId9" xr:uid="{B76FCC48-EF00-4AC2-A950-BB3A204B48D4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="91" orientation="portrait" r:id="rId9"/>
+  <pageSetup scale="91" orientation="portrait" r:id="rId10"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;A</oddHeader>
     <oddFooter>&amp;L&amp;D&amp;CPage &amp;P of &amp;N&amp;R&amp;F</oddFooter>
   </headerFooter>
-  <legacyDrawing r:id="rId10"/>
+  <legacyDrawing r:id="rId11"/>
   <tableParts count="1">
-    <tablePart r:id="rId11"/>
+    <tablePart r:id="rId12"/>
   </tableParts>
 </worksheet>
 </file>
@@ -9243,9 +9306,10 @@
     <col min="5" max="5" width="15.7109375" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.42578125" style="11" customWidth="1"/>
     <col min="7" max="7" width="32" style="4" customWidth="1"/>
-    <col min="8" max="9" width="18" style="4" customWidth="1"/>
+    <col min="8" max="8" width="18" style="4" customWidth="1"/>
+    <col min="9" max="9" width="25" style="4" customWidth="1"/>
     <col min="10" max="10" width="9.140625" style="4"/>
-    <col min="11" max="11" width="16" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.140625" style="4" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11" style="4" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="17.42578125" style="4" bestFit="1" customWidth="1"/>
@@ -9274,7 +9338,7 @@
     </row>
     <row r="2" spans="1:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>46160</v>
+        <v>46164</v>
       </c>
       <c r="B2" s="38" t="s">
         <v>1762</v>
@@ -9294,7 +9358,7 @@
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <f>SUBTOTAL(3,A6:A2107)</f>
-        <v>1208</v>
+        <v>1215</v>
       </c>
       <c r="B3" s="4">
         <f>COUNTIF($B$6:$B$1001,B2)</f>
@@ -53356,7 +53420,7 @@
         <v>0</v>
       </c>
       <c r="K1202" s="1" t="str">
-        <f t="shared" ref="K1202:K1213" si="126">"unclassified_"&amp;H1202</f>
+        <f t="shared" ref="K1202:K1220" si="126">"unclassified_"&amp;H1202</f>
         <v>unclassified_fish</v>
       </c>
       <c r="L1202" s="1" t="s">
@@ -53735,7 +53799,7 @@
         <v>652</v>
       </c>
       <c r="I1212" s="19" t="str">
-        <f t="shared" ref="I1212:I1213" si="130">H1212&amp;"_"&amp;TRIM(A1212)</f>
+        <f t="shared" ref="I1212:I1220" si="130">H1212&amp;"_"&amp;TRIM(A1212)</f>
         <v>bugs_sum_density_m2</v>
       </c>
       <c r="J1212" s="7"/>
@@ -53792,11 +53856,263 @@
         <v>2133</v>
       </c>
     </row>
+    <row r="1214" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1214" s="7" t="s">
+        <v>2385</v>
+      </c>
+      <c r="B1214" s="7" t="s">
+        <v>2386</v>
+      </c>
+      <c r="C1214" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="D1214" s="12"/>
+      <c r="E1214" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1214" s="12"/>
+      <c r="G1214" s="8"/>
+      <c r="H1214" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="I1214" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>bugs_nt_EPT_BCG_att1i2</v>
+      </c>
+      <c r="J1214" s="7"/>
+      <c r="K1214" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_bugs</v>
+      </c>
+      <c r="L1214" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1214" s="7"/>
+      <c r="N1214" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1215" s="7" t="s">
+        <v>2387</v>
+      </c>
+      <c r="B1215" s="7" t="s">
+        <v>2388</v>
+      </c>
+      <c r="C1215" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="D1215" s="12"/>
+      <c r="E1215" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1215" s="12"/>
+      <c r="G1215" s="8"/>
+      <c r="H1215" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="I1215" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>bugs_pt_EPT_BCG_att1i2</v>
+      </c>
+      <c r="J1215" s="7"/>
+      <c r="K1215" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_bugs</v>
+      </c>
+      <c r="L1215" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1215" s="7"/>
+      <c r="N1215" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1216" s="7" t="s">
+        <v>2389</v>
+      </c>
+      <c r="B1216" s="7" t="s">
+        <v>2390</v>
+      </c>
+      <c r="C1216" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="D1216" s="12"/>
+      <c r="E1216" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1216" s="12"/>
+      <c r="G1216" s="8"/>
+      <c r="H1216" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="I1216" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>bugs_pi_EPT_BCG_att1i2</v>
+      </c>
+      <c r="J1216" s="7"/>
+      <c r="K1216" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_bugs</v>
+      </c>
+      <c r="L1216" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1216" s="7"/>
+      <c r="N1216" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1217" s="7" t="s">
+        <v>2391</v>
+      </c>
+      <c r="B1217" s="7" t="s">
+        <v>2392</v>
+      </c>
+      <c r="C1217" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1217" s="12"/>
+      <c r="E1217" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1217" s="12"/>
+      <c r="G1217" s="8"/>
+      <c r="H1217" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="I1217" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>bugs_nord_COEPT</v>
+      </c>
+      <c r="J1217" s="7"/>
+      <c r="K1217" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_bugs</v>
+      </c>
+      <c r="L1217" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1217" s="7"/>
+      <c r="N1217" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1218" s="7" t="s">
+        <v>2393</v>
+      </c>
+      <c r="B1218" s="7" t="s">
+        <v>2394</v>
+      </c>
+      <c r="C1218" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1218" s="12"/>
+      <c r="E1218" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1218" s="12"/>
+      <c r="G1218" s="8"/>
+      <c r="H1218" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="I1218" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>bugs_nt_COEPT</v>
+      </c>
+      <c r="J1218" s="7"/>
+      <c r="K1218" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_bugs</v>
+      </c>
+      <c r="L1218" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1218" s="7"/>
+      <c r="N1218" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1219" s="7" t="s">
+        <v>2395</v>
+      </c>
+      <c r="B1219" s="7" t="s">
+        <v>2396</v>
+      </c>
+      <c r="C1219" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="D1219" s="12"/>
+      <c r="E1219" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1219" s="12"/>
+      <c r="G1219" s="8"/>
+      <c r="H1219" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="I1219" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>bugs_pi_COEPT_BCG_att1i234b4m</v>
+      </c>
+      <c r="J1219" s="7"/>
+      <c r="K1219" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_bugs</v>
+      </c>
+      <c r="L1219" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1219" s="7"/>
+      <c r="N1219" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1220" s="7" t="s">
+        <v>2397</v>
+      </c>
+      <c r="B1220" s="7" t="s">
+        <v>2398</v>
+      </c>
+      <c r="C1220" s="12" t="s">
+        <v>2399</v>
+      </c>
+      <c r="D1220" s="12"/>
+      <c r="E1220" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1220" s="12"/>
+      <c r="G1220" s="8"/>
+      <c r="H1220" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="I1220" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>bugs_nt_EPT_volt_semi</v>
+      </c>
+      <c r="J1220" s="7"/>
+      <c r="K1220" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_bugs</v>
+      </c>
+      <c r="L1220" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1220" s="7"/>
+      <c r="N1220" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
     <row r="2023" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2023" s="52"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:N1213" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A5:N1220" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1004:A1011">
     <sortCondition ref="A1004:A1011"/>
   </sortState>

--- a/inst/extdata/MetricNames.xlsx
+++ b/inst/extdata/MetricNames.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erik.Leppo\Documents\GitHub\BioMonTools\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F906935-EDA5-49D6-9551-2832A171A26D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CFED887-889F-4B50-BBC7-CB906B086A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NOTES" sheetId="4" r:id="rId1"/>
@@ -302,7 +302,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8127" uniqueCount="2400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8645" uniqueCount="2401">
   <si>
     <t>nt_total</t>
   </si>
@@ -7453,9 +7453,6 @@
     <t>Correct name of metric "n_ac_wmf" to "n_ac_mwf"</t>
   </si>
   <si>
-    <t>Additional bug metricss, Issue #142</t>
-  </si>
-  <si>
     <t>https://github.com/leppott/BioMonTools/issues/142</t>
   </si>
   <si>
@@ -7502,6 +7499,12 @@
   </si>
   <si>
     <t>Life_Cycle, Order</t>
+  </si>
+  <si>
+    <t>Additional algae metrics (BCG versions of bug metrics), Issue #142, n = 86</t>
+  </si>
+  <si>
+    <t>Additional bug metricss, Issue #142, n = 7</t>
   </si>
 </sst>
 </file>
@@ -8277,7 +8280,7 @@
   <sheetPr>
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:N116"/>
+  <dimension ref="A1:N117"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -8323,7 +8326,7 @@
       </c>
       <c r="J6" s="42">
         <f>COUNTA(MetricMetadata!$H$6:$H$2023)</f>
-        <v>1215</v>
+        <v>1301</v>
       </c>
       <c r="M6" t="s">
         <v>2012</v>
@@ -8389,7 +8392,7 @@
       </c>
       <c r="H9">
         <f>COUNTIF(MetricMetadata!$H$6:$H$2023,G9)</f>
-        <v>253</v>
+        <v>339</v>
       </c>
       <c r="M9" t="s">
         <v>2018</v>
@@ -8457,7 +8460,7 @@
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="H14" s="41">
         <f>SUM(H7:H11)</f>
-        <v>1215</v>
+        <v>1301</v>
       </c>
       <c r="I14" t="s">
         <v>1998</v>
@@ -9250,10 +9253,21 @@
         <v>46164</v>
       </c>
       <c r="B116" t="s">
+        <v>2400</v>
+      </c>
+      <c r="C116" s="59" t="s">
         <v>2383</v>
       </c>
-      <c r="C116" s="59" t="s">
-        <v>2384</v>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="24">
+        <v>46164</v>
+      </c>
+      <c r="B117" t="s">
+        <v>2399</v>
+      </c>
+      <c r="C117" s="59" t="s">
+        <v>2383</v>
       </c>
     </row>
   </sheetData>
@@ -9277,16 +9291,17 @@
     <hyperlink ref="C62" r:id="rId7" xr:uid="{1F677AEA-DA00-4CC3-A569-4944779084C6}"/>
     <hyperlink ref="C59" r:id="rId8" xr:uid="{E61D1D46-D820-43C4-83A4-C18E3A3A4142}"/>
     <hyperlink ref="C116" r:id="rId9" xr:uid="{B76FCC48-EF00-4AC2-A950-BB3A204B48D4}"/>
+    <hyperlink ref="C117" r:id="rId10" xr:uid="{5F0C2649-67F9-4C6F-AD76-EC9D37137902}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="91" orientation="portrait" r:id="rId10"/>
+  <pageSetup scale="91" orientation="portrait" r:id="rId11"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;A</oddHeader>
     <oddFooter>&amp;L&amp;D&amp;CPage &amp;P of &amp;N&amp;R&amp;F</oddFooter>
   </headerFooter>
-  <legacyDrawing r:id="rId11"/>
+  <legacyDrawing r:id="rId12"/>
   <tableParts count="1">
-    <tablePart r:id="rId12"/>
+    <tablePart r:id="rId13"/>
   </tableParts>
 </worksheet>
 </file>
@@ -9358,7 +9373,7 @@
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <f>SUBTOTAL(3,A6:A2107)</f>
-        <v>1215</v>
+        <v>1301</v>
       </c>
       <c r="B3" s="4">
         <f>COUNTIF($B$6:$B$1001,B2)</f>
@@ -53420,7 +53435,7 @@
         <v>0</v>
       </c>
       <c r="K1202" s="1" t="str">
-        <f t="shared" ref="K1202:K1220" si="126">"unclassified_"&amp;H1202</f>
+        <f t="shared" ref="K1202:K1265" si="126">"unclassified_"&amp;H1202</f>
         <v>unclassified_fish</v>
       </c>
       <c r="L1202" s="1" t="s">
@@ -53799,7 +53814,7 @@
         <v>652</v>
       </c>
       <c r="I1212" s="19" t="str">
-        <f t="shared" ref="I1212:I1220" si="130">H1212&amp;"_"&amp;TRIM(A1212)</f>
+        <f t="shared" ref="I1212:I1275" si="130">H1212&amp;"_"&amp;TRIM(A1212)</f>
         <v>bugs_sum_density_m2</v>
       </c>
       <c r="J1212" s="7"/>
@@ -53858,10 +53873,10 @@
     </row>
     <row r="1214" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1214" s="7" t="s">
+        <v>2384</v>
+      </c>
+      <c r="B1214" s="7" t="s">
         <v>2385</v>
-      </c>
-      <c r="B1214" s="7" t="s">
-        <v>2386</v>
       </c>
       <c r="C1214" s="12" t="s">
         <v>181</v>
@@ -53894,10 +53909,10 @@
     </row>
     <row r="1215" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1215" s="7" t="s">
+        <v>2386</v>
+      </c>
+      <c r="B1215" s="7" t="s">
         <v>2387</v>
-      </c>
-      <c r="B1215" s="7" t="s">
-        <v>2388</v>
       </c>
       <c r="C1215" s="12" t="s">
         <v>181</v>
@@ -53930,10 +53945,10 @@
     </row>
     <row r="1216" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1216" s="7" t="s">
+        <v>2388</v>
+      </c>
+      <c r="B1216" s="7" t="s">
         <v>2389</v>
-      </c>
-      <c r="B1216" s="7" t="s">
-        <v>2390</v>
       </c>
       <c r="C1216" s="12" t="s">
         <v>181</v>
@@ -53966,10 +53981,10 @@
     </row>
     <row r="1217" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1217" s="7" t="s">
+        <v>2390</v>
+      </c>
+      <c r="B1217" s="7" t="s">
         <v>2391</v>
-      </c>
-      <c r="B1217" s="7" t="s">
-        <v>2392</v>
       </c>
       <c r="C1217" s="12" t="s">
         <v>173</v>
@@ -54002,10 +54017,10 @@
     </row>
     <row r="1218" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1218" s="7" t="s">
+        <v>2392</v>
+      </c>
+      <c r="B1218" s="7" t="s">
         <v>2393</v>
-      </c>
-      <c r="B1218" s="7" t="s">
-        <v>2394</v>
       </c>
       <c r="C1218" s="12" t="s">
         <v>173</v>
@@ -54038,10 +54053,10 @@
     </row>
     <row r="1219" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1219" s="7" t="s">
+        <v>2394</v>
+      </c>
+      <c r="B1219" s="7" t="s">
         <v>2395</v>
-      </c>
-      <c r="B1219" s="7" t="s">
-        <v>2396</v>
       </c>
       <c r="C1219" s="12" t="s">
         <v>181</v>
@@ -54074,13 +54089,13 @@
     </row>
     <row r="1220" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1220" s="7" t="s">
+        <v>2396</v>
+      </c>
+      <c r="B1220" s="7" t="s">
         <v>2397</v>
       </c>
-      <c r="B1220" s="7" t="s">
+      <c r="C1220" s="12" t="s">
         <v>2398</v>
-      </c>
-      <c r="C1220" s="12" t="s">
-        <v>2399</v>
       </c>
       <c r="D1220" s="12"/>
       <c r="E1220" s="12" t="s">
@@ -54105,6 +54120,3102 @@
       </c>
       <c r="M1220" s="7"/>
       <c r="N1220" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1221" s="7" t="s">
+        <v>635</v>
+      </c>
+      <c r="B1221" s="7" t="s">
+        <v>636</v>
+      </c>
+      <c r="C1221" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1221" s="12"/>
+      <c r="E1221" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1221" s="12"/>
+      <c r="G1221" s="8"/>
+      <c r="H1221" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1221" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_nt_BCG_att1</v>
+      </c>
+      <c r="J1221" s="7"/>
+      <c r="K1221" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1221" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1221" s="7"/>
+      <c r="N1221" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1222" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="B1222" s="7" t="s">
+        <v>1690</v>
+      </c>
+      <c r="C1222" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1222" s="12"/>
+      <c r="E1222" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1222" s="12"/>
+      <c r="G1222" s="8"/>
+      <c r="H1222" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1222" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_nt_BCG_att1i</v>
+      </c>
+      <c r="J1222" s="7"/>
+      <c r="K1222" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1222" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1222" s="7"/>
+      <c r="N1222" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1223" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1223" s="7" t="s">
+        <v>1694</v>
+      </c>
+      <c r="C1223" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1223" s="12"/>
+      <c r="E1223" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1223" s="12"/>
+      <c r="G1223" s="8"/>
+      <c r="H1223" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1223" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_nt_BCG_att1m</v>
+      </c>
+      <c r="J1223" s="7"/>
+      <c r="K1223" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1223" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1223" s="7"/>
+      <c r="N1223" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1224" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1224" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="C1224" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1224" s="12"/>
+      <c r="E1224" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1224" s="12"/>
+      <c r="G1224" s="8"/>
+      <c r="H1224" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1224" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_nt_BCG_att12</v>
+      </c>
+      <c r="J1224" s="7"/>
+      <c r="K1224" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1224" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1224" s="7"/>
+      <c r="N1224" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1225" s="7" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B1225" s="7" t="s">
+        <v>1839</v>
+      </c>
+      <c r="C1225" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1225" s="12"/>
+      <c r="E1225" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1225" s="12"/>
+      <c r="G1225" s="8"/>
+      <c r="H1225" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1225" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_nt_BCG_att1234</v>
+      </c>
+      <c r="J1225" s="7"/>
+      <c r="K1225" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1225" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1225" s="7"/>
+      <c r="N1225" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1226" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1226" s="7" t="s">
+        <v>574</v>
+      </c>
+      <c r="C1226" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1226" s="12"/>
+      <c r="E1226" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1226" s="12"/>
+      <c r="G1226" s="8"/>
+      <c r="H1226" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1226" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_nt_BCG_att1i2</v>
+      </c>
+      <c r="J1226" s="7"/>
+      <c r="K1226" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1226" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1226" s="7"/>
+      <c r="N1226" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1227" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1227" s="7" t="s">
+        <v>575</v>
+      </c>
+      <c r="C1227" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1227" s="12"/>
+      <c r="E1227" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1227" s="12"/>
+      <c r="G1227" s="8"/>
+      <c r="H1227" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1227" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_nt_BCG_att123</v>
+      </c>
+      <c r="J1227" s="7"/>
+      <c r="K1227" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1227" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1227" s="7"/>
+      <c r="N1227" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1228" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1228" s="7" t="s">
+        <v>576</v>
+      </c>
+      <c r="C1228" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1228" s="12"/>
+      <c r="E1228" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1228" s="12"/>
+      <c r="G1228" s="8"/>
+      <c r="H1228" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1228" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_nt_BCG_att1i23</v>
+      </c>
+      <c r="J1228" s="7"/>
+      <c r="K1228" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1228" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1228" s="7"/>
+      <c r="N1228" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1229" s="7" t="s">
+        <v>1696</v>
+      </c>
+      <c r="B1229" s="7" t="s">
+        <v>1722</v>
+      </c>
+      <c r="C1229" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1229" s="12"/>
+      <c r="E1229" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1229" s="12"/>
+      <c r="G1229" s="8"/>
+      <c r="H1229" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1229" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_nt_BCG_att1i236i</v>
+      </c>
+      <c r="J1229" s="7"/>
+      <c r="K1229" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1229" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1229" s="7"/>
+      <c r="N1229" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1230" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1230" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="C1230" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1230" s="12"/>
+      <c r="E1230" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1230" s="12"/>
+      <c r="G1230" s="8"/>
+      <c r="H1230" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1230" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_nt_BCG_att2</v>
+      </c>
+      <c r="J1230" s="7"/>
+      <c r="K1230" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1230" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1230" s="7"/>
+      <c r="N1230" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1231" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1231" s="7" t="s">
+        <v>578</v>
+      </c>
+      <c r="C1231" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1231" s="12"/>
+      <c r="E1231" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1231" s="12"/>
+      <c r="G1231" s="8"/>
+      <c r="H1231" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1231" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_nt_BCG_att23</v>
+      </c>
+      <c r="J1231" s="7"/>
+      <c r="K1231" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1231" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1231" s="7"/>
+      <c r="N1231" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1232" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1232" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="C1232" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1232" s="12"/>
+      <c r="E1232" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1232" s="12"/>
+      <c r="G1232" s="8"/>
+      <c r="H1232" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1232" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_nt_BCG_att234</v>
+      </c>
+      <c r="J1232" s="7"/>
+      <c r="K1232" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1232" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1232" s="7"/>
+      <c r="N1232" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1233" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="B1233" s="7" t="s">
+        <v>580</v>
+      </c>
+      <c r="C1233" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1233" s="12"/>
+      <c r="E1233" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1233" s="12"/>
+      <c r="G1233" s="8"/>
+      <c r="H1233" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1233" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_nt_BCG_att3</v>
+      </c>
+      <c r="J1233" s="7"/>
+      <c r="K1233" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1233" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1233" s="7"/>
+      <c r="N1233" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1234" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1234" s="7" t="s">
+        <v>581</v>
+      </c>
+      <c r="C1234" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1234" s="12"/>
+      <c r="E1234" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1234" s="12"/>
+      <c r="G1234" s="8"/>
+      <c r="H1234" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1234" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_nt_BCG_att4</v>
+      </c>
+      <c r="J1234" s="7"/>
+      <c r="K1234" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1234" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1234" s="7"/>
+      <c r="N1234" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1235" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1235" s="7" t="s">
+        <v>582</v>
+      </c>
+      <c r="C1235" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1235" s="12"/>
+      <c r="E1235" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1235" s="12"/>
+      <c r="G1235" s="8"/>
+      <c r="H1235" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1235" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_nt_BCG_att45</v>
+      </c>
+      <c r="J1235" s="7"/>
+      <c r="K1235" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1235" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1235" s="7"/>
+      <c r="N1235" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1236" s="7" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B1236" s="7" t="s">
+        <v>1377</v>
+      </c>
+      <c r="C1236" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1236" s="12"/>
+      <c r="E1236" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1236" s="12"/>
+      <c r="G1236" s="8"/>
+      <c r="H1236" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1236" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_nt_BCG_att456</v>
+      </c>
+      <c r="J1236" s="7"/>
+      <c r="K1236" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1236" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1236" s="7"/>
+      <c r="N1236" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1237" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1237" s="7" t="s">
+        <v>583</v>
+      </c>
+      <c r="C1237" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1237" s="12"/>
+      <c r="E1237" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1237" s="12"/>
+      <c r="G1237" s="8"/>
+      <c r="H1237" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1237" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_nt_BCG_att5</v>
+      </c>
+      <c r="J1237" s="7"/>
+      <c r="K1237" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1237" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1237" s="7"/>
+      <c r="N1237" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1238" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1238" s="7" t="s">
+        <v>584</v>
+      </c>
+      <c r="C1238" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1238" s="12"/>
+      <c r="E1238" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1238" s="12"/>
+      <c r="G1238" s="8"/>
+      <c r="H1238" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1238" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_nt_BCG_att56</v>
+      </c>
+      <c r="J1238" s="7"/>
+      <c r="K1238" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1238" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1238" s="7"/>
+      <c r="N1238" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1239" s="7" t="s">
+        <v>1697</v>
+      </c>
+      <c r="B1239" s="7" t="s">
+        <v>1723</v>
+      </c>
+      <c r="C1239" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1239" s="12"/>
+      <c r="E1239" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1239" s="12"/>
+      <c r="G1239" s="8"/>
+      <c r="H1239" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1239" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_nt_BCG_att56t</v>
+      </c>
+      <c r="J1239" s="7"/>
+      <c r="K1239" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1239" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1239" s="7"/>
+      <c r="N1239" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1240" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B1240" s="7" t="s">
+        <v>585</v>
+      </c>
+      <c r="C1240" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1240" s="12"/>
+      <c r="E1240" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1240" s="12"/>
+      <c r="G1240" s="8"/>
+      <c r="H1240" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1240" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_nt_BCG_att6</v>
+      </c>
+      <c r="J1240" s="7"/>
+      <c r="K1240" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1240" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1240" s="7"/>
+      <c r="N1240" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1241" s="7" t="s">
+        <v>1698</v>
+      </c>
+      <c r="B1241" s="7" t="s">
+        <v>1724</v>
+      </c>
+      <c r="C1241" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1241" s="12"/>
+      <c r="E1241" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1241" s="12"/>
+      <c r="G1241" s="8"/>
+      <c r="H1241" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1241" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_nt_BCG_att6i</v>
+      </c>
+      <c r="J1241" s="7"/>
+      <c r="K1241" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1241" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1241" s="7"/>
+      <c r="N1241" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1242" s="7" t="s">
+        <v>1699</v>
+      </c>
+      <c r="B1242" s="7" t="s">
+        <v>1725</v>
+      </c>
+      <c r="C1242" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1242" s="12"/>
+      <c r="E1242" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1242" s="12"/>
+      <c r="G1242" s="8"/>
+      <c r="H1242" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1242" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_nt_BCG_att6m</v>
+      </c>
+      <c r="J1242" s="7"/>
+      <c r="K1242" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1242" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1242" s="7"/>
+      <c r="N1242" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1243" s="7" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B1243" s="7" t="s">
+        <v>1726</v>
+      </c>
+      <c r="C1243" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1243" s="12"/>
+      <c r="E1243" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1243" s="12"/>
+      <c r="G1243" s="8"/>
+      <c r="H1243" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1243" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_nt_BCG_att6t</v>
+      </c>
+      <c r="J1243" s="7"/>
+      <c r="K1243" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1243" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1243" s="7"/>
+      <c r="N1243" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1244" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="B1244" s="7" t="s">
+        <v>586</v>
+      </c>
+      <c r="C1244" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1244" s="12"/>
+      <c r="E1244" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1244" s="12"/>
+      <c r="G1244" s="8"/>
+      <c r="H1244" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1244" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_nt_BCG_attNA</v>
+      </c>
+      <c r="J1244" s="7"/>
+      <c r="K1244" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1244" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1244" s="7"/>
+      <c r="N1244" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1245" s="7" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B1245" s="7" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C1245" s="12" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D1245" s="12"/>
+      <c r="E1245" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1245" s="12"/>
+      <c r="G1245" s="8"/>
+      <c r="H1245" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1245" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_nt_BCG_att4b</v>
+      </c>
+      <c r="J1245" s="7"/>
+      <c r="K1245" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1245" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1245" s="7"/>
+      <c r="N1245" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1246" s="7" t="s">
+        <v>1802</v>
+      </c>
+      <c r="B1246" s="7" t="s">
+        <v>1808</v>
+      </c>
+      <c r="C1246" s="12" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D1246" s="12"/>
+      <c r="E1246" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1246" s="12"/>
+      <c r="G1246" s="8"/>
+      <c r="H1246" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1246" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_nt_BCG_att4m</v>
+      </c>
+      <c r="J1246" s="7"/>
+      <c r="K1246" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1246" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1246" s="7"/>
+      <c r="N1246" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1247" s="7" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B1247" s="7" t="s">
+        <v>1789</v>
+      </c>
+      <c r="C1247" s="12" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D1247" s="12"/>
+      <c r="E1247" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1247" s="12"/>
+      <c r="G1247" s="8"/>
+      <c r="H1247" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1247" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_nt_BCG_att4w</v>
+      </c>
+      <c r="J1247" s="7"/>
+      <c r="K1247" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1247" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1247" s="7"/>
+      <c r="N1247" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1248" s="7" t="s">
+        <v>1813</v>
+      </c>
+      <c r="B1248" s="7" t="s">
+        <v>1810</v>
+      </c>
+      <c r="C1248" s="12" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D1248" s="12"/>
+      <c r="E1248" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1248" s="12"/>
+      <c r="G1248" s="8"/>
+      <c r="H1248" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1248" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_nt_BCG_att1i234b</v>
+      </c>
+      <c r="J1248" s="7"/>
+      <c r="K1248" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1248" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1248" s="7"/>
+      <c r="N1248" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1249" s="7" t="s">
+        <v>1816</v>
+      </c>
+      <c r="B1249" s="7" t="s">
+        <v>1821</v>
+      </c>
+      <c r="C1249" s="12" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D1249" s="12"/>
+      <c r="E1249" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1249" s="12"/>
+      <c r="G1249" s="8"/>
+      <c r="H1249" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1249" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_nt_BCG_att4w5</v>
+      </c>
+      <c r="J1249" s="7"/>
+      <c r="K1249" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1249" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1249" s="7"/>
+      <c r="N1249" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1250" s="7" t="s">
+        <v>634</v>
+      </c>
+      <c r="B1250" s="7" t="s">
+        <v>633</v>
+      </c>
+      <c r="C1250" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1250" s="12"/>
+      <c r="E1250" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1250" s="12"/>
+      <c r="G1250" s="8"/>
+      <c r="H1250" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1250" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_pi_BCG_att1</v>
+      </c>
+      <c r="J1250" s="7"/>
+      <c r="K1250" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1250" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1250" s="7"/>
+      <c r="N1250" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1251" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="B1251" s="7" t="s">
+        <v>1692</v>
+      </c>
+      <c r="C1251" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1251" s="12"/>
+      <c r="E1251" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1251" s="12"/>
+      <c r="G1251" s="8"/>
+      <c r="H1251" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1251" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_pi_BCG_att1i</v>
+      </c>
+      <c r="J1251" s="7"/>
+      <c r="K1251" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1251" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1251" s="7"/>
+      <c r="N1251" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1252" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="B1252" s="7" t="s">
+        <v>1691</v>
+      </c>
+      <c r="C1252" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1252" s="12"/>
+      <c r="E1252" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1252" s="12"/>
+      <c r="G1252" s="8"/>
+      <c r="H1252" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1252" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_pi_BCG_att1m</v>
+      </c>
+      <c r="J1252" s="7"/>
+      <c r="K1252" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1252" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1252" s="7"/>
+      <c r="N1252" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1253" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1253" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="C1253" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1253" s="12"/>
+      <c r="E1253" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1253" s="12"/>
+      <c r="G1253" s="8"/>
+      <c r="H1253" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1253" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_pi_BCG_att12</v>
+      </c>
+      <c r="J1253" s="7"/>
+      <c r="K1253" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1253" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1253" s="7"/>
+      <c r="N1253" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1254" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1254" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="C1254" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1254" s="12"/>
+      <c r="E1254" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1254" s="12"/>
+      <c r="G1254" s="8"/>
+      <c r="H1254" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1254" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_pi_BCG_att1i2</v>
+      </c>
+      <c r="J1254" s="7"/>
+      <c r="K1254" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1254" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1254" s="7"/>
+      <c r="N1254" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1255" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1255" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="C1255" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1255" s="12"/>
+      <c r="E1255" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1255" s="12"/>
+      <c r="G1255" s="8"/>
+      <c r="H1255" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1255" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_pi_BCG_att123</v>
+      </c>
+      <c r="J1255" s="7"/>
+      <c r="K1255" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1255" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1255" s="7"/>
+      <c r="N1255" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1256" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="B1256" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="C1256" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1256" s="12"/>
+      <c r="E1256" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1256" s="12"/>
+      <c r="G1256" s="8"/>
+      <c r="H1256" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1256" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_pi_BCG_att1i23</v>
+      </c>
+      <c r="J1256" s="7"/>
+      <c r="K1256" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1256" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1256" s="7"/>
+      <c r="N1256" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1257" s="7" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B1257" s="7" t="s">
+        <v>1727</v>
+      </c>
+      <c r="C1257" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1257" s="12"/>
+      <c r="E1257" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1257" s="12"/>
+      <c r="G1257" s="8"/>
+      <c r="H1257" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1257" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_pi_BCG_att1i236i</v>
+      </c>
+      <c r="J1257" s="7"/>
+      <c r="K1257" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1257" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1257" s="7"/>
+      <c r="N1257" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1258" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="B1258" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="C1258" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1258" s="12"/>
+      <c r="E1258" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1258" s="12"/>
+      <c r="G1258" s="8"/>
+      <c r="H1258" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1258" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_pi_BCG_att2</v>
+      </c>
+      <c r="J1258" s="7"/>
+      <c r="K1258" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1258" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1258" s="7"/>
+      <c r="N1258" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1259" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1259" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="C1259" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1259" s="12"/>
+      <c r="E1259" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1259" s="12"/>
+      <c r="G1259" s="8"/>
+      <c r="H1259" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1259" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_pi_BCG_att23</v>
+      </c>
+      <c r="J1259" s="7"/>
+      <c r="K1259" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1259" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1259" s="7"/>
+      <c r="N1259" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1260" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1260" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="C1260" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1260" s="12"/>
+      <c r="E1260" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1260" s="12"/>
+      <c r="G1260" s="8"/>
+      <c r="H1260" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1260" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_pi_BCG_att234</v>
+      </c>
+      <c r="J1260" s="7"/>
+      <c r="K1260" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1260" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1260" s="7"/>
+      <c r="N1260" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1261" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="B1261" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="C1261" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1261" s="12"/>
+      <c r="E1261" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1261" s="12"/>
+      <c r="G1261" s="8"/>
+      <c r="H1261" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1261" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_pi_BCG_att3</v>
+      </c>
+      <c r="J1261" s="7"/>
+      <c r="K1261" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1261" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1261" s="7"/>
+      <c r="N1261" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1262" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1262" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="C1262" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1262" s="12"/>
+      <c r="E1262" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1262" s="12"/>
+      <c r="G1262" s="8"/>
+      <c r="H1262" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1262" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_pi_BCG_att4</v>
+      </c>
+      <c r="J1262" s="7"/>
+      <c r="K1262" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1262" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1262" s="7"/>
+      <c r="N1262" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1263" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="B1263" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="C1263" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1263" s="12"/>
+      <c r="E1263" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1263" s="12"/>
+      <c r="G1263" s="8"/>
+      <c r="H1263" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1263" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_pi_BCG_att45</v>
+      </c>
+      <c r="J1263" s="7"/>
+      <c r="K1263" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1263" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1263" s="7"/>
+      <c r="N1263" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1264" s="7" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B1264" s="7" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C1264" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1264" s="12"/>
+      <c r="E1264" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1264" s="12"/>
+      <c r="G1264" s="8"/>
+      <c r="H1264" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1264" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_pi_BCG_att456</v>
+      </c>
+      <c r="J1264" s="7"/>
+      <c r="K1264" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1264" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1264" s="7"/>
+      <c r="N1264" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1265" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1265" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="C1265" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1265" s="12"/>
+      <c r="E1265" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1265" s="12"/>
+      <c r="G1265" s="8"/>
+      <c r="H1265" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1265" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_pi_BCG_att5</v>
+      </c>
+      <c r="J1265" s="7"/>
+      <c r="K1265" s="1" t="str">
+        <f t="shared" si="126"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1265" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1265" s="7"/>
+      <c r="N1265" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1266" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1266" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="C1266" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1266" s="12"/>
+      <c r="E1266" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1266" s="12"/>
+      <c r="G1266" s="8"/>
+      <c r="H1266" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1266" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_pi_BCG_att56</v>
+      </c>
+      <c r="J1266" s="7"/>
+      <c r="K1266" s="1" t="str">
+        <f t="shared" ref="K1266:K1306" si="132">"unclassified_"&amp;H1266</f>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1266" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1266" s="7"/>
+      <c r="N1266" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1267" s="7" t="s">
+        <v>1702</v>
+      </c>
+      <c r="B1267" s="7" t="s">
+        <v>1719</v>
+      </c>
+      <c r="C1267" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1267" s="12"/>
+      <c r="E1267" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1267" s="12"/>
+      <c r="G1267" s="8"/>
+      <c r="H1267" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1267" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_pi_BCG_att56t</v>
+      </c>
+      <c r="J1267" s="7"/>
+      <c r="K1267" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1267" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1267" s="7"/>
+      <c r="N1267" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1268" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1268" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1268" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1268" s="12"/>
+      <c r="E1268" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1268" s="12"/>
+      <c r="G1268" s="8"/>
+      <c r="H1268" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1268" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_pi_BCG_att6</v>
+      </c>
+      <c r="J1268" s="7"/>
+      <c r="K1268" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1268" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1268" s="7"/>
+      <c r="N1268" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1269" s="7" t="s">
+        <v>1703</v>
+      </c>
+      <c r="B1269" s="7" t="s">
+        <v>1718</v>
+      </c>
+      <c r="C1269" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1269" s="12"/>
+      <c r="E1269" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1269" s="12"/>
+      <c r="G1269" s="8"/>
+      <c r="H1269" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1269" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_pi_BCG_att6i</v>
+      </c>
+      <c r="J1269" s="7"/>
+      <c r="K1269" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1269" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1269" s="7"/>
+      <c r="N1269" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1270" s="7" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B1270" s="7" t="s">
+        <v>1717</v>
+      </c>
+      <c r="C1270" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1270" s="12"/>
+      <c r="E1270" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1270" s="12"/>
+      <c r="G1270" s="8"/>
+      <c r="H1270" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1270" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_pi_BCG_att6m</v>
+      </c>
+      <c r="J1270" s="7"/>
+      <c r="K1270" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1270" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1270" s="7"/>
+      <c r="N1270" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1271" s="7" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B1271" s="7" t="s">
+        <v>1716</v>
+      </c>
+      <c r="C1271" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1271" s="12"/>
+      <c r="E1271" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1271" s="12"/>
+      <c r="G1271" s="8"/>
+      <c r="H1271" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1271" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_pi_BCG_att6t</v>
+      </c>
+      <c r="J1271" s="7"/>
+      <c r="K1271" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1271" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1271" s="7"/>
+      <c r="N1271" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1272" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="B1272" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="C1272" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1272" s="12"/>
+      <c r="E1272" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1272" s="12"/>
+      <c r="G1272" s="8"/>
+      <c r="H1272" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1272" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_pi_BCG_attNA</v>
+      </c>
+      <c r="J1272" s="7"/>
+      <c r="K1272" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1272" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1272" s="7"/>
+      <c r="N1272" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1273" s="7" t="s">
+        <v>1780</v>
+      </c>
+      <c r="B1273" s="7" t="s">
+        <v>1782</v>
+      </c>
+      <c r="C1273" s="12" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D1273" s="12"/>
+      <c r="E1273" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1273" s="12"/>
+      <c r="G1273" s="8"/>
+      <c r="H1273" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1273" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_pi_BCG_att4b</v>
+      </c>
+      <c r="J1273" s="7"/>
+      <c r="K1273" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1273" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1273" s="7"/>
+      <c r="N1273" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1274" s="7" t="s">
+        <v>1803</v>
+      </c>
+      <c r="B1274" s="7" t="s">
+        <v>1809</v>
+      </c>
+      <c r="C1274" s="12" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D1274" s="12"/>
+      <c r="E1274" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1274" s="12"/>
+      <c r="G1274" s="8"/>
+      <c r="H1274" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1274" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_pi_BCG_att4m</v>
+      </c>
+      <c r="J1274" s="7"/>
+      <c r="K1274" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1274" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1274" s="7"/>
+      <c r="N1274" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1275" s="7" t="s">
+        <v>1781</v>
+      </c>
+      <c r="B1275" s="7" t="s">
+        <v>1783</v>
+      </c>
+      <c r="C1275" s="12" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D1275" s="12"/>
+      <c r="E1275" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1275" s="12"/>
+      <c r="G1275" s="8"/>
+      <c r="H1275" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1275" s="19" t="str">
+        <f t="shared" si="130"/>
+        <v>algae_pi_BCG_att4w</v>
+      </c>
+      <c r="J1275" s="7"/>
+      <c r="K1275" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1275" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1275" s="7"/>
+      <c r="N1275" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1276" s="7" t="s">
+        <v>1814</v>
+      </c>
+      <c r="B1276" s="7" t="s">
+        <v>1811</v>
+      </c>
+      <c r="C1276" s="12" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D1276" s="12"/>
+      <c r="E1276" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1276" s="12"/>
+      <c r="G1276" s="8"/>
+      <c r="H1276" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1276" s="19" t="str">
+        <f t="shared" ref="I1276:I1306" si="133">H1276&amp;"_"&amp;TRIM(A1276)</f>
+        <v>algae_pi_BCG_att1i234b</v>
+      </c>
+      <c r="J1276" s="7"/>
+      <c r="K1276" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1276" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1276" s="7"/>
+      <c r="N1276" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1277" s="7" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B1277" s="7" t="s">
+        <v>1820</v>
+      </c>
+      <c r="C1277" s="12" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D1277" s="12"/>
+      <c r="E1277" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1277" s="12"/>
+      <c r="G1277" s="8"/>
+      <c r="H1277" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1277" s="19" t="str">
+        <f t="shared" si="133"/>
+        <v>algae_pi_BCG_att4w5</v>
+      </c>
+      <c r="J1277" s="7"/>
+      <c r="K1277" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1277" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1277" s="7"/>
+      <c r="N1277" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1278" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="B1278" s="7" t="s">
+        <v>632</v>
+      </c>
+      <c r="C1278" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1278" s="12"/>
+      <c r="E1278" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1278" s="12"/>
+      <c r="G1278" s="8"/>
+      <c r="H1278" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1278" s="19" t="str">
+        <f t="shared" si="133"/>
+        <v>algae_pt_BCG_att1</v>
+      </c>
+      <c r="J1278" s="7"/>
+      <c r="K1278" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1278" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1278" s="7"/>
+      <c r="N1278" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1279" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="B1279" s="7" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C1279" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1279" s="12"/>
+      <c r="E1279" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1279" s="12"/>
+      <c r="G1279" s="8"/>
+      <c r="H1279" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1279" s="19" t="str">
+        <f t="shared" si="133"/>
+        <v>algae_pt_BCG_att1i</v>
+      </c>
+      <c r="J1279" s="7"/>
+      <c r="K1279" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1279" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1279" s="7"/>
+      <c r="N1279" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1280" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B1280" s="7" t="s">
+        <v>1695</v>
+      </c>
+      <c r="C1280" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1280" s="12"/>
+      <c r="E1280" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1280" s="12"/>
+      <c r="G1280" s="8"/>
+      <c r="H1280" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1280" s="19" t="str">
+        <f t="shared" si="133"/>
+        <v>algae_pt_BCG_att1m</v>
+      </c>
+      <c r="J1280" s="7"/>
+      <c r="K1280" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1280" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1280" s="7"/>
+      <c r="N1280" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1281" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1281" s="7" t="s">
+        <v>352</v>
+      </c>
+      <c r="C1281" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1281" s="12"/>
+      <c r="E1281" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1281" s="12"/>
+      <c r="G1281" s="8"/>
+      <c r="H1281" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1281" s="19" t="str">
+        <f t="shared" si="133"/>
+        <v>algae_pt_BCG_att12</v>
+      </c>
+      <c r="J1281" s="7"/>
+      <c r="K1281" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1281" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1281" s="7"/>
+      <c r="N1281" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1282" s="7" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B1282" s="7" t="s">
+        <v>1837</v>
+      </c>
+      <c r="C1282" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1282" s="12"/>
+      <c r="E1282" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1282" s="12"/>
+      <c r="G1282" s="8"/>
+      <c r="H1282" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1282" s="19" t="str">
+        <f t="shared" si="133"/>
+        <v>algae_pt_BCG_att1234</v>
+      </c>
+      <c r="J1282" s="7"/>
+      <c r="K1282" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1282" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1282" s="7"/>
+      <c r="N1282" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1283" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1283" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="C1283" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1283" s="12"/>
+      <c r="E1283" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1283" s="12"/>
+      <c r="G1283" s="8"/>
+      <c r="H1283" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1283" s="19" t="str">
+        <f t="shared" si="133"/>
+        <v>algae_pt_BCG_att1i2</v>
+      </c>
+      <c r="J1283" s="7"/>
+      <c r="K1283" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1283" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1283" s="7"/>
+      <c r="N1283" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1284" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B1284" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="C1284" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1284" s="12"/>
+      <c r="E1284" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1284" s="12"/>
+      <c r="G1284" s="8"/>
+      <c r="H1284" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1284" s="19" t="str">
+        <f t="shared" si="133"/>
+        <v>algae_pt_BCG_att123</v>
+      </c>
+      <c r="J1284" s="7"/>
+      <c r="K1284" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1284" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1284" s="7"/>
+      <c r="N1284" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1285" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1285" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="C1285" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1285" s="12"/>
+      <c r="E1285" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1285" s="12"/>
+      <c r="G1285" s="8"/>
+      <c r="H1285" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1285" s="19" t="str">
+        <f t="shared" si="133"/>
+        <v>algae_pt_BCG_att1i23</v>
+      </c>
+      <c r="J1285" s="7"/>
+      <c r="K1285" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1285" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1285" s="7"/>
+      <c r="N1285" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1286" s="7" t="s">
+        <v>1706</v>
+      </c>
+      <c r="B1286" s="7" t="s">
+        <v>1715</v>
+      </c>
+      <c r="C1286" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1286" s="12"/>
+      <c r="E1286" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1286" s="12"/>
+      <c r="G1286" s="8"/>
+      <c r="H1286" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1286" s="19" t="str">
+        <f t="shared" si="133"/>
+        <v>algae_pt_BCG_att1i236i</v>
+      </c>
+      <c r="J1286" s="7"/>
+      <c r="K1286" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1286" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1286" s="7"/>
+      <c r="N1286" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1287" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1287" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="C1287" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1287" s="12"/>
+      <c r="E1287" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1287" s="12"/>
+      <c r="G1287" s="8"/>
+      <c r="H1287" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1287" s="19" t="str">
+        <f t="shared" si="133"/>
+        <v>algae_pt_BCG_att2</v>
+      </c>
+      <c r="J1287" s="7"/>
+      <c r="K1287" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1287" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1287" s="7"/>
+      <c r="N1287" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1288" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1288" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="C1288" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1288" s="12"/>
+      <c r="E1288" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1288" s="12"/>
+      <c r="G1288" s="8"/>
+      <c r="H1288" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1288" s="19" t="str">
+        <f t="shared" si="133"/>
+        <v>algae_pt_BCG_att23</v>
+      </c>
+      <c r="J1288" s="7"/>
+      <c r="K1288" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1288" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1288" s="7"/>
+      <c r="N1288" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1289" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1289" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="C1289" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1289" s="12"/>
+      <c r="E1289" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1289" s="12"/>
+      <c r="G1289" s="8"/>
+      <c r="H1289" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1289" s="19" t="str">
+        <f t="shared" si="133"/>
+        <v>algae_pt_BCG_att234</v>
+      </c>
+      <c r="J1289" s="7"/>
+      <c r="K1289" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1289" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1289" s="7"/>
+      <c r="N1289" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1290" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="B1290" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="C1290" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1290" s="12"/>
+      <c r="E1290" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1290" s="12"/>
+      <c r="G1290" s="8"/>
+      <c r="H1290" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1290" s="19" t="str">
+        <f t="shared" si="133"/>
+        <v>algae_pt_BCG_att3</v>
+      </c>
+      <c r="J1290" s="7"/>
+      <c r="K1290" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1290" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1290" s="7"/>
+      <c r="N1290" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1291" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1291" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="C1291" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1291" s="12"/>
+      <c r="E1291" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1291" s="12"/>
+      <c r="G1291" s="8"/>
+      <c r="H1291" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1291" s="19" t="str">
+        <f t="shared" si="133"/>
+        <v>algae_pt_BCG_att4</v>
+      </c>
+      <c r="J1291" s="7"/>
+      <c r="K1291" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1291" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1291" s="7"/>
+      <c r="N1291" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1292" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1292" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="C1292" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1292" s="12"/>
+      <c r="E1292" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1292" s="12"/>
+      <c r="G1292" s="8"/>
+      <c r="H1292" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1292" s="19" t="str">
+        <f t="shared" si="133"/>
+        <v>algae_pt_BCG_att45</v>
+      </c>
+      <c r="J1292" s="7"/>
+      <c r="K1292" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1292" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1292" s="7"/>
+      <c r="N1292" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1293" s="7" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B1293" s="7" t="s">
+        <v>1375</v>
+      </c>
+      <c r="C1293" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1293" s="12"/>
+      <c r="E1293" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1293" s="12"/>
+      <c r="G1293" s="8"/>
+      <c r="H1293" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1293" s="19" t="str">
+        <f t="shared" si="133"/>
+        <v>algae_pt_BCG_att456</v>
+      </c>
+      <c r="J1293" s="7"/>
+      <c r="K1293" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1293" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1293" s="7"/>
+      <c r="N1293" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1294" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1294" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="C1294" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1294" s="12"/>
+      <c r="E1294" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1294" s="12"/>
+      <c r="G1294" s="8"/>
+      <c r="H1294" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1294" s="19" t="str">
+        <f t="shared" si="133"/>
+        <v>algae_pt_BCG_att5</v>
+      </c>
+      <c r="J1294" s="7"/>
+      <c r="K1294" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1294" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1294" s="7"/>
+      <c r="N1294" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1295" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1295" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="C1295" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1295" s="12"/>
+      <c r="E1295" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1295" s="12"/>
+      <c r="G1295" s="8"/>
+      <c r="H1295" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1295" s="19" t="str">
+        <f t="shared" si="133"/>
+        <v>algae_pt_BCG_att56</v>
+      </c>
+      <c r="J1295" s="7"/>
+      <c r="K1295" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1295" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1295" s="7"/>
+      <c r="N1295" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1296" s="7" t="s">
+        <v>1707</v>
+      </c>
+      <c r="B1296" s="7" t="s">
+        <v>1714</v>
+      </c>
+      <c r="C1296" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1296" s="12"/>
+      <c r="E1296" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1296" s="12"/>
+      <c r="G1296" s="8"/>
+      <c r="H1296" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1296" s="19" t="str">
+        <f t="shared" si="133"/>
+        <v>algae_pt_BCG_att56t</v>
+      </c>
+      <c r="J1296" s="7"/>
+      <c r="K1296" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1296" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1296" s="7"/>
+      <c r="N1296" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1297" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B1297" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="C1297" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1297" s="12"/>
+      <c r="E1297" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1297" s="12"/>
+      <c r="G1297" s="8"/>
+      <c r="H1297" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1297" s="19" t="str">
+        <f t="shared" si="133"/>
+        <v>algae_pt_BCG_att6</v>
+      </c>
+      <c r="J1297" s="7"/>
+      <c r="K1297" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1297" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1297" s="7"/>
+      <c r="N1297" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1298" s="7" t="s">
+        <v>1708</v>
+      </c>
+      <c r="B1298" s="7" t="s">
+        <v>1711</v>
+      </c>
+      <c r="C1298" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1298" s="12"/>
+      <c r="E1298" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1298" s="12"/>
+      <c r="G1298" s="8"/>
+      <c r="H1298" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1298" s="19" t="str">
+        <f t="shared" si="133"/>
+        <v>algae_pt_BCG_att6i</v>
+      </c>
+      <c r="J1298" s="7"/>
+      <c r="K1298" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1298" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1298" s="7"/>
+      <c r="N1298" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1299" s="7" t="s">
+        <v>1709</v>
+      </c>
+      <c r="B1299" s="7" t="s">
+        <v>1712</v>
+      </c>
+      <c r="C1299" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1299" s="12"/>
+      <c r="E1299" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1299" s="12"/>
+      <c r="G1299" s="8"/>
+      <c r="H1299" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1299" s="19" t="str">
+        <f t="shared" si="133"/>
+        <v>algae_pt_BCG_att6m</v>
+      </c>
+      <c r="J1299" s="7"/>
+      <c r="K1299" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1299" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1299" s="7"/>
+      <c r="N1299" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1300" s="7" t="s">
+        <v>1710</v>
+      </c>
+      <c r="B1300" s="7" t="s">
+        <v>1713</v>
+      </c>
+      <c r="C1300" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1300" s="12"/>
+      <c r="E1300" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1300" s="12"/>
+      <c r="G1300" s="8"/>
+      <c r="H1300" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1300" s="19" t="str">
+        <f t="shared" si="133"/>
+        <v>algae_pt_BCG_att6t</v>
+      </c>
+      <c r="J1300" s="7"/>
+      <c r="K1300" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1300" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1300" s="7"/>
+      <c r="N1300" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1301" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="B1301" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="C1301" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1301" s="12"/>
+      <c r="E1301" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1301" s="12"/>
+      <c r="G1301" s="8"/>
+      <c r="H1301" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1301" s="19" t="str">
+        <f t="shared" si="133"/>
+        <v>algae_pt_BCG_attNA</v>
+      </c>
+      <c r="J1301" s="7"/>
+      <c r="K1301" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1301" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1301" s="7"/>
+      <c r="N1301" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1302" s="7" t="s">
+        <v>1778</v>
+      </c>
+      <c r="B1302" s="7" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C1302" s="12" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D1302" s="12"/>
+      <c r="E1302" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1302" s="12"/>
+      <c r="G1302" s="8"/>
+      <c r="H1302" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1302" s="19" t="str">
+        <f t="shared" si="133"/>
+        <v>algae_pt_BCG_att4b</v>
+      </c>
+      <c r="J1302" s="7"/>
+      <c r="K1302" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1302" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1302" s="7"/>
+      <c r="N1302" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1303" s="7" t="s">
+        <v>1804</v>
+      </c>
+      <c r="B1303" s="7" t="s">
+        <v>1805</v>
+      </c>
+      <c r="C1303" s="12" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D1303" s="12"/>
+      <c r="E1303" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1303" s="12"/>
+      <c r="G1303" s="8"/>
+      <c r="H1303" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1303" s="19" t="str">
+        <f t="shared" si="133"/>
+        <v>algae_pt_BCG_att4m</v>
+      </c>
+      <c r="J1303" s="7"/>
+      <c r="K1303" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1303" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1303" s="7"/>
+      <c r="N1303" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1304" s="7" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B1304" s="7" t="s">
+        <v>1785</v>
+      </c>
+      <c r="C1304" s="12" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D1304" s="12"/>
+      <c r="E1304" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1304" s="12"/>
+      <c r="G1304" s="8"/>
+      <c r="H1304" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1304" s="19" t="str">
+        <f t="shared" si="133"/>
+        <v>algae_pt_BCG_att4w</v>
+      </c>
+      <c r="J1304" s="7"/>
+      <c r="K1304" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1304" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1304" s="7"/>
+      <c r="N1304" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1305" s="7" t="s">
+        <v>1815</v>
+      </c>
+      <c r="B1305" s="7" t="s">
+        <v>1812</v>
+      </c>
+      <c r="C1305" s="12" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D1305" s="12"/>
+      <c r="E1305" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1305" s="12"/>
+      <c r="G1305" s="8"/>
+      <c r="H1305" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1305" s="19" t="str">
+        <f t="shared" si="133"/>
+        <v>algae_pt_BCG_att1i234b</v>
+      </c>
+      <c r="J1305" s="7"/>
+      <c r="K1305" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1305" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1305" s="7"/>
+      <c r="N1305" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1306" s="7" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B1306" s="7" t="s">
+        <v>1819</v>
+      </c>
+      <c r="C1306" s="12" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D1306" s="12"/>
+      <c r="E1306" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1306" s="12"/>
+      <c r="G1306" s="8"/>
+      <c r="H1306" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1306" s="19" t="str">
+        <f t="shared" si="133"/>
+        <v>algae_pt_BCG_att4w5</v>
+      </c>
+      <c r="J1306" s="7"/>
+      <c r="K1306" s="1" t="str">
+        <f t="shared" si="132"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1306" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1306" s="7"/>
+      <c r="N1306" s="1" t="b">
         <v>0</v>
       </c>
     </row>

--- a/inst/extdata/MetricNames.xlsx
+++ b/inst/extdata/MetricNames.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erik.Leppo\Documents\GitHub\BioMonTools\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CFED887-889F-4B50-BBC7-CB906B086A65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1941FC76-DA25-4BA2-9DA1-B231E2832DC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NOTES" sheetId="4" r:id="rId1"/>
     <sheet name="MetricMetadata" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">MetricMetadata!$A$5:$N$1220</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">MetricMetadata!$A$5:$N$1307</definedName>
     <definedName name="FileName" localSheetId="0">NOTES!$B$8</definedName>
     <definedName name="FileName">#REF!</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">MetricMetadata!$A:$A,MetricMetadata!$5:$5</definedName>
@@ -302,7 +302,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8645" uniqueCount="2401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8654" uniqueCount="2405">
   <si>
     <t>nt_total</t>
   </si>
@@ -7505,6 +7505,18 @@
   </si>
   <si>
     <t>Additional bug metricss, Issue #142, n = 7</t>
+  </si>
+  <si>
+    <t>nord_EPT for BCGcalc ORWA</t>
+  </si>
+  <si>
+    <t>nord_EPT</t>
+  </si>
+  <si>
+    <t>number of unique - orders - Order Ephemeroptera, Plecoptera, or Trichoptera</t>
+  </si>
+  <si>
+    <t>BCG, ORWA</t>
   </si>
 </sst>
 </file>
@@ -8280,7 +8292,7 @@
   <sheetPr>
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:N117"/>
+  <dimension ref="A1:N118"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -8308,7 +8320,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="24">
-        <v>46164</v>
+        <v>46177</v>
       </c>
       <c r="J5" s="43" t="s">
         <v>1999</v>
@@ -8326,7 +8338,7 @@
       </c>
       <c r="J6" s="42">
         <f>COUNTA(MetricMetadata!$H$6:$H$2023)</f>
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="M6" t="s">
         <v>2012</v>
@@ -8348,7 +8360,7 @@
       </c>
       <c r="H7">
         <f>COUNTIF(MetricMetadata!$H$6:$H$2023,G7)</f>
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M7" t="s">
         <v>2014</v>
@@ -8460,7 +8472,7 @@
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="H14" s="41">
         <f>SUM(H7:H11)</f>
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="I14" t="s">
         <v>1998</v>
@@ -9268,6 +9280,14 @@
       </c>
       <c r="C117" s="59" t="s">
         <v>2383</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="24">
+        <v>46177</v>
+      </c>
+      <c r="B118" t="s">
+        <v>2401</v>
       </c>
     </row>
   </sheetData>
@@ -9353,7 +9373,7 @@
     </row>
     <row r="2" spans="1:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>46164</v>
+        <v>46177</v>
       </c>
       <c r="B2" s="38" t="s">
         <v>1762</v>
@@ -9373,7 +9393,7 @@
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <f>SUBTOTAL(3,A6:A2107)</f>
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="B3" s="4">
         <f>COUNTIF($B$6:$B$1001,B2)</f>
@@ -57219,11 +57239,47 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1307" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1307" s="7" t="s">
+        <v>2402</v>
+      </c>
+      <c r="B1307" s="8" t="s">
+        <v>2403</v>
+      </c>
+      <c r="C1307" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1307" s="54"/>
+      <c r="E1307" s="13"/>
+      <c r="F1307" s="13"/>
+      <c r="G1307" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="H1307" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="I1307" s="19" t="s">
+        <v>1947</v>
+      </c>
+      <c r="J1307" s="7">
+        <v>1</v>
+      </c>
+      <c r="K1307" s="1" t="s">
+        <v>1667</v>
+      </c>
+      <c r="L1307" s="1" t="s">
+        <v>1583</v>
+      </c>
+      <c r="M1307" s="1"/>
+      <c r="N1307" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
     <row r="2023" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2023" s="52"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:N1220" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A5:N1307" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1004:A1011">
     <sortCondition ref="A1004:A1011"/>
   </sortState>

--- a/inst/extdata/MetricNames.xlsx
+++ b/inst/extdata/MetricNames.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erik.Leppo\Documents\GitHub\BioMonTools\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64BCC283-0547-47D7-BE8E-097F9840C50A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60AC92FC-BD7C-452F-B745-96222E0A8224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="MetricMetadata" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">MetricMetadata!$A$5:$N$1307</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">MetricMetadata!$A$5:$N$1312</definedName>
     <definedName name="FileName" localSheetId="0">NOTES!$B$8</definedName>
     <definedName name="FileName">#REF!</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">MetricMetadata!$A:$A,MetricMetadata!$5:$5</definedName>
@@ -302,7 +302,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8662" uniqueCount="2408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8688" uniqueCount="2417">
   <si>
     <t>nt_total</t>
   </si>
@@ -7375,12 +7375,6 @@
     <t>percent of taxa - non-Insecta, BCG attributes 4, 5, or 6t</t>
   </si>
   <si>
-    <t>pi_dom01_BCG_att456t</t>
-  </si>
-  <si>
-    <t>percent individuals, dominant 1, BCG attributes 4, 5, or 6t</t>
-  </si>
-  <si>
     <t>percent individuals, dominant 1, BCG attributes 4, 5, or 6</t>
   </si>
   <si>
@@ -7519,13 +7513,46 @@
     <t>BCG, ORWA</t>
   </si>
   <si>
+    <t>pi_dom02_BCG_att456 for ORWA Foothills_Riffle</t>
+  </si>
+  <si>
+    <t>percent individuals, dominant 1, BCG attributes 4, 5, 6m, or 6t</t>
+  </si>
+  <si>
+    <t>pi_dom02_BCG_att456m6t</t>
+  </si>
+  <si>
+    <t>percent individuals, dominant 2, BCG attributes 4, 5, 6m, or 6t</t>
+  </si>
+  <si>
+    <t>nt_NonInsTrombJuga_BCG_att456m6t</t>
+  </si>
+  <si>
+    <t>pi_NonInsTrombJuga_BCG_att456m6t</t>
+  </si>
+  <si>
+    <t>pt_NonInsTrombJuga_BCG_att456m6t</t>
+  </si>
+  <si>
+    <t>number taxa - BCG Attribute 4, 5, 6m, 6t, excluding Class Insecta, Order Trombidiformes, and Genus Juga</t>
+  </si>
+  <si>
+    <t>percent (0-100) individuals - BCG Attribute 4, 5, 6m, 6t, excluding Class Insecta, Order Trombidiformes, and Genus Juga</t>
+  </si>
+  <si>
+    <t>percent (0-100) taxa - BCG Attribute 4, 5, 6m, 6t, excluding Class Insecta, Order Trombidiformes, and Genus Juga</t>
+  </si>
+  <si>
+    <t>Update att 456 to att456m6t for Boise</t>
+  </si>
+  <si>
+    <t>pi_dom01_BCG_att456m6t</t>
+  </si>
+  <si>
     <t>pi_dom02_BCG_att456</t>
   </si>
   <si>
     <t>percent individuals, dominant 2, BCG attributes 4, 5, or 6</t>
-  </si>
-  <si>
-    <t>pi_dom02_BCG_att456 for ORWA Foothills_Riffle</t>
   </si>
 </sst>
 </file>
@@ -8311,7 +8338,7 @@
   <sheetPr>
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:N119"/>
+  <dimension ref="A1:N120"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -8340,7 +8367,7 @@
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="61">
         <f>MAX(A22:A301)</f>
-        <v>46182</v>
+        <v>46210</v>
       </c>
       <c r="J5" s="43" t="s">
         <v>1999</v>
@@ -8357,8 +8384,8 @@
         <v>1832</v>
       </c>
       <c r="J6" s="42">
-        <f>COUNTA(MetricMetadata!$H$6:$H$2023)</f>
-        <v>1303</v>
+        <f>COUNTA(MetricMetadata!$H$6:$H$2022)</f>
+        <v>1307</v>
       </c>
       <c r="M6" t="s">
         <v>2012</v>
@@ -8379,8 +8406,8 @@
         <v>652</v>
       </c>
       <c r="H7">
-        <f>COUNTIF(MetricMetadata!$H$6:$H$2023,G7)</f>
-        <v>565</v>
+        <f>COUNTIF(MetricMetadata!$H$6:$H$2022,G7)</f>
+        <v>569</v>
       </c>
       <c r="M7" t="s">
         <v>2014</v>
@@ -8401,7 +8428,7 @@
         <v>391</v>
       </c>
       <c r="H8">
-        <f>COUNTIF(MetricMetadata!$H$6:$H$2023,G8)</f>
+        <f>COUNTIF(MetricMetadata!$H$6:$H$2022,G8)</f>
         <v>380</v>
       </c>
       <c r="M8" t="s">
@@ -8423,7 +8450,7 @@
         <v>799</v>
       </c>
       <c r="H9">
-        <f>COUNTIF(MetricMetadata!$H$6:$H$2023,G9)</f>
+        <f>COUNTIF(MetricMetadata!$H$6:$H$2022,G9)</f>
         <v>339</v>
       </c>
       <c r="M9" t="s">
@@ -8438,7 +8465,7 @@
         <v>1955</v>
       </c>
       <c r="H10">
-        <f>COUNTIF(MetricMetadata!$H$6:$H$2023,G10)</f>
+        <f>COUNTIF(MetricMetadata!$H$6:$H$2022,G10)</f>
         <v>16</v>
       </c>
       <c r="M10" t="s">
@@ -8456,7 +8483,7 @@
         <v>390</v>
       </c>
       <c r="H11">
-        <f>COUNTIF(MetricMetadata!$H$6:$H$2023,G11)</f>
+        <f>COUNTIF(MetricMetadata!$H$6:$H$2022,G11)</f>
         <v>3</v>
       </c>
       <c r="M11" t="s">
@@ -8471,7 +8498,7 @@
         <v>208</v>
       </c>
       <c r="H12">
-        <f>COUNTIF(MetricMetadata!$H$6:$H$2023,G12)</f>
+        <f>COUNTIF(MetricMetadata!$H$6:$H$2022,G12)</f>
         <v>0</v>
       </c>
       <c r="I12" s="40" t="s">
@@ -8492,7 +8519,7 @@
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="H14" s="41">
         <f>SUM(H7:H11)</f>
-        <v>1303</v>
+        <v>1307</v>
       </c>
       <c r="I14" t="s">
         <v>1998</v>
@@ -9264,12 +9291,12 @@
         <v>46160</v>
       </c>
       <c r="B113" t="s">
-        <v>2366</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B114" t="s">
-        <v>2376</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -9277,7 +9304,7 @@
         <v>46161</v>
       </c>
       <c r="B115" t="s">
-        <v>2382</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -9285,10 +9312,10 @@
         <v>46164</v>
       </c>
       <c r="B116" t="s">
-        <v>2400</v>
+        <v>2398</v>
       </c>
       <c r="C116" s="59" t="s">
-        <v>2383</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -9296,10 +9323,10 @@
         <v>46164</v>
       </c>
       <c r="B117" t="s">
-        <v>2399</v>
+        <v>2397</v>
       </c>
       <c r="C117" s="59" t="s">
-        <v>2383</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -9307,7 +9334,7 @@
         <v>46177</v>
       </c>
       <c r="B118" t="s">
-        <v>2401</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -9315,7 +9342,15 @@
         <v>46182</v>
       </c>
       <c r="B119" s="60" t="s">
-        <v>2407</v>
+        <v>2403</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="24">
+        <v>46210</v>
+      </c>
+      <c r="B120" t="s">
+        <v>2413</v>
       </c>
     </row>
   </sheetData>
@@ -9359,7 +9394,7 @@
   <sheetPr codeName="Sheet3" filterMode="1">
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
-  <dimension ref="A1:N2023"/>
+  <dimension ref="A1:N2022"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.7109375" style="4" bestFit="1" customWidth="1"/>
@@ -9401,7 +9436,7 @@
     </row>
     <row r="2" spans="1:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
-        <v>46182</v>
+        <v>46210</v>
       </c>
       <c r="B2" s="38" t="s">
         <v>1762</v>
@@ -9420,8 +9455,8 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
-        <f>SUBTOTAL(3,A6:A2107)</f>
-        <v>3</v>
+        <f>SUBTOTAL(3,A6:A2106)</f>
+        <v>6</v>
       </c>
       <c r="B3" s="4">
         <f>COUNTIF($B$6:$B$1001,B2)</f>
@@ -15639,7 +15674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A176" s="7" t="s">
         <v>137</v>
       </c>
@@ -20559,7 +20594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A310" s="7" t="s">
         <v>145</v>
       </c>
@@ -25702,7 +25737,7 @@
         <v>1530</v>
       </c>
       <c r="B452" s="7" t="s">
-        <v>2362</v>
+        <v>2360</v>
       </c>
       <c r="C452" s="16" t="s">
         <v>180</v>
@@ -25738,7 +25773,7 @@
         <v>1531</v>
       </c>
       <c r="B453" s="7" t="s">
-        <v>2361</v>
+        <v>2359</v>
       </c>
       <c r="C453" s="16" t="s">
         <v>180</v>
@@ -40468,7 +40503,7 @@
         <v>2133</v>
       </c>
     </row>
-    <row r="852" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A852" s="7" t="s">
         <v>145</v>
       </c>
@@ -43362,7 +43397,7 @@
         <v>1530</v>
       </c>
       <c r="B932" s="7" t="s">
-        <v>2362</v>
+        <v>2360</v>
       </c>
       <c r="C932" s="12" t="s">
         <v>1720</v>
@@ -43398,7 +43433,7 @@
         <v>1853</v>
       </c>
       <c r="B933" s="7" t="s">
-        <v>2360</v>
+        <v>2358</v>
       </c>
       <c r="C933" s="12" t="s">
         <v>1720</v>
@@ -43434,7 +43469,7 @@
         <v>1531</v>
       </c>
       <c r="B934" s="7" t="s">
-        <v>2361</v>
+        <v>2359</v>
       </c>
       <c r="C934" s="12" t="s">
         <v>1720</v>
@@ -43470,7 +43505,7 @@
         <v>1854</v>
       </c>
       <c r="B935" s="7" t="s">
-        <v>2363</v>
+        <v>2361</v>
       </c>
       <c r="C935" s="12" t="s">
         <v>1720</v>
@@ -43506,7 +43541,7 @@
         <v>1855</v>
       </c>
       <c r="B936" s="7" t="s">
-        <v>2364</v>
+        <v>2362</v>
       </c>
       <c r="C936" s="12" t="s">
         <v>1720</v>
@@ -43542,7 +43577,7 @@
         <v>1532</v>
       </c>
       <c r="B937" s="7" t="s">
-        <v>2365</v>
+        <v>2363</v>
       </c>
       <c r="C937" s="12" t="s">
         <v>1720</v>
@@ -50019,7 +50054,7 @@
         <v>2133</v>
       </c>
     </row>
-    <row r="1111" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1111" s="7" t="s">
         <v>2082</v>
       </c>
@@ -53578,10 +53613,10 @@
     </row>
     <row r="1205" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1205" s="7" t="s">
-        <v>2379</v>
+        <v>2377</v>
       </c>
       <c r="B1205" s="7" t="s">
-        <v>2380</v>
+        <v>2378</v>
       </c>
       <c r="C1205" s="12" t="s">
         <v>193</v>
@@ -53658,12 +53693,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1207" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1207" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1207" s="7" t="s">
         <v>2354</v>
       </c>
       <c r="B1207" s="7" t="s">
-        <v>2359</v>
+        <v>2357</v>
       </c>
       <c r="C1207" s="12" t="s">
         <v>180</v>
@@ -53699,12 +53734,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1208" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1208" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1208" s="7" t="s">
-        <v>2357</v>
+        <v>2414</v>
       </c>
       <c r="B1208" s="7" t="s">
-        <v>2358</v>
+        <v>2404</v>
       </c>
       <c r="C1208" s="12" t="s">
         <v>180</v>
@@ -53722,7 +53757,7 @@
       </c>
       <c r="I1208" s="19" t="str">
         <f t="shared" si="121"/>
-        <v>bugs_pi_dom01_BCG_att456t</v>
+        <v>bugs_pi_dom01_BCG_att456m6t</v>
       </c>
       <c r="J1208" s="7">
         <f t="shared" si="125"/>
@@ -53742,10 +53777,10 @@
     </row>
     <row r="1209" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1209" s="7" t="s">
-        <v>2367</v>
+        <v>2365</v>
       </c>
       <c r="B1209" s="7" t="s">
-        <v>2370</v>
+        <v>2368</v>
       </c>
       <c r="C1209" s="12" t="s">
         <v>229</v>
@@ -53767,7 +53802,7 @@
         <v>unclassified_bugs</v>
       </c>
       <c r="L1209" s="1" t="s">
-        <v>2374</v>
+        <v>2372</v>
       </c>
       <c r="M1209" s="7"/>
       <c r="N1209" s="1" t="b">
@@ -53776,10 +53811,10 @@
     </row>
     <row r="1210" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1210" s="7" t="s">
-        <v>2368</v>
+        <v>2366</v>
       </c>
       <c r="B1210" s="7" t="s">
-        <v>2371</v>
+        <v>2369</v>
       </c>
       <c r="C1210" s="12" t="s">
         <v>229</v>
@@ -53801,7 +53836,7 @@
         <v>unclassified_bugs</v>
       </c>
       <c r="L1210" s="1" t="s">
-        <v>2374</v>
+        <v>2372</v>
       </c>
       <c r="M1210" s="7"/>
       <c r="N1210" s="1" t="b">
@@ -53813,10 +53848,10 @@
         <v>403</v>
       </c>
       <c r="B1211" s="7" t="s">
-        <v>2369</v>
+        <v>2367</v>
       </c>
       <c r="C1211" s="12" t="s">
-        <v>2378</v>
+        <v>2376</v>
       </c>
       <c r="D1211" s="12"/>
       <c r="E1211" s="12"/>
@@ -53835,7 +53870,7 @@
         <v>unclassified_bugs</v>
       </c>
       <c r="L1211" s="1" t="s">
-        <v>2374</v>
+        <v>2372</v>
       </c>
       <c r="M1211" s="7"/>
       <c r="N1211" s="1" t="b">
@@ -53844,13 +53879,13 @@
     </row>
     <row r="1212" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1212" s="7" t="s">
-        <v>2372</v>
+        <v>2370</v>
       </c>
       <c r="B1212" s="7" t="s">
-        <v>2373</v>
+        <v>2371</v>
       </c>
       <c r="C1212" s="12" t="s">
-        <v>2377</v>
+        <v>2375</v>
       </c>
       <c r="D1212" s="12"/>
       <c r="E1212" s="12" t="s">
@@ -53880,10 +53915,10 @@
     </row>
     <row r="1213" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1213" s="7" t="s">
-        <v>2381</v>
+        <v>2379</v>
       </c>
       <c r="B1213" s="7" t="s">
-        <v>2375</v>
+        <v>2373</v>
       </c>
       <c r="C1213" s="16" t="s">
         <v>2322</v>
@@ -53921,10 +53956,10 @@
     </row>
     <row r="1214" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1214" s="7" t="s">
-        <v>2384</v>
+        <v>2382</v>
       </c>
       <c r="B1214" s="7" t="s">
-        <v>2385</v>
+        <v>2383</v>
       </c>
       <c r="C1214" s="12" t="s">
         <v>181</v>
@@ -53957,10 +53992,10 @@
     </row>
     <row r="1215" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1215" s="7" t="s">
-        <v>2386</v>
+        <v>2384</v>
       </c>
       <c r="B1215" s="7" t="s">
-        <v>2387</v>
+        <v>2385</v>
       </c>
       <c r="C1215" s="12" t="s">
         <v>181</v>
@@ -53993,10 +54028,10 @@
     </row>
     <row r="1216" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1216" s="7" t="s">
-        <v>2388</v>
+        <v>2386</v>
       </c>
       <c r="B1216" s="7" t="s">
-        <v>2389</v>
+        <v>2387</v>
       </c>
       <c r="C1216" s="12" t="s">
         <v>181</v>
@@ -54029,10 +54064,10 @@
     </row>
     <row r="1217" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1217" s="7" t="s">
-        <v>2390</v>
+        <v>2388</v>
       </c>
       <c r="B1217" s="7" t="s">
-        <v>2391</v>
+        <v>2389</v>
       </c>
       <c r="C1217" s="12" t="s">
         <v>173</v>
@@ -54065,10 +54100,10 @@
     </row>
     <row r="1218" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1218" s="7" t="s">
-        <v>2392</v>
+        <v>2390</v>
       </c>
       <c r="B1218" s="7" t="s">
-        <v>2393</v>
+        <v>2391</v>
       </c>
       <c r="C1218" s="12" t="s">
         <v>173</v>
@@ -54101,10 +54136,10 @@
     </row>
     <row r="1219" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1219" s="7" t="s">
-        <v>2394</v>
+        <v>2392</v>
       </c>
       <c r="B1219" s="7" t="s">
-        <v>2395</v>
+        <v>2393</v>
       </c>
       <c r="C1219" s="12" t="s">
         <v>181</v>
@@ -54137,13 +54172,13 @@
     </row>
     <row r="1220" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1220" s="7" t="s">
+        <v>2394</v>
+      </c>
+      <c r="B1220" s="7" t="s">
+        <v>2395</v>
+      </c>
+      <c r="C1220" s="12" t="s">
         <v>2396</v>
-      </c>
-      <c r="B1220" s="7" t="s">
-        <v>2397</v>
-      </c>
-      <c r="C1220" s="12" t="s">
-        <v>2398</v>
       </c>
       <c r="D1220" s="12"/>
       <c r="E1220" s="12" t="s">
@@ -57269,10 +57304,10 @@
     </row>
     <row r="1307" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1307" s="7" t="s">
-        <v>2402</v>
+        <v>2400</v>
       </c>
       <c r="B1307" s="8" t="s">
-        <v>2403</v>
+        <v>2401</v>
       </c>
       <c r="C1307" s="13" t="s">
         <v>173</v>
@@ -57281,7 +57316,7 @@
       <c r="E1307" s="13"/>
       <c r="F1307" s="13"/>
       <c r="G1307" s="8" t="s">
-        <v>2404</v>
+        <v>2402</v>
       </c>
       <c r="H1307" s="1" t="s">
         <v>652</v>
@@ -57305,10 +57340,10 @@
     </row>
     <row r="1308" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1308" s="7" t="s">
-        <v>2405</v>
+        <v>2415</v>
       </c>
       <c r="B1308" s="7" t="s">
-        <v>2406</v>
+        <v>2416</v>
       </c>
       <c r="C1308" s="12" t="s">
         <v>180</v>
@@ -57344,15 +57379,166 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2023" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2023" s="52"/>
+    <row r="1309" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1309" s="7" t="s">
+        <v>2405</v>
+      </c>
+      <c r="B1309" s="7" t="s">
+        <v>2406</v>
+      </c>
+      <c r="C1309" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1309" s="12"/>
+      <c r="E1309" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1309" s="12"/>
+      <c r="G1309" s="8" t="s">
+        <v>2296</v>
+      </c>
+      <c r="H1309" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="I1309" s="19" t="str">
+        <f t="shared" ref="I1309:I1312" si="137">H1309&amp;"_"&amp;TRIM(A1309)</f>
+        <v>bugs_pi_dom02_BCG_att456m6t</v>
+      </c>
+      <c r="J1309" s="7">
+        <f t="shared" ref="J1309" si="138">COUNTIF($I$6:$I$1194,I1309)</f>
+        <v>0</v>
+      </c>
+      <c r="K1309" s="1" t="str">
+        <f t="shared" ref="K1309" si="139">"unclassified_"&amp;H1309</f>
+        <v>unclassified_bugs</v>
+      </c>
+      <c r="L1309" s="1" t="s">
+        <v>2355</v>
+      </c>
+      <c r="M1309" s="7"/>
+      <c r="N1309" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A1310" s="7" t="s">
+        <v>2407</v>
+      </c>
+      <c r="B1310" s="8" t="s">
+        <v>2410</v>
+      </c>
+      <c r="C1310" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="D1310" s="55"/>
+      <c r="E1310" s="13"/>
+      <c r="F1310" s="13"/>
+      <c r="G1310" s="8"/>
+      <c r="H1310" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="I1310" s="19" t="str">
+        <f t="shared" si="137"/>
+        <v>bugs_nt_NonInsTrombJuga_BCG_att456m6t</v>
+      </c>
+      <c r="J1310" s="7">
+        <f t="shared" ref="J1310:J1312" si="140">COUNTIF($I$6:$I$1123,I1310)</f>
+        <v>0</v>
+      </c>
+      <c r="K1310" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="L1310" s="1" t="s">
+        <v>1583</v>
+      </c>
+      <c r="M1310" s="1"/>
+      <c r="N1310" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A1311" s="7" t="s">
+        <v>2408</v>
+      </c>
+      <c r="B1311" s="8" t="s">
+        <v>2411</v>
+      </c>
+      <c r="C1311" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="D1311" s="55"/>
+      <c r="E1311" s="13"/>
+      <c r="F1311" s="13"/>
+      <c r="G1311" s="8"/>
+      <c r="H1311" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="I1311" s="19" t="str">
+        <f t="shared" si="137"/>
+        <v>bugs_pi_NonInsTrombJuga_BCG_att456m6t</v>
+      </c>
+      <c r="J1311" s="7">
+        <f t="shared" si="140"/>
+        <v>0</v>
+      </c>
+      <c r="K1311" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="L1311" s="1" t="s">
+        <v>1583</v>
+      </c>
+      <c r="M1311" s="1"/>
+      <c r="N1311" s="7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A1312" s="7" t="s">
+        <v>2409</v>
+      </c>
+      <c r="B1312" s="8" t="s">
+        <v>2412</v>
+      </c>
+      <c r="C1312" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="D1312" s="55"/>
+      <c r="E1312" s="13"/>
+      <c r="F1312" s="13"/>
+      <c r="G1312" s="8"/>
+      <c r="H1312" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="I1312" s="19" t="str">
+        <f t="shared" si="137"/>
+        <v>bugs_pt_NonInsTrombJuga_BCG_att456m6t</v>
+      </c>
+      <c r="J1312" s="7">
+        <f t="shared" si="140"/>
+        <v>0</v>
+      </c>
+      <c r="K1312" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="L1312" s="1" t="s">
+        <v>1583</v>
+      </c>
+      <c r="M1312" s="1"/>
+      <c r="N1312" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2022" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2022" s="52"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:N1307" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A5:N1312" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="pi_dom01_BCG_att456"/>
-        <filter val="pi_dom01_BCG_att456t"/>
+        <filter val="pi_dom02"/>
+        <filter val="pi_dom02_BCG_att456_NoJugaRiss"/>
+        <filter val="pi_dom02_BCG_att456m6t"/>
+        <filter val="pi_dom02_ExclSchool"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/inst/extdata/MetricNames.xlsx
+++ b/inst/extdata/MetricNames.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erik.Leppo\Documents\GitHub\BioMonTools\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60AC92FC-BD7C-452F-B745-96222E0A8224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19B26921-F316-4FC3-9257-869224B43F71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="MetricMetadata" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">MetricMetadata!$A$5:$N$1312</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">MetricMetadata!$A$5:$N$1313</definedName>
     <definedName name="FileName" localSheetId="0">NOTES!$B$8</definedName>
     <definedName name="FileName">#REF!</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">MetricMetadata!$A:$A,MetricMetadata!$5:$5</definedName>
@@ -225,7 +225,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1211" authorId="1" shapeId="0" xr:uid="{EE6C7705-7E87-436A-AE80-A5FABC228A99}">
+    <comment ref="B1212" authorId="1" shapeId="0" xr:uid="{EE6C7705-7E87-436A-AE80-A5FABC228A99}">
       <text>
         <r>
           <rPr>
@@ -249,7 +249,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1211" authorId="1" shapeId="0" xr:uid="{905B8F54-2067-4968-9CE3-86EB0853D83A}">
+    <comment ref="C1212" authorId="1" shapeId="0" xr:uid="{905B8F54-2067-4968-9CE3-86EB0853D83A}">
       <text>
         <r>
           <rPr>
@@ -273,7 +273,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1212" authorId="1" shapeId="0" xr:uid="{C301695B-A8C0-41F3-B34F-89A2B62122FA}">
+    <comment ref="B1213" authorId="1" shapeId="0" xr:uid="{C301695B-A8C0-41F3-B34F-89A2B62122FA}">
       <text>
         <r>
           <rPr>
@@ -302,7 +302,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8688" uniqueCount="2417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8703" uniqueCount="2422">
   <si>
     <t>nt_total</t>
   </si>
@@ -7553,6 +7553,21 @@
   </si>
   <si>
     <t>percent individuals, dominant 2, BCG attributes 4, 5, or 6</t>
+  </si>
+  <si>
+    <t>pi_dom01_BCG_att456t</t>
+  </si>
+  <si>
+    <t>percent individuals, dominant 1, BCG attributes 4, 5, or 6t</t>
+  </si>
+  <si>
+    <t>Add back pi_dom01_BCG_att456t and pi_dom02_BCG_att456t</t>
+  </si>
+  <si>
+    <t>pi_dom02_BCG_att456t</t>
+  </si>
+  <si>
+    <t>percent individuals, dominant 2, BCG attributes 4, 5, or 6t</t>
   </si>
 </sst>
 </file>
@@ -8338,7 +8353,7 @@
   <sheetPr>
     <tabColor theme="1" tint="0.499984740745262"/>
   </sheetPr>
-  <dimension ref="A1:N120"/>
+  <dimension ref="A1:N121"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -8384,8 +8399,8 @@
         <v>1832</v>
       </c>
       <c r="J6" s="42">
-        <f>COUNTA(MetricMetadata!$H$6:$H$2022)</f>
-        <v>1307</v>
+        <f>COUNTA(MetricMetadata!$H$6:$H$2023)</f>
+        <v>1309</v>
       </c>
       <c r="M6" t="s">
         <v>2012</v>
@@ -8406,8 +8421,8 @@
         <v>652</v>
       </c>
       <c r="H7">
-        <f>COUNTIF(MetricMetadata!$H$6:$H$2022,G7)</f>
-        <v>569</v>
+        <f>COUNTIF(MetricMetadata!$H$6:$H$2023,G7)</f>
+        <v>571</v>
       </c>
       <c r="M7" t="s">
         <v>2014</v>
@@ -8428,7 +8443,7 @@
         <v>391</v>
       </c>
       <c r="H8">
-        <f>COUNTIF(MetricMetadata!$H$6:$H$2022,G8)</f>
+        <f>COUNTIF(MetricMetadata!$H$6:$H$2023,G8)</f>
         <v>380</v>
       </c>
       <c r="M8" t="s">
@@ -8450,7 +8465,7 @@
         <v>799</v>
       </c>
       <c r="H9">
-        <f>COUNTIF(MetricMetadata!$H$6:$H$2022,G9)</f>
+        <f>COUNTIF(MetricMetadata!$H$6:$H$2023,G9)</f>
         <v>339</v>
       </c>
       <c r="M9" t="s">
@@ -8465,7 +8480,7 @@
         <v>1955</v>
       </c>
       <c r="H10">
-        <f>COUNTIF(MetricMetadata!$H$6:$H$2022,G10)</f>
+        <f>COUNTIF(MetricMetadata!$H$6:$H$2023,G10)</f>
         <v>16</v>
       </c>
       <c r="M10" t="s">
@@ -8483,7 +8498,7 @@
         <v>390</v>
       </c>
       <c r="H11">
-        <f>COUNTIF(MetricMetadata!$H$6:$H$2022,G11)</f>
+        <f>COUNTIF(MetricMetadata!$H$6:$H$2023,G11)</f>
         <v>3</v>
       </c>
       <c r="M11" t="s">
@@ -8498,7 +8513,7 @@
         <v>208</v>
       </c>
       <c r="H12">
-        <f>COUNTIF(MetricMetadata!$H$6:$H$2022,G12)</f>
+        <f>COUNTIF(MetricMetadata!$H$6:$H$2023,G12)</f>
         <v>0</v>
       </c>
       <c r="I12" s="40" t="s">
@@ -8519,7 +8534,7 @@
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="H14" s="41">
         <f>SUM(H7:H11)</f>
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="I14" t="s">
         <v>1998</v>
@@ -9351,6 +9366,14 @@
       </c>
       <c r="B120" t="s">
         <v>2413</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="24">
+        <v>46210</v>
+      </c>
+      <c r="B121" t="s">
+        <v>2419</v>
       </c>
     </row>
   </sheetData>
@@ -9394,7 +9417,7 @@
   <sheetPr codeName="Sheet3" filterMode="1">
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
-  <dimension ref="A1:N2022"/>
+  <dimension ref="A1:N2023"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38.7109375" style="4" bestFit="1" customWidth="1"/>
@@ -9455,8 +9478,8 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
-        <f>SUBTOTAL(3,A6:A2106)</f>
-        <v>6</v>
+        <f>SUBTOTAL(3,A6:A2107)</f>
+        <v>4</v>
       </c>
       <c r="B3" s="4">
         <f>COUNTIF($B$6:$B$1001,B2)</f>
@@ -15674,7 +15697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="7" t="s">
         <v>137</v>
       </c>
@@ -20594,7 +20617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="7" t="s">
         <v>145</v>
       </c>
@@ -40503,7 +40526,7 @@
         <v>2133</v>
       </c>
     </row>
-    <row r="852" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A852" s="7" t="s">
         <v>145</v>
       </c>
@@ -50054,7 +50077,7 @@
         <v>2133</v>
       </c>
     </row>
-    <row r="1111" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1111" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1111" s="7" t="s">
         <v>2082</v>
       </c>
@@ -53217,7 +53240,7 @@
         <v>391</v>
       </c>
       <c r="I1195" s="19" t="str">
-        <f t="shared" ref="I1195:I1211" si="121">H1195&amp;"_"&amp;TRIM(A1195)</f>
+        <f t="shared" ref="I1195:I1212" si="121">H1195&amp;"_"&amp;TRIM(A1195)</f>
         <v>fish_n_ac_Cott</v>
       </c>
       <c r="J1195" s="7">
@@ -53514,11 +53537,11 @@
         <v>fish_x_Obs_CatoRhin</v>
       </c>
       <c r="J1202" s="7">
-        <f t="shared" ref="J1202:J1208" si="125">COUNTIF($I$6:$I$1194,I1202)</f>
+        <f t="shared" ref="J1202:J1209" si="125">COUNTIF($I$6:$I$1194,I1202)</f>
         <v>0</v>
       </c>
       <c r="K1202" s="1" t="str">
-        <f t="shared" ref="K1202:K1265" si="126">"unclassified_"&amp;H1202</f>
+        <f t="shared" ref="K1202:K1266" si="126">"unclassified_"&amp;H1202</f>
         <v>unclassified_fish</v>
       </c>
       <c r="L1202" s="1" t="s">
@@ -53693,7 +53716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1207" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1207" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1207" s="7" t="s">
         <v>2354</v>
       </c>
@@ -53734,12 +53757,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1208" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1208" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1208" s="7" t="s">
-        <v>2414</v>
+        <v>2417</v>
       </c>
       <c r="B1208" s="7" t="s">
-        <v>2404</v>
+        <v>2418</v>
       </c>
       <c r="C1208" s="12" t="s">
         <v>180</v>
@@ -53756,15 +53779,15 @@
         <v>652</v>
       </c>
       <c r="I1208" s="19" t="str">
-        <f t="shared" si="121"/>
-        <v>bugs_pi_dom01_BCG_att456m6t</v>
+        <f t="shared" ref="I1208" si="130">H1208&amp;"_"&amp;TRIM(A1208)</f>
+        <v>bugs_pi_dom01_BCG_att456t</v>
       </c>
       <c r="J1208" s="7">
-        <f t="shared" si="125"/>
+        <f t="shared" ref="J1208" si="131">COUNTIF($I$6:$I$1194,I1208)</f>
         <v>0</v>
       </c>
       <c r="K1208" s="1" t="str">
-        <f t="shared" si="126"/>
+        <f t="shared" ref="K1208" si="132">"unclassified_"&amp;H1208</f>
         <v>unclassified_bugs</v>
       </c>
       <c r="L1208" s="1" t="s">
@@ -53775,34 +53798,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1209" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1209" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1209" s="7" t="s">
-        <v>2365</v>
+        <v>2414</v>
       </c>
       <c r="B1209" s="7" t="s">
-        <v>2368</v>
+        <v>2404</v>
       </c>
       <c r="C1209" s="12" t="s">
-        <v>229</v>
+        <v>180</v>
       </c>
       <c r="D1209" s="12"/>
-      <c r="E1209" s="12"/>
+      <c r="E1209" s="12" t="s">
+        <v>1960</v>
+      </c>
       <c r="F1209" s="12"/>
-      <c r="G1209" s="8"/>
+      <c r="G1209" s="8" t="s">
+        <v>2329</v>
+      </c>
       <c r="H1209" s="7" t="s">
         <v>652</v>
       </c>
       <c r="I1209" s="19" t="str">
         <f t="shared" si="121"/>
-        <v>bugs_nt_ffg2_deepdep</v>
-      </c>
-      <c r="J1209" s="7"/>
+        <v>bugs_pi_dom01_BCG_att456m6t</v>
+      </c>
+      <c r="J1209" s="7">
+        <f t="shared" si="125"/>
+        <v>0</v>
+      </c>
       <c r="K1209" s="1" t="str">
         <f t="shared" si="126"/>
         <v>unclassified_bugs</v>
       </c>
       <c r="L1209" s="1" t="s">
-        <v>2372</v>
+        <v>2355</v>
       </c>
       <c r="M1209" s="7"/>
       <c r="N1209" s="1" t="b">
@@ -53811,10 +53841,10 @@
     </row>
     <row r="1210" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1210" s="7" t="s">
-        <v>2366</v>
+        <v>2365</v>
       </c>
       <c r="B1210" s="7" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="C1210" s="12" t="s">
         <v>229</v>
@@ -53828,7 +53858,7 @@
       </c>
       <c r="I1210" s="19" t="str">
         <f t="shared" si="121"/>
-        <v>bugs_pi_ffg2_deepdep</v>
+        <v>bugs_nt_ffg2_deepdep</v>
       </c>
       <c r="J1210" s="7"/>
       <c r="K1210" s="1" t="str">
@@ -53845,13 +53875,13 @@
     </row>
     <row r="1211" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1211" s="7" t="s">
-        <v>403</v>
+        <v>2366</v>
       </c>
       <c r="B1211" s="7" t="s">
-        <v>2367</v>
+        <v>2369</v>
       </c>
       <c r="C1211" s="12" t="s">
-        <v>2376</v>
+        <v>229</v>
       </c>
       <c r="D1211" s="12"/>
       <c r="E1211" s="12"/>
@@ -53862,7 +53892,7 @@
       </c>
       <c r="I1211" s="19" t="str">
         <f t="shared" si="121"/>
-        <v>bugs_ni_m2</v>
+        <v>bugs_pi_ffg2_deepdep</v>
       </c>
       <c r="J1211" s="7"/>
       <c r="K1211" s="1" t="str">
@@ -53879,26 +53909,24 @@
     </row>
     <row r="1212" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1212" s="7" t="s">
-        <v>2370</v>
+        <v>403</v>
       </c>
       <c r="B1212" s="7" t="s">
-        <v>2371</v>
+        <v>2367</v>
       </c>
       <c r="C1212" s="12" t="s">
-        <v>2375</v>
+        <v>2376</v>
       </c>
       <c r="D1212" s="12"/>
-      <c r="E1212" s="12" t="s">
-        <v>1960</v>
-      </c>
+      <c r="E1212" s="12"/>
       <c r="F1212" s="12"/>
       <c r="G1212" s="8"/>
       <c r="H1212" s="7" t="s">
         <v>652</v>
       </c>
       <c r="I1212" s="19" t="str">
-        <f t="shared" ref="I1212:I1275" si="130">H1212&amp;"_"&amp;TRIM(A1212)</f>
-        <v>bugs_sum_density_m2</v>
+        <f t="shared" si="121"/>
+        <v>bugs_ni_m2</v>
       </c>
       <c r="J1212" s="7"/>
       <c r="K1212" s="1" t="str">
@@ -53906,7 +53934,7 @@
         <v>unclassified_bugs</v>
       </c>
       <c r="L1212" s="1" t="s">
-        <v>2355</v>
+        <v>2372</v>
       </c>
       <c r="M1212" s="7"/>
       <c r="N1212" s="1" t="b">
@@ -53915,87 +53943,87 @@
     </row>
     <row r="1213" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1213" s="7" t="s">
-        <v>2379</v>
+        <v>2370</v>
       </c>
       <c r="B1213" s="7" t="s">
-        <v>2373</v>
-      </c>
-      <c r="C1213" s="16" t="s">
-        <v>2322</v>
-      </c>
-      <c r="D1213" s="55"/>
+        <v>2371</v>
+      </c>
+      <c r="C1213" s="12" t="s">
+        <v>2375</v>
+      </c>
+      <c r="D1213" s="12"/>
       <c r="E1213" s="12" t="s">
         <v>1960</v>
       </c>
       <c r="F1213" s="12"/>
-      <c r="G1213" s="8" t="s">
-        <v>2329</v>
-      </c>
-      <c r="H1213" s="1" t="s">
-        <v>391</v>
+      <c r="G1213" s="8"/>
+      <c r="H1213" s="7" t="s">
+        <v>652</v>
       </c>
       <c r="I1213" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>fish_n_ac_mwf</v>
-      </c>
-      <c r="J1213" s="7">
-        <f t="shared" ref="J1213" si="131">COUNTIF($I$6:$I$1123,I1213)</f>
-        <v>0</v>
-      </c>
+        <f t="shared" ref="I1213:I1276" si="133">H1213&amp;"_"&amp;TRIM(A1213)</f>
+        <v>bugs_sum_density_m2</v>
+      </c>
+      <c r="J1213" s="7"/>
       <c r="K1213" s="1" t="str">
         <f t="shared" si="126"/>
-        <v>unclassified_fish</v>
+        <v>unclassified_bugs</v>
       </c>
       <c r="L1213" s="1" t="s">
-        <v>1577</v>
-      </c>
-      <c r="M1213" s="1"/>
-      <c r="N1213" s="1" t="s">
-        <v>2133</v>
+        <v>2355</v>
+      </c>
+      <c r="M1213" s="7"/>
+      <c r="N1213" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="1214" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1214" s="7" t="s">
-        <v>2382</v>
+        <v>2379</v>
       </c>
       <c r="B1214" s="7" t="s">
-        <v>2383</v>
-      </c>
-      <c r="C1214" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="D1214" s="12"/>
+        <v>2373</v>
+      </c>
+      <c r="C1214" s="16" t="s">
+        <v>2322</v>
+      </c>
+      <c r="D1214" s="55"/>
       <c r="E1214" s="12" t="s">
         <v>1960</v>
       </c>
       <c r="F1214" s="12"/>
-      <c r="G1214" s="8"/>
-      <c r="H1214" s="7" t="s">
-        <v>652</v>
+      <c r="G1214" s="8" t="s">
+        <v>2329</v>
+      </c>
+      <c r="H1214" s="1" t="s">
+        <v>391</v>
       </c>
       <c r="I1214" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>bugs_nt_EPT_BCG_att1i2</v>
-      </c>
-      <c r="J1214" s="7"/>
+        <f t="shared" si="133"/>
+        <v>fish_n_ac_mwf</v>
+      </c>
+      <c r="J1214" s="7">
+        <f t="shared" ref="J1214" si="134">COUNTIF($I$6:$I$1123,I1214)</f>
+        <v>0</v>
+      </c>
       <c r="K1214" s="1" t="str">
         <f t="shared" si="126"/>
-        <v>unclassified_bugs</v>
+        <v>unclassified_fish</v>
       </c>
       <c r="L1214" s="1" t="s">
-        <v>1565</v>
-      </c>
-      <c r="M1214" s="7"/>
-      <c r="N1214" s="1" t="b">
-        <v>0</v>
+        <v>1577</v>
+      </c>
+      <c r="M1214" s="1"/>
+      <c r="N1214" s="1" t="s">
+        <v>2133</v>
       </c>
     </row>
     <row r="1215" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1215" s="7" t="s">
-        <v>2384</v>
+        <v>2382</v>
       </c>
       <c r="B1215" s="7" t="s">
-        <v>2385</v>
+        <v>2383</v>
       </c>
       <c r="C1215" s="12" t="s">
         <v>181</v>
@@ -54010,8 +54038,8 @@
         <v>652</v>
       </c>
       <c r="I1215" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>bugs_pt_EPT_BCG_att1i2</v>
+        <f t="shared" si="133"/>
+        <v>bugs_nt_EPT_BCG_att1i2</v>
       </c>
       <c r="J1215" s="7"/>
       <c r="K1215" s="1" t="str">
@@ -54028,10 +54056,10 @@
     </row>
     <row r="1216" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1216" s="7" t="s">
-        <v>2386</v>
+        <v>2384</v>
       </c>
       <c r="B1216" s="7" t="s">
-        <v>2387</v>
+        <v>2385</v>
       </c>
       <c r="C1216" s="12" t="s">
         <v>181</v>
@@ -54046,8 +54074,8 @@
         <v>652</v>
       </c>
       <c r="I1216" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>bugs_pi_EPT_BCG_att1i2</v>
+        <f t="shared" si="133"/>
+        <v>bugs_pt_EPT_BCG_att1i2</v>
       </c>
       <c r="J1216" s="7"/>
       <c r="K1216" s="1" t="str">
@@ -54064,13 +54092,13 @@
     </row>
     <row r="1217" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1217" s="7" t="s">
-        <v>2388</v>
+        <v>2386</v>
       </c>
       <c r="B1217" s="7" t="s">
-        <v>2389</v>
+        <v>2387</v>
       </c>
       <c r="C1217" s="12" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="D1217" s="12"/>
       <c r="E1217" s="12" t="s">
@@ -54082,8 +54110,8 @@
         <v>652</v>
       </c>
       <c r="I1217" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>bugs_nord_COEPT</v>
+        <f t="shared" si="133"/>
+        <v>bugs_pi_EPT_BCG_att1i2</v>
       </c>
       <c r="J1217" s="7"/>
       <c r="K1217" s="1" t="str">
@@ -54100,10 +54128,10 @@
     </row>
     <row r="1218" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1218" s="7" t="s">
-        <v>2390</v>
+        <v>2388</v>
       </c>
       <c r="B1218" s="7" t="s">
-        <v>2391</v>
+        <v>2389</v>
       </c>
       <c r="C1218" s="12" t="s">
         <v>173</v>
@@ -54118,8 +54146,8 @@
         <v>652</v>
       </c>
       <c r="I1218" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>bugs_nt_COEPT</v>
+        <f t="shared" si="133"/>
+        <v>bugs_nord_COEPT</v>
       </c>
       <c r="J1218" s="7"/>
       <c r="K1218" s="1" t="str">
@@ -54136,13 +54164,13 @@
     </row>
     <row r="1219" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1219" s="7" t="s">
-        <v>2392</v>
+        <v>2390</v>
       </c>
       <c r="B1219" s="7" t="s">
-        <v>2393</v>
+        <v>2391</v>
       </c>
       <c r="C1219" s="12" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="D1219" s="12"/>
       <c r="E1219" s="12" t="s">
@@ -54154,8 +54182,8 @@
         <v>652</v>
       </c>
       <c r="I1219" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>bugs_pi_COEPT_BCG_att1i234b4m</v>
+        <f t="shared" si="133"/>
+        <v>bugs_nt_COEPT</v>
       </c>
       <c r="J1219" s="7"/>
       <c r="K1219" s="1" t="str">
@@ -54172,13 +54200,13 @@
     </row>
     <row r="1220" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1220" s="7" t="s">
-        <v>2394</v>
+        <v>2392</v>
       </c>
       <c r="B1220" s="7" t="s">
-        <v>2395</v>
+        <v>2393</v>
       </c>
       <c r="C1220" s="12" t="s">
-        <v>2396</v>
+        <v>181</v>
       </c>
       <c r="D1220" s="12"/>
       <c r="E1220" s="12" t="s">
@@ -54190,8 +54218,8 @@
         <v>652</v>
       </c>
       <c r="I1220" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>bugs_nt_EPT_volt_semi</v>
+        <f t="shared" si="133"/>
+        <v>bugs_pi_COEPT_BCG_att1i234b4m</v>
       </c>
       <c r="J1220" s="7"/>
       <c r="K1220" s="1" t="str">
@@ -54208,13 +54236,13 @@
     </row>
     <row r="1221" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1221" s="7" t="s">
-        <v>635</v>
+        <v>2394</v>
       </c>
       <c r="B1221" s="7" t="s">
-        <v>636</v>
+        <v>2395</v>
       </c>
       <c r="C1221" s="12" t="s">
-        <v>180</v>
+        <v>2396</v>
       </c>
       <c r="D1221" s="12"/>
       <c r="E1221" s="12" t="s">
@@ -54223,16 +54251,16 @@
       <c r="F1221" s="12"/>
       <c r="G1221" s="8"/>
       <c r="H1221" s="7" t="s">
-        <v>799</v>
+        <v>652</v>
       </c>
       <c r="I1221" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_nt_BCG_att1</v>
+        <f t="shared" si="133"/>
+        <v>bugs_nt_EPT_volt_semi</v>
       </c>
       <c r="J1221" s="7"/>
       <c r="K1221" s="1" t="str">
         <f t="shared" si="126"/>
-        <v>unclassified_algae</v>
+        <v>unclassified_bugs</v>
       </c>
       <c r="L1221" s="1" t="s">
         <v>1565</v>
@@ -54244,10 +54272,10 @@
     </row>
     <row r="1222" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1222" s="7" t="s">
-        <v>154</v>
+        <v>635</v>
       </c>
       <c r="B1222" s="7" t="s">
-        <v>1690</v>
+        <v>636</v>
       </c>
       <c r="C1222" s="12" t="s">
         <v>180</v>
@@ -54262,8 +54290,8 @@
         <v>799</v>
       </c>
       <c r="I1222" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_nt_BCG_att1i</v>
+        <f t="shared" si="133"/>
+        <v>algae_nt_BCG_att1</v>
       </c>
       <c r="J1222" s="7"/>
       <c r="K1222" s="1" t="str">
@@ -54280,10 +54308,10 @@
     </row>
     <row r="1223" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1223" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B1223" s="7" t="s">
-        <v>1694</v>
+        <v>1690</v>
       </c>
       <c r="C1223" s="12" t="s">
         <v>180</v>
@@ -54298,8 +54326,8 @@
         <v>799</v>
       </c>
       <c r="I1223" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_nt_BCG_att1m</v>
+        <f t="shared" si="133"/>
+        <v>algae_nt_BCG_att1i</v>
       </c>
       <c r="J1223" s="7"/>
       <c r="K1223" s="1" t="str">
@@ -54316,10 +54344,10 @@
     </row>
     <row r="1224" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1224" s="7" t="s">
-        <v>93</v>
+        <v>155</v>
       </c>
       <c r="B1224" s="7" t="s">
-        <v>573</v>
+        <v>1694</v>
       </c>
       <c r="C1224" s="12" t="s">
         <v>180</v>
@@ -54334,8 +54362,8 @@
         <v>799</v>
       </c>
       <c r="I1224" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_nt_BCG_att12</v>
+        <f t="shared" si="133"/>
+        <v>algae_nt_BCG_att1m</v>
       </c>
       <c r="J1224" s="7"/>
       <c r="K1224" s="1" t="str">
@@ -54352,10 +54380,10 @@
     </row>
     <row r="1225" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1225" s="7" t="s">
-        <v>1838</v>
+        <v>93</v>
       </c>
       <c r="B1225" s="7" t="s">
-        <v>1839</v>
+        <v>573</v>
       </c>
       <c r="C1225" s="12" t="s">
         <v>180</v>
@@ -54370,8 +54398,8 @@
         <v>799</v>
       </c>
       <c r="I1225" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_nt_BCG_att1234</v>
+        <f t="shared" si="133"/>
+        <v>algae_nt_BCG_att12</v>
       </c>
       <c r="J1225" s="7"/>
       <c r="K1225" s="1" t="str">
@@ -54388,10 +54416,10 @@
     </row>
     <row r="1226" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1226" s="7" t="s">
-        <v>94</v>
+        <v>1838</v>
       </c>
       <c r="B1226" s="7" t="s">
-        <v>574</v>
+        <v>1839</v>
       </c>
       <c r="C1226" s="12" t="s">
         <v>180</v>
@@ -54406,8 +54434,8 @@
         <v>799</v>
       </c>
       <c r="I1226" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_nt_BCG_att1i2</v>
+        <f t="shared" si="133"/>
+        <v>algae_nt_BCG_att1234</v>
       </c>
       <c r="J1226" s="7"/>
       <c r="K1226" s="1" t="str">
@@ -54424,10 +54452,10 @@
     </row>
     <row r="1227" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1227" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B1227" s="7" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C1227" s="12" t="s">
         <v>180</v>
@@ -54442,8 +54470,8 @@
         <v>799</v>
       </c>
       <c r="I1227" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_nt_BCG_att123</v>
+        <f t="shared" si="133"/>
+        <v>algae_nt_BCG_att1i2</v>
       </c>
       <c r="J1227" s="7"/>
       <c r="K1227" s="1" t="str">
@@ -54460,10 +54488,10 @@
     </row>
     <row r="1228" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1228" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B1228" s="7" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C1228" s="12" t="s">
         <v>180</v>
@@ -54478,8 +54506,8 @@
         <v>799</v>
       </c>
       <c r="I1228" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_nt_BCG_att1i23</v>
+        <f t="shared" si="133"/>
+        <v>algae_nt_BCG_att123</v>
       </c>
       <c r="J1228" s="7"/>
       <c r="K1228" s="1" t="str">
@@ -54496,10 +54524,10 @@
     </row>
     <row r="1229" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1229" s="7" t="s">
-        <v>1696</v>
+        <v>96</v>
       </c>
       <c r="B1229" s="7" t="s">
-        <v>1722</v>
+        <v>576</v>
       </c>
       <c r="C1229" s="12" t="s">
         <v>180</v>
@@ -54514,8 +54542,8 @@
         <v>799</v>
       </c>
       <c r="I1229" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_nt_BCG_att1i236i</v>
+        <f t="shared" si="133"/>
+        <v>algae_nt_BCG_att1i23</v>
       </c>
       <c r="J1229" s="7"/>
       <c r="K1229" s="1" t="str">
@@ -54532,10 +54560,10 @@
     </row>
     <row r="1230" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1230" s="7" t="s">
-        <v>97</v>
+        <v>1696</v>
       </c>
       <c r="B1230" s="7" t="s">
-        <v>577</v>
+        <v>1722</v>
       </c>
       <c r="C1230" s="12" t="s">
         <v>180</v>
@@ -54550,8 +54578,8 @@
         <v>799</v>
       </c>
       <c r="I1230" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_nt_BCG_att2</v>
+        <f t="shared" si="133"/>
+        <v>algae_nt_BCG_att1i236i</v>
       </c>
       <c r="J1230" s="7"/>
       <c r="K1230" s="1" t="str">
@@ -54568,10 +54596,10 @@
     </row>
     <row r="1231" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1231" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B1231" s="7" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C1231" s="12" t="s">
         <v>180</v>
@@ -54586,8 +54614,8 @@
         <v>799</v>
       </c>
       <c r="I1231" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_nt_BCG_att23</v>
+        <f t="shared" si="133"/>
+        <v>algae_nt_BCG_att2</v>
       </c>
       <c r="J1231" s="7"/>
       <c r="K1231" s="1" t="str">
@@ -54604,10 +54632,10 @@
     </row>
     <row r="1232" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1232" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B1232" s="7" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C1232" s="12" t="s">
         <v>180</v>
@@ -54622,8 +54650,8 @@
         <v>799</v>
       </c>
       <c r="I1232" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_nt_BCG_att234</v>
+        <f t="shared" si="133"/>
+        <v>algae_nt_BCG_att23</v>
       </c>
       <c r="J1232" s="7"/>
       <c r="K1232" s="1" t="str">
@@ -54640,10 +54668,10 @@
     </row>
     <row r="1233" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1233" s="7" t="s">
-        <v>156</v>
+        <v>99</v>
       </c>
       <c r="B1233" s="7" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C1233" s="12" t="s">
         <v>180</v>
@@ -54658,8 +54686,8 @@
         <v>799</v>
       </c>
       <c r="I1233" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_nt_BCG_att3</v>
+        <f t="shared" si="133"/>
+        <v>algae_nt_BCG_att234</v>
       </c>
       <c r="J1233" s="7"/>
       <c r="K1233" s="1" t="str">
@@ -54676,10 +54704,10 @@
     </row>
     <row r="1234" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1234" s="7" t="s">
-        <v>100</v>
+        <v>156</v>
       </c>
       <c r="B1234" s="7" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C1234" s="12" t="s">
         <v>180</v>
@@ -54694,8 +54722,8 @@
         <v>799</v>
       </c>
       <c r="I1234" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_nt_BCG_att4</v>
+        <f t="shared" si="133"/>
+        <v>algae_nt_BCG_att3</v>
       </c>
       <c r="J1234" s="7"/>
       <c r="K1234" s="1" t="str">
@@ -54712,10 +54740,10 @@
     </row>
     <row r="1235" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1235" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B1235" s="7" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C1235" s="12" t="s">
         <v>180</v>
@@ -54730,8 +54758,8 @@
         <v>799</v>
       </c>
       <c r="I1235" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_nt_BCG_att45</v>
+        <f t="shared" si="133"/>
+        <v>algae_nt_BCG_att4</v>
       </c>
       <c r="J1235" s="7"/>
       <c r="K1235" s="1" t="str">
@@ -54748,10 +54776,10 @@
     </row>
     <row r="1236" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1236" s="7" t="s">
-        <v>1372</v>
+        <v>101</v>
       </c>
       <c r="B1236" s="7" t="s">
-        <v>1377</v>
+        <v>582</v>
       </c>
       <c r="C1236" s="12" t="s">
         <v>180</v>
@@ -54766,8 +54794,8 @@
         <v>799</v>
       </c>
       <c r="I1236" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_nt_BCG_att456</v>
+        <f t="shared" si="133"/>
+        <v>algae_nt_BCG_att45</v>
       </c>
       <c r="J1236" s="7"/>
       <c r="K1236" s="1" t="str">
@@ -54784,10 +54812,10 @@
     </row>
     <row r="1237" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1237" s="7" t="s">
-        <v>102</v>
+        <v>1372</v>
       </c>
       <c r="B1237" s="7" t="s">
-        <v>583</v>
+        <v>1377</v>
       </c>
       <c r="C1237" s="12" t="s">
         <v>180</v>
@@ -54802,8 +54830,8 @@
         <v>799</v>
       </c>
       <c r="I1237" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_nt_BCG_att5</v>
+        <f t="shared" si="133"/>
+        <v>algae_nt_BCG_att456</v>
       </c>
       <c r="J1237" s="7"/>
       <c r="K1237" s="1" t="str">
@@ -54820,10 +54848,10 @@
     </row>
     <row r="1238" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1238" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B1238" s="7" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C1238" s="12" t="s">
         <v>180</v>
@@ -54838,8 +54866,8 @@
         <v>799</v>
       </c>
       <c r="I1238" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_nt_BCG_att56</v>
+        <f t="shared" si="133"/>
+        <v>algae_nt_BCG_att5</v>
       </c>
       <c r="J1238" s="7"/>
       <c r="K1238" s="1" t="str">
@@ -54856,10 +54884,10 @@
     </row>
     <row r="1239" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1239" s="7" t="s">
-        <v>1697</v>
+        <v>103</v>
       </c>
       <c r="B1239" s="7" t="s">
-        <v>1723</v>
+        <v>584</v>
       </c>
       <c r="C1239" s="12" t="s">
         <v>180</v>
@@ -54874,8 +54902,8 @@
         <v>799</v>
       </c>
       <c r="I1239" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_nt_BCG_att56t</v>
+        <f t="shared" si="133"/>
+        <v>algae_nt_BCG_att56</v>
       </c>
       <c r="J1239" s="7"/>
       <c r="K1239" s="1" t="str">
@@ -54892,10 +54920,10 @@
     </row>
     <row r="1240" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1240" s="7" t="s">
-        <v>104</v>
+        <v>1697</v>
       </c>
       <c r="B1240" s="7" t="s">
-        <v>585</v>
+        <v>1723</v>
       </c>
       <c r="C1240" s="12" t="s">
         <v>180</v>
@@ -54910,8 +54938,8 @@
         <v>799</v>
       </c>
       <c r="I1240" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_nt_BCG_att6</v>
+        <f t="shared" si="133"/>
+        <v>algae_nt_BCG_att56t</v>
       </c>
       <c r="J1240" s="7"/>
       <c r="K1240" s="1" t="str">
@@ -54928,10 +54956,10 @@
     </row>
     <row r="1241" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1241" s="7" t="s">
-        <v>1698</v>
+        <v>104</v>
       </c>
       <c r="B1241" s="7" t="s">
-        <v>1724</v>
+        <v>585</v>
       </c>
       <c r="C1241" s="12" t="s">
         <v>180</v>
@@ -54946,8 +54974,8 @@
         <v>799</v>
       </c>
       <c r="I1241" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_nt_BCG_att6i</v>
+        <f t="shared" si="133"/>
+        <v>algae_nt_BCG_att6</v>
       </c>
       <c r="J1241" s="7"/>
       <c r="K1241" s="1" t="str">
@@ -54964,10 +54992,10 @@
     </row>
     <row r="1242" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1242" s="7" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="B1242" s="7" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="C1242" s="12" t="s">
         <v>180</v>
@@ -54982,8 +55010,8 @@
         <v>799</v>
       </c>
       <c r="I1242" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_nt_BCG_att6m</v>
+        <f t="shared" si="133"/>
+        <v>algae_nt_BCG_att6i</v>
       </c>
       <c r="J1242" s="7"/>
       <c r="K1242" s="1" t="str">
@@ -55000,10 +55028,10 @@
     </row>
     <row r="1243" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1243" s="7" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="B1243" s="7" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="C1243" s="12" t="s">
         <v>180</v>
@@ -55018,8 +55046,8 @@
         <v>799</v>
       </c>
       <c r="I1243" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_nt_BCG_att6t</v>
+        <f t="shared" si="133"/>
+        <v>algae_nt_BCG_att6m</v>
       </c>
       <c r="J1243" s="7"/>
       <c r="K1243" s="1" t="str">
@@ -55036,10 +55064,10 @@
     </row>
     <row r="1244" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1244" s="7" t="s">
-        <v>418</v>
+        <v>1700</v>
       </c>
       <c r="B1244" s="7" t="s">
-        <v>586</v>
+        <v>1726</v>
       </c>
       <c r="C1244" s="12" t="s">
         <v>180</v>
@@ -55054,8 +55082,8 @@
         <v>799</v>
       </c>
       <c r="I1244" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_nt_BCG_attNA</v>
+        <f t="shared" si="133"/>
+        <v>algae_nt_BCG_att6t</v>
       </c>
       <c r="J1244" s="7"/>
       <c r="K1244" s="1" t="str">
@@ -55072,13 +55100,13 @@
     </row>
     <row r="1245" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1245" s="7" t="s">
-        <v>1786</v>
+        <v>418</v>
       </c>
       <c r="B1245" s="7" t="s">
-        <v>1788</v>
+        <v>586</v>
       </c>
       <c r="C1245" s="12" t="s">
-        <v>1806</v>
+        <v>180</v>
       </c>
       <c r="D1245" s="12"/>
       <c r="E1245" s="12" t="s">
@@ -55090,8 +55118,8 @@
         <v>799</v>
       </c>
       <c r="I1245" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_nt_BCG_att4b</v>
+        <f t="shared" si="133"/>
+        <v>algae_nt_BCG_attNA</v>
       </c>
       <c r="J1245" s="7"/>
       <c r="K1245" s="1" t="str">
@@ -55108,10 +55136,10 @@
     </row>
     <row r="1246" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1246" s="7" t="s">
-        <v>1802</v>
+        <v>1786</v>
       </c>
       <c r="B1246" s="7" t="s">
-        <v>1808</v>
+        <v>1788</v>
       </c>
       <c r="C1246" s="12" t="s">
         <v>1806</v>
@@ -55126,8 +55154,8 @@
         <v>799</v>
       </c>
       <c r="I1246" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_nt_BCG_att4m</v>
+        <f t="shared" si="133"/>
+        <v>algae_nt_BCG_att4b</v>
       </c>
       <c r="J1246" s="7"/>
       <c r="K1246" s="1" t="str">
@@ -55144,10 +55172,10 @@
     </row>
     <row r="1247" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1247" s="7" t="s">
-        <v>1787</v>
+        <v>1802</v>
       </c>
       <c r="B1247" s="7" t="s">
-        <v>1789</v>
+        <v>1808</v>
       </c>
       <c r="C1247" s="12" t="s">
         <v>1806</v>
@@ -55162,8 +55190,8 @@
         <v>799</v>
       </c>
       <c r="I1247" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_nt_BCG_att4w</v>
+        <f t="shared" si="133"/>
+        <v>algae_nt_BCG_att4m</v>
       </c>
       <c r="J1247" s="7"/>
       <c r="K1247" s="1" t="str">
@@ -55180,13 +55208,13 @@
     </row>
     <row r="1248" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1248" s="7" t="s">
-        <v>1813</v>
+        <v>1787</v>
       </c>
       <c r="B1248" s="7" t="s">
-        <v>1810</v>
+        <v>1789</v>
       </c>
       <c r="C1248" s="12" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="D1248" s="12"/>
       <c r="E1248" s="12" t="s">
@@ -55198,8 +55226,8 @@
         <v>799</v>
       </c>
       <c r="I1248" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_nt_BCG_att1i234b</v>
+        <f t="shared" si="133"/>
+        <v>algae_nt_BCG_att4w</v>
       </c>
       <c r="J1248" s="7"/>
       <c r="K1248" s="1" t="str">
@@ -55216,10 +55244,10 @@
     </row>
     <row r="1249" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1249" s="7" t="s">
-        <v>1816</v>
+        <v>1813</v>
       </c>
       <c r="B1249" s="7" t="s">
-        <v>1821</v>
+        <v>1810</v>
       </c>
       <c r="C1249" s="12" t="s">
         <v>1807</v>
@@ -55234,8 +55262,8 @@
         <v>799</v>
       </c>
       <c r="I1249" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_nt_BCG_att4w5</v>
+        <f t="shared" si="133"/>
+        <v>algae_nt_BCG_att1i234b</v>
       </c>
       <c r="J1249" s="7"/>
       <c r="K1249" s="1" t="str">
@@ -55252,13 +55280,13 @@
     </row>
     <row r="1250" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1250" s="7" t="s">
-        <v>634</v>
+        <v>1816</v>
       </c>
       <c r="B1250" s="7" t="s">
-        <v>633</v>
+        <v>1821</v>
       </c>
       <c r="C1250" s="12" t="s">
-        <v>180</v>
+        <v>1807</v>
       </c>
       <c r="D1250" s="12"/>
       <c r="E1250" s="12" t="s">
@@ -55270,8 +55298,8 @@
         <v>799</v>
       </c>
       <c r="I1250" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_pi_BCG_att1</v>
+        <f t="shared" si="133"/>
+        <v>algae_nt_BCG_att4w5</v>
       </c>
       <c r="J1250" s="7"/>
       <c r="K1250" s="1" t="str">
@@ -55288,10 +55316,10 @@
     </row>
     <row r="1251" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1251" s="7" t="s">
-        <v>157</v>
+        <v>634</v>
       </c>
       <c r="B1251" s="7" t="s">
-        <v>1692</v>
+        <v>633</v>
       </c>
       <c r="C1251" s="12" t="s">
         <v>180</v>
@@ -55306,8 +55334,8 @@
         <v>799</v>
       </c>
       <c r="I1251" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_pi_BCG_att1i</v>
+        <f t="shared" si="133"/>
+        <v>algae_pi_BCG_att1</v>
       </c>
       <c r="J1251" s="7"/>
       <c r="K1251" s="1" t="str">
@@ -55324,10 +55352,10 @@
     </row>
     <row r="1252" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1252" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B1252" s="7" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="C1252" s="12" t="s">
         <v>180</v>
@@ -55342,8 +55370,8 @@
         <v>799</v>
       </c>
       <c r="I1252" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_pi_BCG_att1m</v>
+        <f t="shared" si="133"/>
+        <v>algae_pi_BCG_att1i</v>
       </c>
       <c r="J1252" s="7"/>
       <c r="K1252" s="1" t="str">
@@ -55360,10 +55388,10 @@
     </row>
     <row r="1253" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1253" s="7" t="s">
-        <v>107</v>
+        <v>158</v>
       </c>
       <c r="B1253" s="7" t="s">
-        <v>338</v>
+        <v>1691</v>
       </c>
       <c r="C1253" s="12" t="s">
         <v>180</v>
@@ -55378,8 +55406,8 @@
         <v>799</v>
       </c>
       <c r="I1253" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_pi_BCG_att12</v>
+        <f t="shared" si="133"/>
+        <v>algae_pi_BCG_att1m</v>
       </c>
       <c r="J1253" s="7"/>
       <c r="K1253" s="1" t="str">
@@ -55396,10 +55424,10 @@
     </row>
     <row r="1254" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1254" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B1254" s="7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C1254" s="12" t="s">
         <v>180</v>
@@ -55414,8 +55442,8 @@
         <v>799</v>
       </c>
       <c r="I1254" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_pi_BCG_att1i2</v>
+        <f t="shared" si="133"/>
+        <v>algae_pi_BCG_att12</v>
       </c>
       <c r="J1254" s="7"/>
       <c r="K1254" s="1" t="str">
@@ -55432,10 +55460,10 @@
     </row>
     <row r="1255" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1255" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B1255" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C1255" s="12" t="s">
         <v>180</v>
@@ -55450,8 +55478,8 @@
         <v>799</v>
       </c>
       <c r="I1255" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_pi_BCG_att123</v>
+        <f t="shared" si="133"/>
+        <v>algae_pi_BCG_att1i2</v>
       </c>
       <c r="J1255" s="7"/>
       <c r="K1255" s="1" t="str">
@@ -55468,10 +55496,10 @@
     </row>
     <row r="1256" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1256" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B1256" s="7" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C1256" s="12" t="s">
         <v>180</v>
@@ -55486,8 +55514,8 @@
         <v>799</v>
       </c>
       <c r="I1256" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_pi_BCG_att1i23</v>
+        <f t="shared" si="133"/>
+        <v>algae_pi_BCG_att123</v>
       </c>
       <c r="J1256" s="7"/>
       <c r="K1256" s="1" t="str">
@@ -55504,10 +55532,10 @@
     </row>
     <row r="1257" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1257" s="7" t="s">
-        <v>1701</v>
+        <v>110</v>
       </c>
       <c r="B1257" s="7" t="s">
-        <v>1727</v>
+        <v>341</v>
       </c>
       <c r="C1257" s="12" t="s">
         <v>180</v>
@@ -55522,8 +55550,8 @@
         <v>799</v>
       </c>
       <c r="I1257" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_pi_BCG_att1i236i</v>
+        <f t="shared" si="133"/>
+        <v>algae_pi_BCG_att1i23</v>
       </c>
       <c r="J1257" s="7"/>
       <c r="K1257" s="1" t="str">
@@ -55540,10 +55568,10 @@
     </row>
     <row r="1258" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1258" s="7" t="s">
-        <v>159</v>
+        <v>1701</v>
       </c>
       <c r="B1258" s="7" t="s">
-        <v>342</v>
+        <v>1727</v>
       </c>
       <c r="C1258" s="12" t="s">
         <v>180</v>
@@ -55558,8 +55586,8 @@
         <v>799</v>
       </c>
       <c r="I1258" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_pi_BCG_att2</v>
+        <f t="shared" si="133"/>
+        <v>algae_pi_BCG_att1i236i</v>
       </c>
       <c r="J1258" s="7"/>
       <c r="K1258" s="1" t="str">
@@ -55576,10 +55604,10 @@
     </row>
     <row r="1259" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1259" s="7" t="s">
-        <v>111</v>
+        <v>159</v>
       </c>
       <c r="B1259" s="7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C1259" s="12" t="s">
         <v>180</v>
@@ -55594,8 +55622,8 @@
         <v>799</v>
       </c>
       <c r="I1259" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_pi_BCG_att23</v>
+        <f t="shared" si="133"/>
+        <v>algae_pi_BCG_att2</v>
       </c>
       <c r="J1259" s="7"/>
       <c r="K1259" s="1" t="str">
@@ -55612,10 +55640,10 @@
     </row>
     <row r="1260" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1260" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B1260" s="7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C1260" s="12" t="s">
         <v>180</v>
@@ -55630,8 +55658,8 @@
         <v>799</v>
       </c>
       <c r="I1260" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_pi_BCG_att234</v>
+        <f t="shared" si="133"/>
+        <v>algae_pi_BCG_att23</v>
       </c>
       <c r="J1260" s="7"/>
       <c r="K1260" s="1" t="str">
@@ -55648,10 +55676,10 @@
     </row>
     <row r="1261" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1261" s="7" t="s">
-        <v>160</v>
+        <v>112</v>
       </c>
       <c r="B1261" s="7" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C1261" s="12" t="s">
         <v>180</v>
@@ -55666,8 +55694,8 @@
         <v>799</v>
       </c>
       <c r="I1261" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_pi_BCG_att3</v>
+        <f t="shared" si="133"/>
+        <v>algae_pi_BCG_att234</v>
       </c>
       <c r="J1261" s="7"/>
       <c r="K1261" s="1" t="str">
@@ -55684,10 +55712,10 @@
     </row>
     <row r="1262" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1262" s="7" t="s">
-        <v>113</v>
+        <v>160</v>
       </c>
       <c r="B1262" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C1262" s="12" t="s">
         <v>180</v>
@@ -55702,8 +55730,8 @@
         <v>799</v>
       </c>
       <c r="I1262" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_pi_BCG_att4</v>
+        <f t="shared" si="133"/>
+        <v>algae_pi_BCG_att3</v>
       </c>
       <c r="J1262" s="7"/>
       <c r="K1262" s="1" t="str">
@@ -55720,10 +55748,10 @@
     </row>
     <row r="1263" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1263" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B1263" s="7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C1263" s="12" t="s">
         <v>180</v>
@@ -55738,8 +55766,8 @@
         <v>799</v>
       </c>
       <c r="I1263" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_pi_BCG_att45</v>
+        <f t="shared" si="133"/>
+        <v>algae_pi_BCG_att4</v>
       </c>
       <c r="J1263" s="7"/>
       <c r="K1263" s="1" t="str">
@@ -55756,10 +55784,10 @@
     </row>
     <row r="1264" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1264" s="7" t="s">
-        <v>1373</v>
+        <v>114</v>
       </c>
       <c r="B1264" s="7" t="s">
-        <v>1376</v>
+        <v>347</v>
       </c>
       <c r="C1264" s="12" t="s">
         <v>180</v>
@@ -55774,8 +55802,8 @@
         <v>799</v>
       </c>
       <c r="I1264" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_pi_BCG_att456</v>
+        <f t="shared" si="133"/>
+        <v>algae_pi_BCG_att45</v>
       </c>
       <c r="J1264" s="7"/>
       <c r="K1264" s="1" t="str">
@@ -55792,10 +55820,10 @@
     </row>
     <row r="1265" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1265" s="7" t="s">
-        <v>115</v>
+        <v>1373</v>
       </c>
       <c r="B1265" s="7" t="s">
-        <v>348</v>
+        <v>1376</v>
       </c>
       <c r="C1265" s="12" t="s">
         <v>180</v>
@@ -55810,8 +55838,8 @@
         <v>799</v>
       </c>
       <c r="I1265" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_pi_BCG_att5</v>
+        <f t="shared" si="133"/>
+        <v>algae_pi_BCG_att456</v>
       </c>
       <c r="J1265" s="7"/>
       <c r="K1265" s="1" t="str">
@@ -55828,10 +55856,10 @@
     </row>
     <row r="1266" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1266" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B1266" s="7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C1266" s="12" t="s">
         <v>180</v>
@@ -55846,12 +55874,12 @@
         <v>799</v>
       </c>
       <c r="I1266" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_pi_BCG_att56</v>
+        <f t="shared" si="133"/>
+        <v>algae_pi_BCG_att5</v>
       </c>
       <c r="J1266" s="7"/>
       <c r="K1266" s="1" t="str">
-        <f t="shared" ref="K1266:K1306" si="132">"unclassified_"&amp;H1266</f>
+        <f t="shared" si="126"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1266" s="1" t="s">
@@ -55864,10 +55892,10 @@
     </row>
     <row r="1267" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1267" s="7" t="s">
-        <v>1702</v>
+        <v>116</v>
       </c>
       <c r="B1267" s="7" t="s">
-        <v>1719</v>
+        <v>349</v>
       </c>
       <c r="C1267" s="12" t="s">
         <v>180</v>
@@ -55882,12 +55910,12 @@
         <v>799</v>
       </c>
       <c r="I1267" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_pi_BCG_att56t</v>
+        <f t="shared" si="133"/>
+        <v>algae_pi_BCG_att56</v>
       </c>
       <c r="J1267" s="7"/>
       <c r="K1267" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" ref="K1267:K1307" si="135">"unclassified_"&amp;H1267</f>
         <v>unclassified_algae</v>
       </c>
       <c r="L1267" s="1" t="s">
@@ -55900,10 +55928,10 @@
     </row>
     <row r="1268" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1268" s="7" t="s">
-        <v>117</v>
+        <v>1702</v>
       </c>
       <c r="B1268" s="7" t="s">
-        <v>350</v>
+        <v>1719</v>
       </c>
       <c r="C1268" s="12" t="s">
         <v>180</v>
@@ -55918,12 +55946,12 @@
         <v>799</v>
       </c>
       <c r="I1268" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_pi_BCG_att6</v>
+        <f t="shared" si="133"/>
+        <v>algae_pi_BCG_att56t</v>
       </c>
       <c r="J1268" s="7"/>
       <c r="K1268" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1268" s="1" t="s">
@@ -55936,10 +55964,10 @@
     </row>
     <row r="1269" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1269" s="7" t="s">
-        <v>1703</v>
+        <v>117</v>
       </c>
       <c r="B1269" s="7" t="s">
-        <v>1718</v>
+        <v>350</v>
       </c>
       <c r="C1269" s="12" t="s">
         <v>180</v>
@@ -55954,12 +55982,12 @@
         <v>799</v>
       </c>
       <c r="I1269" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_pi_BCG_att6i</v>
+        <f t="shared" si="133"/>
+        <v>algae_pi_BCG_att6</v>
       </c>
       <c r="J1269" s="7"/>
       <c r="K1269" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1269" s="1" t="s">
@@ -55972,10 +56000,10 @@
     </row>
     <row r="1270" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1270" s="7" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="B1270" s="7" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="C1270" s="12" t="s">
         <v>180</v>
@@ -55990,12 +56018,12 @@
         <v>799</v>
       </c>
       <c r="I1270" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_pi_BCG_att6m</v>
+        <f t="shared" si="133"/>
+        <v>algae_pi_BCG_att6i</v>
       </c>
       <c r="J1270" s="7"/>
       <c r="K1270" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1270" s="1" t="s">
@@ -56008,10 +56036,10 @@
     </row>
     <row r="1271" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1271" s="7" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="B1271" s="7" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="C1271" s="12" t="s">
         <v>180</v>
@@ -56026,12 +56054,12 @@
         <v>799</v>
       </c>
       <c r="I1271" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_pi_BCG_att6t</v>
+        <f t="shared" si="133"/>
+        <v>algae_pi_BCG_att6m</v>
       </c>
       <c r="J1271" s="7"/>
       <c r="K1271" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1271" s="1" t="s">
@@ -56044,10 +56072,10 @@
     </row>
     <row r="1272" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1272" s="7" t="s">
-        <v>417</v>
+        <v>1705</v>
       </c>
       <c r="B1272" s="7" t="s">
-        <v>416</v>
+        <v>1716</v>
       </c>
       <c r="C1272" s="12" t="s">
         <v>180</v>
@@ -56062,12 +56090,12 @@
         <v>799</v>
       </c>
       <c r="I1272" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_pi_BCG_attNA</v>
+        <f t="shared" si="133"/>
+        <v>algae_pi_BCG_att6t</v>
       </c>
       <c r="J1272" s="7"/>
       <c r="K1272" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1272" s="1" t="s">
@@ -56080,13 +56108,13 @@
     </row>
     <row r="1273" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1273" s="7" t="s">
-        <v>1780</v>
+        <v>417</v>
       </c>
       <c r="B1273" s="7" t="s">
-        <v>1782</v>
+        <v>416</v>
       </c>
       <c r="C1273" s="12" t="s">
-        <v>1806</v>
+        <v>180</v>
       </c>
       <c r="D1273" s="12"/>
       <c r="E1273" s="12" t="s">
@@ -56098,12 +56126,12 @@
         <v>799</v>
       </c>
       <c r="I1273" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_pi_BCG_att4b</v>
+        <f t="shared" si="133"/>
+        <v>algae_pi_BCG_attNA</v>
       </c>
       <c r="J1273" s="7"/>
       <c r="K1273" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1273" s="1" t="s">
@@ -56116,10 +56144,10 @@
     </row>
     <row r="1274" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1274" s="7" t="s">
-        <v>1803</v>
+        <v>1780</v>
       </c>
       <c r="B1274" s="7" t="s">
-        <v>1809</v>
+        <v>1782</v>
       </c>
       <c r="C1274" s="12" t="s">
         <v>1806</v>
@@ -56134,12 +56162,12 @@
         <v>799</v>
       </c>
       <c r="I1274" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_pi_BCG_att4m</v>
+        <f t="shared" si="133"/>
+        <v>algae_pi_BCG_att4b</v>
       </c>
       <c r="J1274" s="7"/>
       <c r="K1274" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1274" s="1" t="s">
@@ -56152,10 +56180,10 @@
     </row>
     <row r="1275" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1275" s="7" t="s">
-        <v>1781</v>
+        <v>1803</v>
       </c>
       <c r="B1275" s="7" t="s">
-        <v>1783</v>
+        <v>1809</v>
       </c>
       <c r="C1275" s="12" t="s">
         <v>1806</v>
@@ -56170,12 +56198,12 @@
         <v>799</v>
       </c>
       <c r="I1275" s="19" t="str">
-        <f t="shared" si="130"/>
-        <v>algae_pi_BCG_att4w</v>
+        <f t="shared" si="133"/>
+        <v>algae_pi_BCG_att4m</v>
       </c>
       <c r="J1275" s="7"/>
       <c r="K1275" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1275" s="1" t="s">
@@ -56188,13 +56216,13 @@
     </row>
     <row r="1276" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1276" s="7" t="s">
-        <v>1814</v>
+        <v>1781</v>
       </c>
       <c r="B1276" s="7" t="s">
-        <v>1811</v>
+        <v>1783</v>
       </c>
       <c r="C1276" s="12" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="D1276" s="12"/>
       <c r="E1276" s="12" t="s">
@@ -56206,12 +56234,12 @@
         <v>799</v>
       </c>
       <c r="I1276" s="19" t="str">
-        <f t="shared" ref="I1276:I1306" si="133">H1276&amp;"_"&amp;TRIM(A1276)</f>
-        <v>algae_pi_BCG_att1i234b</v>
+        <f t="shared" si="133"/>
+        <v>algae_pi_BCG_att4w</v>
       </c>
       <c r="J1276" s="7"/>
       <c r="K1276" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1276" s="1" t="s">
@@ -56224,10 +56252,10 @@
     </row>
     <row r="1277" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1277" s="7" t="s">
-        <v>1817</v>
+        <v>1814</v>
       </c>
       <c r="B1277" s="7" t="s">
-        <v>1820</v>
+        <v>1811</v>
       </c>
       <c r="C1277" s="12" t="s">
         <v>1807</v>
@@ -56242,12 +56270,12 @@
         <v>799</v>
       </c>
       <c r="I1277" s="19" t="str">
-        <f t="shared" si="133"/>
-        <v>algae_pi_BCG_att4w5</v>
+        <f t="shared" ref="I1277:I1307" si="136">H1277&amp;"_"&amp;TRIM(A1277)</f>
+        <v>algae_pi_BCG_att1i234b</v>
       </c>
       <c r="J1277" s="7"/>
       <c r="K1277" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1277" s="1" t="s">
@@ -56260,13 +56288,13 @@
     </row>
     <row r="1278" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1278" s="7" t="s">
-        <v>631</v>
+        <v>1817</v>
       </c>
       <c r="B1278" s="7" t="s">
-        <v>632</v>
+        <v>1820</v>
       </c>
       <c r="C1278" s="12" t="s">
-        <v>180</v>
+        <v>1807</v>
       </c>
       <c r="D1278" s="12"/>
       <c r="E1278" s="12" t="s">
@@ -56278,12 +56306,12 @@
         <v>799</v>
       </c>
       <c r="I1278" s="19" t="str">
-        <f t="shared" si="133"/>
-        <v>algae_pt_BCG_att1</v>
+        <f t="shared" si="136"/>
+        <v>algae_pi_BCG_att4w5</v>
       </c>
       <c r="J1278" s="7"/>
       <c r="K1278" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1278" s="1" t="s">
@@ -56296,10 +56324,10 @@
     </row>
     <row r="1279" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1279" s="7" t="s">
-        <v>161</v>
+        <v>631</v>
       </c>
       <c r="B1279" s="7" t="s">
-        <v>1693</v>
+        <v>632</v>
       </c>
       <c r="C1279" s="12" t="s">
         <v>180</v>
@@ -56314,12 +56342,12 @@
         <v>799</v>
       </c>
       <c r="I1279" s="19" t="str">
-        <f t="shared" si="133"/>
-        <v>algae_pt_BCG_att1i</v>
+        <f t="shared" si="136"/>
+        <v>algae_pt_BCG_att1</v>
       </c>
       <c r="J1279" s="7"/>
       <c r="K1279" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1279" s="1" t="s">
@@ -56332,10 +56360,10 @@
     </row>
     <row r="1280" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1280" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B1280" s="7" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="C1280" s="12" t="s">
         <v>180</v>
@@ -56350,12 +56378,12 @@
         <v>799</v>
       </c>
       <c r="I1280" s="19" t="str">
-        <f t="shared" si="133"/>
-        <v>algae_pt_BCG_att1m</v>
+        <f t="shared" si="136"/>
+        <v>algae_pt_BCG_att1i</v>
       </c>
       <c r="J1280" s="7"/>
       <c r="K1280" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1280" s="1" t="s">
@@ -56368,10 +56396,10 @@
     </row>
     <row r="1281" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1281" s="7" t="s">
-        <v>119</v>
+        <v>162</v>
       </c>
       <c r="B1281" s="7" t="s">
-        <v>352</v>
+        <v>1695</v>
       </c>
       <c r="C1281" s="12" t="s">
         <v>180</v>
@@ -56386,12 +56414,12 @@
         <v>799</v>
       </c>
       <c r="I1281" s="19" t="str">
-        <f t="shared" si="133"/>
-        <v>algae_pt_BCG_att12</v>
+        <f t="shared" si="136"/>
+        <v>algae_pt_BCG_att1m</v>
       </c>
       <c r="J1281" s="7"/>
       <c r="K1281" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1281" s="1" t="s">
@@ -56404,10 +56432,10 @@
     </row>
     <row r="1282" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1282" s="7" t="s">
-        <v>1836</v>
+        <v>119</v>
       </c>
       <c r="B1282" s="7" t="s">
-        <v>1837</v>
+        <v>352</v>
       </c>
       <c r="C1282" s="12" t="s">
         <v>180</v>
@@ -56422,12 +56450,12 @@
         <v>799</v>
       </c>
       <c r="I1282" s="19" t="str">
-        <f t="shared" si="133"/>
-        <v>algae_pt_BCG_att1234</v>
+        <f t="shared" si="136"/>
+        <v>algae_pt_BCG_att12</v>
       </c>
       <c r="J1282" s="7"/>
       <c r="K1282" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1282" s="1" t="s">
@@ -56440,10 +56468,10 @@
     </row>
     <row r="1283" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1283" s="7" t="s">
-        <v>120</v>
+        <v>1836</v>
       </c>
       <c r="B1283" s="7" t="s">
-        <v>353</v>
+        <v>1837</v>
       </c>
       <c r="C1283" s="12" t="s">
         <v>180</v>
@@ -56458,12 +56486,12 @@
         <v>799</v>
       </c>
       <c r="I1283" s="19" t="str">
-        <f t="shared" si="133"/>
-        <v>algae_pt_BCG_att1i2</v>
+        <f t="shared" si="136"/>
+        <v>algae_pt_BCG_att1234</v>
       </c>
       <c r="J1283" s="7"/>
       <c r="K1283" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1283" s="1" t="s">
@@ -56476,10 +56504,10 @@
     </row>
     <row r="1284" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1284" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B1284" s="7" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C1284" s="12" t="s">
         <v>180</v>
@@ -56494,12 +56522,12 @@
         <v>799</v>
       </c>
       <c r="I1284" s="19" t="str">
-        <f t="shared" si="133"/>
-        <v>algae_pt_BCG_att123</v>
+        <f t="shared" si="136"/>
+        <v>algae_pt_BCG_att1i2</v>
       </c>
       <c r="J1284" s="7"/>
       <c r="K1284" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1284" s="1" t="s">
@@ -56512,10 +56540,10 @@
     </row>
     <row r="1285" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1285" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B1285" s="7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C1285" s="12" t="s">
         <v>180</v>
@@ -56530,12 +56558,12 @@
         <v>799</v>
       </c>
       <c r="I1285" s="19" t="str">
-        <f t="shared" si="133"/>
-        <v>algae_pt_BCG_att1i23</v>
+        <f t="shared" si="136"/>
+        <v>algae_pt_BCG_att123</v>
       </c>
       <c r="J1285" s="7"/>
       <c r="K1285" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1285" s="1" t="s">
@@ -56548,10 +56576,10 @@
     </row>
     <row r="1286" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1286" s="7" t="s">
-        <v>1706</v>
+        <v>122</v>
       </c>
       <c r="B1286" s="7" t="s">
-        <v>1715</v>
+        <v>355</v>
       </c>
       <c r="C1286" s="12" t="s">
         <v>180</v>
@@ -56566,12 +56594,12 @@
         <v>799</v>
       </c>
       <c r="I1286" s="19" t="str">
-        <f t="shared" si="133"/>
-        <v>algae_pt_BCG_att1i236i</v>
+        <f t="shared" si="136"/>
+        <v>algae_pt_BCG_att1i23</v>
       </c>
       <c r="J1286" s="7"/>
       <c r="K1286" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1286" s="1" t="s">
@@ -56584,10 +56612,10 @@
     </row>
     <row r="1287" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1287" s="7" t="s">
-        <v>123</v>
+        <v>1706</v>
       </c>
       <c r="B1287" s="7" t="s">
-        <v>356</v>
+        <v>1715</v>
       </c>
       <c r="C1287" s="12" t="s">
         <v>180</v>
@@ -56602,12 +56630,12 @@
         <v>799</v>
       </c>
       <c r="I1287" s="19" t="str">
-        <f t="shared" si="133"/>
-        <v>algae_pt_BCG_att2</v>
+        <f t="shared" si="136"/>
+        <v>algae_pt_BCG_att1i236i</v>
       </c>
       <c r="J1287" s="7"/>
       <c r="K1287" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1287" s="1" t="s">
@@ -56620,10 +56648,10 @@
     </row>
     <row r="1288" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1288" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B1288" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C1288" s="12" t="s">
         <v>180</v>
@@ -56638,12 +56666,12 @@
         <v>799</v>
       </c>
       <c r="I1288" s="19" t="str">
-        <f t="shared" si="133"/>
-        <v>algae_pt_BCG_att23</v>
+        <f t="shared" si="136"/>
+        <v>algae_pt_BCG_att2</v>
       </c>
       <c r="J1288" s="7"/>
       <c r="K1288" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1288" s="1" t="s">
@@ -56656,10 +56684,10 @@
     </row>
     <row r="1289" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1289" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B1289" s="7" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C1289" s="12" t="s">
         <v>180</v>
@@ -56674,12 +56702,12 @@
         <v>799</v>
       </c>
       <c r="I1289" s="19" t="str">
-        <f t="shared" si="133"/>
-        <v>algae_pt_BCG_att234</v>
+        <f t="shared" si="136"/>
+        <v>algae_pt_BCG_att23</v>
       </c>
       <c r="J1289" s="7"/>
       <c r="K1289" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1289" s="1" t="s">
@@ -56692,10 +56720,10 @@
     </row>
     <row r="1290" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1290" s="7" t="s">
-        <v>163</v>
+        <v>125</v>
       </c>
       <c r="B1290" s="7" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C1290" s="12" t="s">
         <v>180</v>
@@ -56710,12 +56738,12 @@
         <v>799</v>
       </c>
       <c r="I1290" s="19" t="str">
-        <f t="shared" si="133"/>
-        <v>algae_pt_BCG_att3</v>
+        <f t="shared" si="136"/>
+        <v>algae_pt_BCG_att234</v>
       </c>
       <c r="J1290" s="7"/>
       <c r="K1290" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1290" s="1" t="s">
@@ -56728,10 +56756,10 @@
     </row>
     <row r="1291" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1291" s="7" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="B1291" s="7" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C1291" s="12" t="s">
         <v>180</v>
@@ -56746,12 +56774,12 @@
         <v>799</v>
       </c>
       <c r="I1291" s="19" t="str">
-        <f t="shared" si="133"/>
-        <v>algae_pt_BCG_att4</v>
+        <f t="shared" si="136"/>
+        <v>algae_pt_BCG_att3</v>
       </c>
       <c r="J1291" s="7"/>
       <c r="K1291" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1291" s="1" t="s">
@@ -56764,10 +56792,10 @@
     </row>
     <row r="1292" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1292" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B1292" s="7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C1292" s="12" t="s">
         <v>180</v>
@@ -56782,12 +56810,12 @@
         <v>799</v>
       </c>
       <c r="I1292" s="19" t="str">
-        <f t="shared" si="133"/>
-        <v>algae_pt_BCG_att45</v>
+        <f t="shared" si="136"/>
+        <v>algae_pt_BCG_att4</v>
       </c>
       <c r="J1292" s="7"/>
       <c r="K1292" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1292" s="1" t="s">
@@ -56800,10 +56828,10 @@
     </row>
     <row r="1293" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1293" s="7" t="s">
-        <v>1374</v>
+        <v>127</v>
       </c>
       <c r="B1293" s="7" t="s">
-        <v>1375</v>
+        <v>361</v>
       </c>
       <c r="C1293" s="12" t="s">
         <v>180</v>
@@ -56818,12 +56846,12 @@
         <v>799</v>
       </c>
       <c r="I1293" s="19" t="str">
-        <f t="shared" si="133"/>
-        <v>algae_pt_BCG_att456</v>
+        <f t="shared" si="136"/>
+        <v>algae_pt_BCG_att45</v>
       </c>
       <c r="J1293" s="7"/>
       <c r="K1293" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1293" s="1" t="s">
@@ -56836,10 +56864,10 @@
     </row>
     <row r="1294" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1294" s="7" t="s">
-        <v>128</v>
+        <v>1374</v>
       </c>
       <c r="B1294" s="7" t="s">
-        <v>362</v>
+        <v>1375</v>
       </c>
       <c r="C1294" s="12" t="s">
         <v>180</v>
@@ -56854,12 +56882,12 @@
         <v>799</v>
       </c>
       <c r="I1294" s="19" t="str">
-        <f t="shared" si="133"/>
-        <v>algae_pt_BCG_att5</v>
+        <f t="shared" si="136"/>
+        <v>algae_pt_BCG_att456</v>
       </c>
       <c r="J1294" s="7"/>
       <c r="K1294" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1294" s="1" t="s">
@@ -56872,10 +56900,10 @@
     </row>
     <row r="1295" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1295" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B1295" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C1295" s="12" t="s">
         <v>180</v>
@@ -56890,12 +56918,12 @@
         <v>799</v>
       </c>
       <c r="I1295" s="19" t="str">
-        <f t="shared" si="133"/>
-        <v>algae_pt_BCG_att56</v>
+        <f t="shared" si="136"/>
+        <v>algae_pt_BCG_att5</v>
       </c>
       <c r="J1295" s="7"/>
       <c r="K1295" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1295" s="1" t="s">
@@ -56908,10 +56936,10 @@
     </row>
     <row r="1296" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1296" s="7" t="s">
-        <v>1707</v>
+        <v>129</v>
       </c>
       <c r="B1296" s="7" t="s">
-        <v>1714</v>
+        <v>363</v>
       </c>
       <c r="C1296" s="12" t="s">
         <v>180</v>
@@ -56926,12 +56954,12 @@
         <v>799</v>
       </c>
       <c r="I1296" s="19" t="str">
-        <f t="shared" si="133"/>
-        <v>algae_pt_BCG_att56t</v>
+        <f t="shared" si="136"/>
+        <v>algae_pt_BCG_att56</v>
       </c>
       <c r="J1296" s="7"/>
       <c r="K1296" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1296" s="1" t="s">
@@ -56944,10 +56972,10 @@
     </row>
     <row r="1297" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1297" s="7" t="s">
-        <v>130</v>
+        <v>1707</v>
       </c>
       <c r="B1297" s="7" t="s">
-        <v>364</v>
+        <v>1714</v>
       </c>
       <c r="C1297" s="12" t="s">
         <v>180</v>
@@ -56962,12 +56990,12 @@
         <v>799</v>
       </c>
       <c r="I1297" s="19" t="str">
-        <f t="shared" si="133"/>
-        <v>algae_pt_BCG_att6</v>
+        <f t="shared" si="136"/>
+        <v>algae_pt_BCG_att56t</v>
       </c>
       <c r="J1297" s="7"/>
       <c r="K1297" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1297" s="1" t="s">
@@ -56980,10 +57008,10 @@
     </row>
     <row r="1298" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1298" s="7" t="s">
-        <v>1708</v>
+        <v>130</v>
       </c>
       <c r="B1298" s="7" t="s">
-        <v>1711</v>
+        <v>364</v>
       </c>
       <c r="C1298" s="12" t="s">
         <v>180</v>
@@ -56998,12 +57026,12 @@
         <v>799</v>
       </c>
       <c r="I1298" s="19" t="str">
-        <f t="shared" si="133"/>
-        <v>algae_pt_BCG_att6i</v>
+        <f t="shared" si="136"/>
+        <v>algae_pt_BCG_att6</v>
       </c>
       <c r="J1298" s="7"/>
       <c r="K1298" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1298" s="1" t="s">
@@ -57016,10 +57044,10 @@
     </row>
     <row r="1299" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1299" s="7" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="B1299" s="7" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="C1299" s="12" t="s">
         <v>180</v>
@@ -57034,12 +57062,12 @@
         <v>799</v>
       </c>
       <c r="I1299" s="19" t="str">
-        <f t="shared" si="133"/>
-        <v>algae_pt_BCG_att6m</v>
+        <f t="shared" si="136"/>
+        <v>algae_pt_BCG_att6i</v>
       </c>
       <c r="J1299" s="7"/>
       <c r="K1299" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1299" s="1" t="s">
@@ -57052,10 +57080,10 @@
     </row>
     <row r="1300" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1300" s="7" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="B1300" s="7" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="C1300" s="12" t="s">
         <v>180</v>
@@ -57070,12 +57098,12 @@
         <v>799</v>
       </c>
       <c r="I1300" s="19" t="str">
-        <f t="shared" si="133"/>
-        <v>algae_pt_BCG_att6t</v>
+        <f t="shared" si="136"/>
+        <v>algae_pt_BCG_att6m</v>
       </c>
       <c r="J1300" s="7"/>
       <c r="K1300" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1300" s="1" t="s">
@@ -57088,10 +57116,10 @@
     </row>
     <row r="1301" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1301" s="7" t="s">
-        <v>414</v>
+        <v>1710</v>
       </c>
       <c r="B1301" s="7" t="s">
-        <v>415</v>
+        <v>1713</v>
       </c>
       <c r="C1301" s="12" t="s">
         <v>180</v>
@@ -57106,12 +57134,12 @@
         <v>799</v>
       </c>
       <c r="I1301" s="19" t="str">
-        <f t="shared" si="133"/>
-        <v>algae_pt_BCG_attNA</v>
+        <f t="shared" si="136"/>
+        <v>algae_pt_BCG_att6t</v>
       </c>
       <c r="J1301" s="7"/>
       <c r="K1301" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1301" s="1" t="s">
@@ -57124,13 +57152,13 @@
     </row>
     <row r="1302" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1302" s="7" t="s">
-        <v>1778</v>
+        <v>414</v>
       </c>
       <c r="B1302" s="7" t="s">
-        <v>1784</v>
+        <v>415</v>
       </c>
       <c r="C1302" s="12" t="s">
-        <v>1806</v>
+        <v>180</v>
       </c>
       <c r="D1302" s="12"/>
       <c r="E1302" s="12" t="s">
@@ -57142,12 +57170,12 @@
         <v>799</v>
       </c>
       <c r="I1302" s="19" t="str">
-        <f t="shared" si="133"/>
-        <v>algae_pt_BCG_att4b</v>
+        <f t="shared" si="136"/>
+        <v>algae_pt_BCG_attNA</v>
       </c>
       <c r="J1302" s="7"/>
       <c r="K1302" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1302" s="1" t="s">
@@ -57160,10 +57188,10 @@
     </row>
     <row r="1303" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1303" s="7" t="s">
-        <v>1804</v>
+        <v>1778</v>
       </c>
       <c r="B1303" s="7" t="s">
-        <v>1805</v>
+        <v>1784</v>
       </c>
       <c r="C1303" s="12" t="s">
         <v>1806</v>
@@ -57178,12 +57206,12 @@
         <v>799</v>
       </c>
       <c r="I1303" s="19" t="str">
-        <f t="shared" si="133"/>
-        <v>algae_pt_BCG_att4m</v>
+        <f t="shared" si="136"/>
+        <v>algae_pt_BCG_att4b</v>
       </c>
       <c r="J1303" s="7"/>
       <c r="K1303" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1303" s="1" t="s">
@@ -57196,10 +57224,10 @@
     </row>
     <row r="1304" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1304" s="7" t="s">
-        <v>1779</v>
+        <v>1804</v>
       </c>
       <c r="B1304" s="7" t="s">
-        <v>1785</v>
+        <v>1805</v>
       </c>
       <c r="C1304" s="12" t="s">
         <v>1806</v>
@@ -57214,12 +57242,12 @@
         <v>799</v>
       </c>
       <c r="I1304" s="19" t="str">
-        <f t="shared" si="133"/>
-        <v>algae_pt_BCG_att4w</v>
+        <f t="shared" si="136"/>
+        <v>algae_pt_BCG_att4m</v>
       </c>
       <c r="J1304" s="7"/>
       <c r="K1304" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1304" s="1" t="s">
@@ -57232,13 +57260,13 @@
     </row>
     <row r="1305" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1305" s="7" t="s">
-        <v>1815</v>
+        <v>1779</v>
       </c>
       <c r="B1305" s="7" t="s">
-        <v>1812</v>
+        <v>1785</v>
       </c>
       <c r="C1305" s="12" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="D1305" s="12"/>
       <c r="E1305" s="12" t="s">
@@ -57250,12 +57278,12 @@
         <v>799</v>
       </c>
       <c r="I1305" s="19" t="str">
-        <f t="shared" si="133"/>
-        <v>algae_pt_BCG_att1i234b</v>
+        <f t="shared" si="136"/>
+        <v>algae_pt_BCG_att4w</v>
       </c>
       <c r="J1305" s="7"/>
       <c r="K1305" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1305" s="1" t="s">
@@ -57268,10 +57296,10 @@
     </row>
     <row r="1306" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1306" s="7" t="s">
-        <v>1818</v>
+        <v>1815</v>
       </c>
       <c r="B1306" s="7" t="s">
-        <v>1819</v>
+        <v>1812</v>
       </c>
       <c r="C1306" s="12" t="s">
         <v>1807</v>
@@ -57286,12 +57314,12 @@
         <v>799</v>
       </c>
       <c r="I1306" s="19" t="str">
-        <f t="shared" si="133"/>
-        <v>algae_pt_BCG_att4w5</v>
+        <f t="shared" si="136"/>
+        <v>algae_pt_BCG_att1i234b</v>
       </c>
       <c r="J1306" s="7"/>
       <c r="K1306" s="1" t="str">
-        <f t="shared" si="132"/>
+        <f t="shared" si="135"/>
         <v>unclassified_algae</v>
       </c>
       <c r="L1306" s="1" t="s">
@@ -57304,87 +57332,82 @@
     </row>
     <row r="1307" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1307" s="7" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B1307" s="7" t="s">
+        <v>1819</v>
+      </c>
+      <c r="C1307" s="12" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D1307" s="12"/>
+      <c r="E1307" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1307" s="12"/>
+      <c r="G1307" s="8"/>
+      <c r="H1307" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="I1307" s="19" t="str">
+        <f t="shared" si="136"/>
+        <v>algae_pt_BCG_att4w5</v>
+      </c>
+      <c r="J1307" s="7"/>
+      <c r="K1307" s="1" t="str">
+        <f t="shared" si="135"/>
+        <v>unclassified_algae</v>
+      </c>
+      <c r="L1307" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="M1307" s="7"/>
+      <c r="N1307" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A1308" s="7" t="s">
         <v>2400</v>
       </c>
-      <c r="B1307" s="8" t="s">
+      <c r="B1308" s="8" t="s">
         <v>2401</v>
       </c>
-      <c r="C1307" s="13" t="s">
+      <c r="C1308" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="D1307" s="54"/>
-      <c r="E1307" s="13"/>
-      <c r="F1307" s="13"/>
-      <c r="G1307" s="8" t="s">
+      <c r="D1308" s="54"/>
+      <c r="E1308" s="13"/>
+      <c r="F1308" s="13"/>
+      <c r="G1308" s="8" t="s">
         <v>2402</v>
       </c>
-      <c r="H1307" s="1" t="s">
+      <c r="H1308" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="I1307" s="19" t="s">
+      <c r="I1308" s="19" t="s">
         <v>1947</v>
       </c>
-      <c r="J1307" s="7">
-        <v>1</v>
-      </c>
-      <c r="K1307" s="1" t="s">
+      <c r="J1308" s="7">
+        <v>1</v>
+      </c>
+      <c r="K1308" s="1" t="s">
         <v>1667</v>
       </c>
-      <c r="L1307" s="1" t="s">
+      <c r="L1308" s="1" t="s">
         <v>1583</v>
       </c>
-      <c r="M1307" s="1"/>
-      <c r="N1307" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="1308" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1308" s="7" t="s">
+      <c r="M1308" s="1"/>
+      <c r="N1308" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A1309" s="7" t="s">
         <v>2415</v>
       </c>
-      <c r="B1308" s="7" t="s">
+      <c r="B1309" s="7" t="s">
         <v>2416</v>
-      </c>
-      <c r="C1308" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="D1308" s="12"/>
-      <c r="E1308" s="12" t="s">
-        <v>1960</v>
-      </c>
-      <c r="F1308" s="12"/>
-      <c r="G1308" s="8" t="s">
-        <v>2296</v>
-      </c>
-      <c r="H1308" s="7" t="s">
-        <v>652</v>
-      </c>
-      <c r="I1308" s="19" t="str">
-        <f t="shared" ref="I1308" si="134">H1308&amp;"_"&amp;TRIM(A1308)</f>
-        <v>bugs_pi_dom02_BCG_att456</v>
-      </c>
-      <c r="J1308" s="7">
-        <f t="shared" ref="J1308" si="135">COUNTIF($I$6:$I$1194,I1308)</f>
-        <v>0</v>
-      </c>
-      <c r="K1308" s="1" t="str">
-        <f t="shared" ref="K1308" si="136">"unclassified_"&amp;H1308</f>
-        <v>unclassified_bugs</v>
-      </c>
-      <c r="L1308" s="1" t="s">
-        <v>2355</v>
-      </c>
-      <c r="M1308" s="7"/>
-      <c r="N1308" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="1309" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A1309" s="7" t="s">
-        <v>2405</v>
-      </c>
-      <c r="B1309" s="7" t="s">
-        <v>2406</v>
       </c>
       <c r="C1309" s="12" t="s">
         <v>180</v>
@@ -57401,8 +57424,8 @@
         <v>652</v>
       </c>
       <c r="I1309" s="19" t="str">
-        <f t="shared" ref="I1309:I1312" si="137">H1309&amp;"_"&amp;TRIM(A1309)</f>
-        <v>bugs_pi_dom02_BCG_att456m6t</v>
+        <f t="shared" ref="I1309" si="137">H1309&amp;"_"&amp;TRIM(A1309)</f>
+        <v>bugs_pi_dom02_BCG_att456</v>
       </c>
       <c r="J1309" s="7">
         <f t="shared" ref="J1309" si="138">COUNTIF($I$6:$I$1194,I1309)</f>
@@ -57422,46 +57445,51 @@
     </row>
     <row r="1310" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1310" s="7" t="s">
-        <v>2407</v>
-      </c>
-      <c r="B1310" s="8" t="s">
-        <v>2410</v>
-      </c>
-      <c r="C1310" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="D1310" s="55"/>
-      <c r="E1310" s="13"/>
-      <c r="F1310" s="13"/>
-      <c r="G1310" s="8"/>
-      <c r="H1310" s="1" t="s">
+        <v>2405</v>
+      </c>
+      <c r="B1310" s="7" t="s">
+        <v>2406</v>
+      </c>
+      <c r="C1310" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1310" s="12"/>
+      <c r="E1310" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1310" s="12"/>
+      <c r="G1310" s="8" t="s">
+        <v>2296</v>
+      </c>
+      <c r="H1310" s="7" t="s">
         <v>652</v>
       </c>
       <c r="I1310" s="19" t="str">
-        <f t="shared" si="137"/>
-        <v>bugs_nt_NonInsTrombJuga_BCG_att456m6t</v>
+        <f t="shared" ref="I1310:I1314" si="140">H1310&amp;"_"&amp;TRIM(A1310)</f>
+        <v>bugs_pi_dom02_BCG_att456m6t</v>
       </c>
       <c r="J1310" s="7">
-        <f t="shared" ref="J1310:J1312" si="140">COUNTIF($I$6:$I$1123,I1310)</f>
+        <f t="shared" ref="J1310" si="141">COUNTIF($I$6:$I$1194,I1310)</f>
         <v>0</v>
       </c>
-      <c r="K1310" s="1" t="s">
-        <v>1565</v>
+      <c r="K1310" s="1" t="str">
+        <f t="shared" ref="K1310" si="142">"unclassified_"&amp;H1310</f>
+        <v>unclassified_bugs</v>
       </c>
       <c r="L1310" s="1" t="s">
-        <v>1583</v>
-      </c>
-      <c r="M1310" s="1"/>
-      <c r="N1310" s="7" t="b">
-        <v>1</v>
+        <v>2355</v>
+      </c>
+      <c r="M1310" s="7"/>
+      <c r="N1310" s="1" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="1311" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1311" s="7" t="s">
-        <v>2408</v>
+        <v>2407</v>
       </c>
       <c r="B1311" s="8" t="s">
-        <v>2411</v>
+        <v>2410</v>
       </c>
       <c r="C1311" s="16" t="s">
         <v>185</v>
@@ -57474,11 +57502,11 @@
         <v>652</v>
       </c>
       <c r="I1311" s="19" t="str">
-        <f t="shared" si="137"/>
-        <v>bugs_pi_NonInsTrombJuga_BCG_att456m6t</v>
+        <f t="shared" si="140"/>
+        <v>bugs_nt_NonInsTrombJuga_BCG_att456m6t</v>
       </c>
       <c r="J1311" s="7">
-        <f t="shared" si="140"/>
+        <f t="shared" ref="J1311:J1313" si="143">COUNTIF($I$6:$I$1123,I1311)</f>
         <v>0</v>
       </c>
       <c r="K1311" s="1" t="s">
@@ -57489,15 +57517,15 @@
       </c>
       <c r="M1311" s="1"/>
       <c r="N1311" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1312" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1312" s="7" t="s">
-        <v>2409</v>
+        <v>2408</v>
       </c>
       <c r="B1312" s="8" t="s">
-        <v>2412</v>
+        <v>2411</v>
       </c>
       <c r="C1312" s="16" t="s">
         <v>185</v>
@@ -57510,11 +57538,11 @@
         <v>652</v>
       </c>
       <c r="I1312" s="19" t="str">
-        <f t="shared" si="137"/>
-        <v>bugs_pt_NonInsTrombJuga_BCG_att456m6t</v>
+        <f t="shared" si="140"/>
+        <v>bugs_pi_NonInsTrombJuga_BCG_att456m6t</v>
       </c>
       <c r="J1312" s="7">
-        <f t="shared" si="140"/>
+        <f t="shared" si="143"/>
         <v>0</v>
       </c>
       <c r="K1312" s="1" t="s">
@@ -57525,20 +57553,95 @@
       </c>
       <c r="M1312" s="1"/>
       <c r="N1312" s="7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2022" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2022" s="52"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A1313" s="7" t="s">
+        <v>2409</v>
+      </c>
+      <c r="B1313" s="8" t="s">
+        <v>2412</v>
+      </c>
+      <c r="C1313" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="D1313" s="55"/>
+      <c r="E1313" s="13"/>
+      <c r="F1313" s="13"/>
+      <c r="G1313" s="8"/>
+      <c r="H1313" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="I1313" s="19" t="str">
+        <f t="shared" si="140"/>
+        <v>bugs_pt_NonInsTrombJuga_BCG_att456m6t</v>
+      </c>
+      <c r="J1313" s="7">
+        <f t="shared" si="143"/>
+        <v>0</v>
+      </c>
+      <c r="K1313" s="1" t="s">
+        <v>1565</v>
+      </c>
+      <c r="L1313" s="1" t="s">
+        <v>1583</v>
+      </c>
+      <c r="M1313" s="1"/>
+      <c r="N1313" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1314" s="7" t="s">
+        <v>2420</v>
+      </c>
+      <c r="B1314" s="7" t="s">
+        <v>2421</v>
+      </c>
+      <c r="C1314" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D1314" s="12"/>
+      <c r="E1314" s="12" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F1314" s="12"/>
+      <c r="G1314" s="8" t="s">
+        <v>2329</v>
+      </c>
+      <c r="H1314" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="I1314" s="19" t="str">
+        <f t="shared" si="140"/>
+        <v>bugs_pi_dom02_BCG_att456t</v>
+      </c>
+      <c r="J1314" s="7">
+        <f t="shared" ref="J1314" si="144">COUNTIF($I$6:$I$1194,I1314)</f>
+        <v>0</v>
+      </c>
+      <c r="K1314" s="1" t="str">
+        <f t="shared" ref="K1314" si="145">"unclassified_"&amp;H1314</f>
+        <v>unclassified_bugs</v>
+      </c>
+      <c r="L1314" s="1" t="s">
+        <v>2355</v>
+      </c>
+      <c r="M1314" s="7"/>
+      <c r="N1314" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2023" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2023" s="52"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:N1312" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter ref="A5:N1313" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="pi_dom02"/>
-        <filter val="pi_dom02_BCG_att456_NoJugaRiss"/>
-        <filter val="pi_dom02_BCG_att456m6t"/>
-        <filter val="pi_dom02_ExclSchool"/>
+        <filter val="pi_dom01_BCG_att456"/>
+        <filter val="pi_dom01_BCG_att456m6t"/>
       </filters>
     </filterColumn>
   </autoFilter>
